--- a/Property_Scope_Plan_Jupiter_v2.xlsx
+++ b/Property_Scope_Plan_Jupiter_v2.xlsx
@@ -101,12 +101,48 @@
         </r>
       </text>
     </comment>
+    <comment ref="O67" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Status/notes look carried over from the previous property template; the 21-Sep session reports Jupiter fully stripped with no MEP work done - verify status, cost and balance.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O68" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Status/notes look carried over from the previous property template; the 21-Sep session reports Jupiter fully stripped with no MEP work done - verify status, cost and balance.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O74" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Status/notes look carried over from the previous property template; the 21-Sep session reports Jupiter fully stripped with no MEP work done - verify status, cost and balance.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="722">
   <si>
     <t xml:space="preserve">COMPLETE RENOVATION - PENDING ITEMS + COST TRACKER</t>
   </si>
@@ -138,7 +174,7 @@
     <t xml:space="preserve">Updated: July 2, 2026 - costs per Project Status &amp; Cost Summary PDF</t>
   </si>
   <si>
-    <t xml:space="preserve">Schedule proposal Sep 24, 2026 (session 2026-ACTA-JUPITER-01): dates in F-H are driven by 'Schedule Logic'. N1-N9 = activities added from the 21-Sep session.</t>
+    <t xml:space="preserve">Schedule proposal Sep 24, 2026 (session 2026-ACTA-JUPITER-01): dates in F-H are driven by 'Schedule Logic'. N1-N10 = activities added from the 21-Sep session.</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -405,7 +441,7 @@
     <t xml:space="preserve">Site protection + inventory (windows, railings, outlets, switches, smoke detectors)</t>
   </si>
   <si>
-    <t xml:space="preserve">Added from 21-Sep session [16:10]-[17:08]: tape/plastic on windows + railings; inventory and cover outlets, switches, smoke detectors before any new trade enters (lesson: tile crew cement on windows/railings)</t>
+    <t xml:space="preserve">Added from 21-Sep session [16:10]-[17:08]: tape/plastic on windows + railings; inventory and cover outlets, switches, smoke detectors before any new trade enters (lesson: tile crew cement on windows/railings); seal AC returns/registers, air handler off or filtered during dusty work</t>
   </si>
   <si>
     <t xml:space="preserve">N2</t>
@@ -678,6 +714,21 @@
     <t xml:space="preserve">$1,000-$2,100 range; final cost depends on slab repaired in-house vs fully replaced; permit + inspection required (quick turnaround); A: hire service company</t>
   </si>
   <si>
+    <t xml:space="preserve">N10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct modifications - removed partitions, kitchen hood + bath exhaust ducting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added from 21-Sep session [12:07]-[12:38] + [33:19]: walls removed for open concept may carry supply/return runs; hood + bath fan ducts (master coupling pending) go in before walls close. Mechanical rough inspected in N4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ductwork inspection / repair / clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean AFTER drywall sanding + primer (dust); returns/registers sealed and filters changed during dusty work</t>
+  </si>
+  <si>
     <t xml:space="preserve">HVAC coil cleaning</t>
   </si>
   <si>
@@ -687,9 +738,6 @@
     <t xml:space="preserve">HVAC coolant refill service</t>
   </si>
   <si>
-    <t xml:space="preserve">Ductwork inspection / repair / clean</t>
-  </si>
-  <si>
     <t xml:space="preserve">AC diffusers</t>
   </si>
   <si>
@@ -1425,7 +1473,7 @@
     <t xml:space="preserve">Repaired / replaced as needed</t>
   </si>
   <si>
-    <t xml:space="preserve">SCHEDULE LOGIC - PRE-CONSTRUCTION, DEMO/STRUCTURE, ELECTRICAL, PLUMBING (proposed baseline)</t>
+    <t xml:space="preserve">SCHEDULE LOGIC - PRE-CONSTRUCTION, DEMO/STRUCTURE, ELECTRICAL, PLUMBING, HVAC (proposed baseline)</t>
   </si>
   <si>
     <t xml:space="preserve">Working days Mon-Fri excluding holidays in column M. Edit only the yellow cells (baseline) and blue cells (lag, duration, effort); Start/End recalculate and feed Scope Checklist columns F-H.</t>
@@ -1626,7 +1674,7 @@
     <t xml:space="preserve">Existing scope note; same crew as N3</t>
   </si>
   <si>
-    <t xml:space="preserve">After framing, slabs, panel, electrical rough-in (N7) + plumbing top-out (N9); link HVAC ductwork when HVAC is scheduled</t>
+    <t xml:space="preserve">After framing, slabs, panel, electrical rough-in (N7), plumbing top-out (N9) + duct modifications (N10)</t>
   </si>
   <si>
     <t xml:space="preserve">[35:22]-[36:34] each step waits for next-day inspector; buffer for 1 re-inspection</t>
@@ -1746,6 +1794,36 @@
     <t xml:space="preserve">With final plumbing labor</t>
   </si>
   <si>
+    <t xml:space="preserve">After mechanical permit + framing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[33:19] mechanical sub-permit; [12:07] removed partitions; must be in before N4 inspection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After primer (dusty work finished)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industry practice: clean ducts after sanding, not before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After primer (with duct cleaning visit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing scope: part of maintenance line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same visit as coil cleaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing scope: purchase early, install after final paint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umbrella: AC slab repair start -&gt; last maintenance item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract envelope ($2,100); hours carried by the detail rows</t>
+  </si>
+  <si>
     <t xml:space="preserve">Milestones</t>
   </si>
   <si>
@@ -1770,6 +1848,9 @@
     <t xml:space="preserve">Plumbing complete (trim)</t>
   </si>
   <si>
+    <t xml:space="preserve">HVAC complete (diffusers + thermostat)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total effort - Pre-Construction (hrs)</t>
   </si>
   <si>
@@ -1780,6 +1861,9 @@
   </si>
   <si>
     <t xml:space="preserve">Total effort - Plumbing (hrs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total effort - HVAC (hrs)</t>
   </si>
   <si>
     <t xml:space="preserve">3-WEEK EXECUTION PLAN - A = Andres | V = Victor | H = Hans | S = Sub | M = Martin (stone) | G = Gino (glass)</t>
@@ -5798,258 +5882,351 @@
       <c r="O66" s="56"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="10" t="n">
+      <c r="A67" s="30" t="n">
         <v>73</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="E67" s="29" t="s">
+      <c r="E67" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="17" t="s">
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
+      <c r="H67" s="50"/>
+      <c r="I67" s="51"/>
+      <c r="J67" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="K67" s="18"/>
-      <c r="L67" s="19"/>
-      <c r="M67" s="19"/>
-      <c r="N67" s="11"/>
-      <c r="O67" s="12" t="s">
+      <c r="K67" s="24"/>
+      <c r="L67" s="25"/>
+      <c r="M67" s="25"/>
+      <c r="N67" s="21"/>
+      <c r="O67" s="22" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="30" t="n">
+      <c r="A68" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="B68" s="21" t="s">
+      <c r="B68" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="D68" s="22" t="s">
+      <c r="D68" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="E68" s="27" t="s">
+      <c r="E68" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F68" s="27"/>
-      <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="27"/>
-      <c r="J68" s="27" t="s">
+      <c r="F68" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G69</f>
+        <v>46371</v>
+      </c>
+      <c r="G68" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H69</f>
+        <v>46415</v>
+      </c>
+      <c r="H68" s="40" t="str">
+        <f aca="false">'Schedule Logic'!I69</f>
+        <v>-</v>
+      </c>
+      <c r="I68" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="K68" s="24" t="s">
+      <c r="K68" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="L68" s="25" t="n">
+      <c r="L68" s="19" t="n">
         <v>2100</v>
       </c>
-      <c r="M68" s="25" t="n">
+      <c r="M68" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="N68" s="21"/>
-      <c r="O68" s="22" t="s">
+      <c r="N68" s="11"/>
+      <c r="O68" s="12" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="10" t="n">
+    <row r="69" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D69" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F69" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G63</f>
+        <v>46378</v>
+      </c>
+      <c r="G69" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H63</f>
+        <v>46384</v>
+      </c>
+      <c r="H69" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I63</f>
+        <v>24</v>
+      </c>
+      <c r="I69" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="K69" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="L69" s="25"/>
+      <c r="M69" s="25"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F70" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G64</f>
+        <v>46414</v>
+      </c>
+      <c r="G70" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H64</f>
+        <v>46415</v>
+      </c>
+      <c r="H70" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I64</f>
+        <v>16</v>
+      </c>
+      <c r="I70" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="K70" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="L70" s="19"/>
+      <c r="M70" s="19"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="30" t="n">
         <v>75</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B71" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C71" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="D69" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="E69" s="13" t="s">
+      <c r="D71" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="E71" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13" t="s">
+      <c r="F71" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G65</f>
+        <v>46414</v>
+      </c>
+      <c r="G71" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H65</f>
+        <v>46414</v>
+      </c>
+      <c r="H71" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I65</f>
+        <v>4</v>
+      </c>
+      <c r="I71" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="K69" s="18" t="s">
+      <c r="K71" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L69" s="19"/>
-      <c r="M69" s="19"/>
-      <c r="N69" s="11"/>
-      <c r="O69" s="12" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="30" t="n">
+      <c r="L71" s="25"/>
+      <c r="M71" s="25"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="22" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="B70" s="21" t="s">
+      <c r="B72" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C70" s="21" t="s">
+      <c r="C72" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D70" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="E70" s="27" t="s">
+      <c r="D72" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E72" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27" t="s">
+      <c r="F72" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G66</f>
+        <v>46414</v>
+      </c>
+      <c r="G72" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H66</f>
+        <v>46414</v>
+      </c>
+      <c r="H72" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I66</f>
+        <v>3</v>
+      </c>
+      <c r="I72" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="K70" s="24" t="s">
+      <c r="K72" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="L70" s="25"/>
-      <c r="M70" s="25"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="22" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="10" t="n">
-        <v>77</v>
-      </c>
-      <c r="B71" s="11" t="s">
+      <c r="L72" s="19"/>
+      <c r="M72" s="19"/>
+      <c r="N72" s="11"/>
+      <c r="O72" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="30" t="n">
+        <v>78</v>
+      </c>
+      <c r="B73" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C73" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="D71" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="E71" s="13" t="s">
+      <c r="D73" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="E73" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="K71" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="L71" s="19"/>
-      <c r="M71" s="19"/>
-      <c r="N71" s="11"/>
-      <c r="O71" s="12"/>
-    </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="30" t="n">
-        <v>78</v>
-      </c>
-      <c r="B72" s="21" t="s">
+      <c r="F73" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G67</f>
+        <v>46443</v>
+      </c>
+      <c r="G73" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H67</f>
+        <v>46443</v>
+      </c>
+      <c r="H73" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I67</f>
+        <v>4</v>
+      </c>
+      <c r="I73" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="K73" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="L73" s="25"/>
+      <c r="M73" s="25"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="B74" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C72" s="21" t="s">
+      <c r="C74" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D72" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="E72" s="27" t="s">
+      <c r="D74" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="E74" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="27"/>
-      <c r="I72" s="27"/>
-      <c r="J72" s="27" t="s">
+      <c r="F74" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G68</f>
+        <v>46443</v>
+      </c>
+      <c r="G74" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H68</f>
+        <v>46443</v>
+      </c>
+      <c r="H74" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I68</f>
+        <v>2</v>
+      </c>
+      <c r="I74" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="K72" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="L72" s="25"/>
-      <c r="M72" s="25"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="22" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="10" t="n">
-        <v>79</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="K73" s="18" t="s">
+      <c r="K74" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="L73" s="19"/>
-      <c r="M73" s="19"/>
-      <c r="N73" s="11"/>
-      <c r="O73" s="12" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="10" t="n">
-        <v>81</v>
-      </c>
-      <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="10"/>
-      <c r="N74" s="10"/>
-      <c r="O74" s="10"/>
+      <c r="L74" s="19"/>
+      <c r="M74" s="19"/>
+      <c r="N74" s="11"/>
+      <c r="O74" s="12" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B75" s="55"/>
       <c r="C75" s="55"/>
@@ -6071,13 +6248,13 @@
         <v>80</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D76" s="22" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E76" s="38" t="s">
         <v>81</v>
@@ -6087,7 +6264,7 @@
       <c r="H76" s="38"/>
       <c r="I76" s="38"/>
       <c r="J76" s="27" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="K76" s="24" t="s">
         <v>71</v>
@@ -6099,10 +6276,10 @@
         <v>4875</v>
       </c>
       <c r="N76" s="21" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="O76" s="22" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6110,13 +6287,13 @@
         <v>81</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E77" s="13" t="s">
         <v>30</v>
@@ -6126,10 +6303,10 @@
       <c r="H77" s="13"/>
       <c r="I77" s="13"/>
       <c r="J77" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K77" s="18" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L77" s="19" t="n">
         <v>5925</v>
@@ -6138,10 +6315,10 @@
         <v>4500</v>
       </c>
       <c r="N77" s="11" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O77" s="12" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6149,13 +6326,13 @@
         <v>82</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D78" s="22" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E78" s="27" t="s">
         <v>30</v>
@@ -6165,7 +6342,7 @@
       <c r="H78" s="27"/>
       <c r="I78" s="27"/>
       <c r="J78" s="27" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K78" s="24" t="s">
         <v>53</v>
@@ -6180,13 +6357,13 @@
         <v>83</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E79" s="13" t="s">
         <v>30</v>
@@ -6196,7 +6373,7 @@
       <c r="H79" s="13"/>
       <c r="I79" s="13"/>
       <c r="J79" s="13" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K79" s="18" t="s">
         <v>158</v>
@@ -6205,7 +6382,7 @@
       <c r="M79" s="19"/>
       <c r="N79" s="11"/>
       <c r="O79" s="12" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6213,13 +6390,13 @@
         <v>84</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D80" s="22" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E80" s="27" t="s">
         <v>30</v>
@@ -6242,7 +6419,7 @@
       </c>
       <c r="N80" s="21"/>
       <c r="O80" s="22" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6250,13 +6427,13 @@
         <v>85</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E81" s="29" t="s">
         <v>126</v>
@@ -6279,13 +6456,13 @@
         <v>86</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D82" s="22" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E82" s="27" t="s">
         <v>30</v>
@@ -6304,7 +6481,7 @@
       <c r="M82" s="25"/>
       <c r="N82" s="21"/>
       <c r="O82" s="22" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6328,7 +6505,7 @@
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B84" s="55"/>
       <c r="C84" s="55"/>
@@ -6350,13 +6527,13 @@
         <v>87</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E85" s="13" t="s">
         <v>30</v>
@@ -6366,7 +6543,7 @@
       <c r="H85" s="13"/>
       <c r="I85" s="13"/>
       <c r="J85" s="13" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="K85" s="18" t="s">
         <v>71</v>
@@ -6374,10 +6551,10 @@
       <c r="L85" s="19"/>
       <c r="M85" s="19"/>
       <c r="N85" s="11" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="O85" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6385,13 +6562,13 @@
         <v>88</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D86" s="22" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E86" s="27" t="s">
         <v>30</v>
@@ -6401,7 +6578,7 @@
       <c r="H86" s="27"/>
       <c r="I86" s="27"/>
       <c r="J86" s="27" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K86" s="24" t="s">
         <v>53</v>
@@ -6410,7 +6587,7 @@
       <c r="M86" s="25"/>
       <c r="N86" s="21"/>
       <c r="O86" s="22" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6418,13 +6595,13 @@
         <v>89</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E87" s="13" t="s">
         <v>30</v>
@@ -6434,7 +6611,7 @@
       <c r="H87" s="13"/>
       <c r="I87" s="13"/>
       <c r="J87" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K87" s="18" t="s">
         <v>53</v>
@@ -6442,10 +6619,10 @@
       <c r="L87" s="19"/>
       <c r="M87" s="19"/>
       <c r="N87" s="11" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O87" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6453,13 +6630,13 @@
         <v>90</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D88" s="22" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E88" s="27" t="s">
         <v>30</v>
@@ -6469,14 +6646,14 @@
       <c r="H88" s="27"/>
       <c r="I88" s="27"/>
       <c r="J88" s="54" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K88" s="24"/>
       <c r="L88" s="25"/>
       <c r="M88" s="25"/>
       <c r="N88" s="21"/>
       <c r="O88" s="22" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6484,13 +6661,13 @@
         <v>91</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E89" s="13" t="s">
         <v>30</v>
@@ -6500,7 +6677,7 @@
       <c r="H89" s="13"/>
       <c r="I89" s="13"/>
       <c r="J89" s="13" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K89" s="18" t="s">
         <v>92</v>
@@ -6509,7 +6686,7 @@
       <c r="M89" s="19"/>
       <c r="N89" s="11"/>
       <c r="O89" s="12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6517,13 +6694,13 @@
         <v>92</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D90" s="22" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E90" s="27" t="s">
         <v>30</v>
@@ -6533,14 +6710,14 @@
       <c r="H90" s="27"/>
       <c r="I90" s="27"/>
       <c r="J90" s="38" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K90" s="24"/>
       <c r="L90" s="25"/>
       <c r="M90" s="25"/>
       <c r="N90" s="21"/>
       <c r="O90" s="22" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6548,13 +6725,13 @@
         <v>93</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E91" s="13" t="s">
         <v>30</v>
@@ -6573,7 +6750,7 @@
       <c r="M91" s="19"/>
       <c r="N91" s="11"/>
       <c r="O91" s="12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6581,13 +6758,13 @@
         <v>94</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D92" s="22" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E92" s="27" t="s">
         <v>30</v>
@@ -6597,7 +6774,7 @@
       <c r="H92" s="27"/>
       <c r="I92" s="27"/>
       <c r="J92" s="27" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K92" s="24" t="s">
         <v>53</v>
@@ -6606,7 +6783,7 @@
       <c r="M92" s="25"/>
       <c r="N92" s="21"/>
       <c r="O92" s="22" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6614,13 +6791,13 @@
         <v>95</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E93" s="13" t="s">
         <v>30</v>
@@ -6630,7 +6807,7 @@
       <c r="H93" s="13"/>
       <c r="I93" s="13"/>
       <c r="J93" s="13" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K93" s="18" t="s">
         <v>92</v>
@@ -6639,7 +6816,7 @@
       <c r="M93" s="19"/>
       <c r="N93" s="11"/>
       <c r="O93" s="12" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6647,13 +6824,13 @@
         <v>96</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D94" s="22" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E94" s="27" t="s">
         <v>30</v>
@@ -6663,7 +6840,7 @@
       <c r="H94" s="27"/>
       <c r="I94" s="27"/>
       <c r="J94" s="27" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K94" s="24" t="s">
         <v>92</v>
@@ -6672,7 +6849,7 @@
       <c r="M94" s="25"/>
       <c r="N94" s="21"/>
       <c r="O94" s="22" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6680,13 +6857,13 @@
         <v>97</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E95" s="13" t="s">
         <v>30</v>
@@ -6696,7 +6873,7 @@
       <c r="H95" s="13"/>
       <c r="I95" s="13"/>
       <c r="J95" s="13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K95" s="18" t="s">
         <v>92</v>
@@ -6705,7 +6882,7 @@
       <c r="M95" s="19"/>
       <c r="N95" s="11"/>
       <c r="O95" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6713,13 +6890,13 @@
         <v>98</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D96" s="22" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E96" s="27" t="s">
         <v>30</v>
@@ -6729,7 +6906,7 @@
       <c r="H96" s="27"/>
       <c r="I96" s="27"/>
       <c r="J96" s="38" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K96" s="24" t="s">
         <v>102</v>
@@ -6740,7 +6917,7 @@
       </c>
       <c r="N96" s="21"/>
       <c r="O96" s="22" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6748,13 +6925,13 @@
         <v>99</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E97" s="13" t="s">
         <v>30</v>
@@ -6773,7 +6950,7 @@
       <c r="M97" s="19"/>
       <c r="N97" s="11"/>
       <c r="O97" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6781,13 +6958,13 @@
         <v>100</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D98" s="22" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E98" s="27" t="s">
         <v>30</v>
@@ -6797,18 +6974,18 @@
       <c r="H98" s="27"/>
       <c r="I98" s="27"/>
       <c r="J98" s="54" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K98" s="24" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="L98" s="25"/>
       <c r="M98" s="25"/>
       <c r="N98" s="21" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O98" s="22" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6816,13 +6993,13 @@
         <v>101</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E99" s="13" t="s">
         <v>30</v>
@@ -6832,10 +7009,10 @@
       <c r="H99" s="13"/>
       <c r="I99" s="13"/>
       <c r="J99" s="57" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K99" s="18" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="L99" s="19" t="n">
         <v>3000</v>
@@ -6844,10 +7021,10 @@
         <v>3000</v>
       </c>
       <c r="N99" s="11" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="O99" s="12" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6855,13 +7032,13 @@
         <v>102</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D100" s="22" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E100" s="27" t="s">
         <v>30</v>
@@ -6871,7 +7048,7 @@
       <c r="H100" s="27"/>
       <c r="I100" s="27"/>
       <c r="J100" s="38" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="K100" s="24" t="s">
         <v>123</v>
@@ -6886,13 +7063,13 @@
         <v>103</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E101" s="13" t="s">
         <v>30</v>
@@ -6902,7 +7079,7 @@
       <c r="H101" s="13"/>
       <c r="I101" s="13"/>
       <c r="J101" s="33" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K101" s="18" t="s">
         <v>123</v>
@@ -6936,13 +7113,13 @@
         <v>104</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D103" s="22" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E103" s="27" t="s">
         <v>30</v>
@@ -6955,13 +7132,13 @@
         <v>154</v>
       </c>
       <c r="K103" s="24" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="L103" s="25"/>
       <c r="M103" s="25"/>
       <c r="N103" s="21"/>
       <c r="O103" s="22" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6988,13 +7165,13 @@
         <v>105</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E105" s="13" t="s">
         <v>30</v>
@@ -7013,12 +7190,12 @@
       <c r="M105" s="19"/>
       <c r="N105" s="11"/>
       <c r="O105" s="12" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="9" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B106" s="55"/>
       <c r="C106" s="55"/>
@@ -7040,13 +7217,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="21" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D107" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E107" s="27" t="s">
         <v>30</v>
@@ -7056,7 +7233,7 @@
       <c r="H107" s="27"/>
       <c r="I107" s="27"/>
       <c r="J107" s="27" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="K107" s="24" t="s">
         <v>71</v>
@@ -7064,10 +7241,10 @@
       <c r="L107" s="25"/>
       <c r="M107" s="25"/>
       <c r="N107" s="21" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="O107" s="22" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7075,13 +7252,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E108" s="13" t="s">
         <v>30</v>
@@ -7091,7 +7268,7 @@
       <c r="H108" s="13"/>
       <c r="I108" s="13"/>
       <c r="J108" s="13" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K108" s="18" t="s">
         <v>53</v>
@@ -7100,7 +7277,7 @@
       <c r="M108" s="19"/>
       <c r="N108" s="11"/>
       <c r="O108" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7108,13 +7285,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="21" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D109" s="22" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E109" s="27" t="s">
         <v>30</v>
@@ -7124,7 +7301,7 @@
       <c r="H109" s="27"/>
       <c r="I109" s="27"/>
       <c r="J109" s="27" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K109" s="24" t="s">
         <v>53</v>
@@ -7132,10 +7309,10 @@
       <c r="L109" s="25"/>
       <c r="M109" s="25"/>
       <c r="N109" s="21" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O109" s="22" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7143,13 +7320,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>30</v>
@@ -7159,14 +7336,14 @@
       <c r="H110" s="13"/>
       <c r="I110" s="13"/>
       <c r="J110" s="57" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K110" s="18"/>
       <c r="L110" s="19"/>
       <c r="M110" s="19"/>
       <c r="N110" s="11"/>
       <c r="O110" s="12" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7174,13 +7351,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="21" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D111" s="22" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E111" s="27" t="s">
         <v>30</v>
@@ -7190,7 +7367,7 @@
       <c r="H111" s="27"/>
       <c r="I111" s="27"/>
       <c r="J111" s="27" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K111" s="24" t="s">
         <v>92</v>
@@ -7199,7 +7376,7 @@
       <c r="M111" s="25"/>
       <c r="N111" s="21"/>
       <c r="O111" s="22" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7207,13 +7384,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E112" s="13" t="s">
         <v>30</v>
@@ -7232,7 +7409,7 @@
       <c r="M112" s="19"/>
       <c r="N112" s="11"/>
       <c r="O112" s="12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7240,13 +7417,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="21" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D113" s="22" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E113" s="27" t="s">
         <v>30</v>
@@ -7256,7 +7433,7 @@
       <c r="H113" s="27"/>
       <c r="I113" s="27"/>
       <c r="J113" s="27" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K113" s="24" t="s">
         <v>92</v>
@@ -7265,7 +7442,7 @@
       <c r="M113" s="25"/>
       <c r="N113" s="21"/>
       <c r="O113" s="22" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7273,13 +7450,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E114" s="13" t="s">
         <v>30</v>
@@ -7289,7 +7466,7 @@
       <c r="H114" s="13"/>
       <c r="I114" s="13"/>
       <c r="J114" s="13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K114" s="18" t="s">
         <v>92</v>
@@ -7298,7 +7475,7 @@
       <c r="M114" s="19"/>
       <c r="N114" s="11"/>
       <c r="O114" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7306,13 +7483,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D115" s="22" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E115" s="27" t="s">
         <v>30</v>
@@ -7322,7 +7499,7 @@
       <c r="H115" s="27"/>
       <c r="I115" s="27"/>
       <c r="J115" s="38" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K115" s="24" t="s">
         <v>102</v>
@@ -7331,7 +7508,7 @@
       <c r="M115" s="25"/>
       <c r="N115" s="21"/>
       <c r="O115" s="22" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7339,13 +7516,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E116" s="13" t="s">
         <v>30</v>
@@ -7364,7 +7541,7 @@
       <c r="M116" s="19"/>
       <c r="N116" s="11"/>
       <c r="O116" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7372,13 +7549,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D117" s="22" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E117" s="27" t="s">
         <v>30</v>
@@ -7388,15 +7565,15 @@
       <c r="H117" s="27"/>
       <c r="I117" s="27"/>
       <c r="J117" s="54" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K117" s="24" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="L117" s="25"/>
       <c r="M117" s="25"/>
       <c r="N117" s="21" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O117" s="22"/>
     </row>
@@ -7405,13 +7582,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E118" s="13" t="s">
         <v>30</v>
@@ -7421,16 +7598,16 @@
       <c r="H118" s="13"/>
       <c r="I118" s="13"/>
       <c r="J118" s="57" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K118" s="18" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="L118" s="19"/>
       <c r="M118" s="19"/>
       <c r="N118" s="11"/>
       <c r="O118" s="12" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7457,13 +7634,13 @@
         <v>118</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D120" s="22" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E120" s="27" t="s">
         <v>30</v>
@@ -7473,7 +7650,7 @@
       <c r="H120" s="27"/>
       <c r="I120" s="27"/>
       <c r="J120" s="38" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K120" s="24" t="s">
         <v>123</v>
@@ -7507,13 +7684,13 @@
         <v>119</v>
       </c>
       <c r="B122" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C122" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="C122" s="11" t="s">
-        <v>271</v>
-      </c>
       <c r="D122" s="12" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>30</v>
@@ -7532,12 +7709,12 @@
       <c r="M122" s="19"/>
       <c r="N122" s="11"/>
       <c r="O122" s="12" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="9" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B123" s="55"/>
       <c r="C123" s="55"/>
@@ -7559,13 +7736,13 @@
         <v>120</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D124" s="22" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E124" s="27" t="s">
         <v>30</v>
@@ -7575,7 +7752,7 @@
       <c r="H124" s="27"/>
       <c r="I124" s="27"/>
       <c r="J124" s="38" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K124" s="24"/>
       <c r="L124" s="25"/>
@@ -7588,13 +7765,13 @@
         <v>121</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E125" s="13" t="s">
         <v>30</v>
@@ -7604,7 +7781,7 @@
       <c r="H125" s="13"/>
       <c r="I125" s="13"/>
       <c r="J125" s="33" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K125" s="18"/>
       <c r="L125" s="19"/>
@@ -7617,13 +7794,13 @@
         <v>122</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D126" s="22" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E126" s="27" t="s">
         <v>30</v>
@@ -7633,16 +7810,16 @@
       <c r="H126" s="27"/>
       <c r="I126" s="27"/>
       <c r="J126" s="38" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K126" s="24" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="L126" s="25"/>
       <c r="M126" s="25"/>
       <c r="N126" s="21"/>
       <c r="O126" s="22" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7650,13 +7827,13 @@
         <v>123</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E127" s="13" t="s">
         <v>30</v>
@@ -7666,7 +7843,7 @@
       <c r="H127" s="13"/>
       <c r="I127" s="13"/>
       <c r="J127" s="33" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K127" s="18" t="s">
         <v>123</v>
@@ -7681,13 +7858,13 @@
         <v>124</v>
       </c>
       <c r="B128" s="21" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D128" s="22" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E128" s="27" t="s">
         <v>30</v>
@@ -7697,7 +7874,7 @@
       <c r="H128" s="27"/>
       <c r="I128" s="27"/>
       <c r="J128" s="38" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K128" s="24" t="s">
         <v>123</v>
@@ -7712,13 +7889,13 @@
         <v>125</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E129" s="13" t="s">
         <v>30</v>
@@ -7728,7 +7905,7 @@
       <c r="H129" s="13"/>
       <c r="I129" s="13"/>
       <c r="J129" s="33" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K129" s="18" t="s">
         <v>123</v>
@@ -7743,13 +7920,13 @@
         <v>126</v>
       </c>
       <c r="B130" s="21" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C130" s="21" t="s">
         <v>134</v>
       </c>
       <c r="D130" s="22" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E130" s="27" t="s">
         <v>30</v>
@@ -7759,7 +7936,7 @@
       <c r="H130" s="27"/>
       <c r="I130" s="27"/>
       <c r="J130" s="38" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="K130" s="24" t="s">
         <v>123</v>
@@ -7768,7 +7945,7 @@
       <c r="M130" s="25"/>
       <c r="N130" s="21"/>
       <c r="O130" s="22" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7776,13 +7953,13 @@
         <v>127</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C131" s="11" t="s">
         <v>134</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E131" s="13" t="s">
         <v>30</v>
@@ -7792,14 +7969,14 @@
       <c r="H131" s="13"/>
       <c r="I131" s="13"/>
       <c r="J131" s="33" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K131" s="11"/>
       <c r="L131" s="19"/>
       <c r="M131" s="19"/>
       <c r="N131" s="11"/>
       <c r="O131" s="12" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7807,13 +7984,13 @@
         <v>128</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C132" s="21" t="s">
         <v>134</v>
       </c>
       <c r="D132" s="22" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E132" s="27" t="s">
         <v>30</v>
@@ -7823,7 +8000,7 @@
       <c r="H132" s="27"/>
       <c r="I132" s="27"/>
       <c r="J132" s="38" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K132" s="24" t="s">
         <v>123</v>
@@ -7838,13 +8015,13 @@
         <v>129</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C133" s="11" t="s">
         <v>134</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E133" s="13" t="s">
         <v>30</v>
@@ -7854,7 +8031,7 @@
       <c r="H133" s="13"/>
       <c r="I133" s="13"/>
       <c r="J133" s="57" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="K133" s="18" t="s">
         <v>71</v>
@@ -7863,7 +8040,7 @@
       <c r="M133" s="19"/>
       <c r="N133" s="11"/>
       <c r="O133" s="12" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7871,13 +8048,13 @@
         <v>130</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D134" s="22" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E134" s="27" t="s">
         <v>30</v>
@@ -7887,7 +8064,7 @@
       <c r="H134" s="27"/>
       <c r="I134" s="27"/>
       <c r="J134" s="38" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="K134" s="24" t="s">
         <v>71</v>
@@ -7896,7 +8073,7 @@
       <c r="M134" s="25"/>
       <c r="N134" s="21"/>
       <c r="O134" s="22" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7904,13 +8081,13 @@
         <v>131</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E135" s="13" t="s">
         <v>30</v>
@@ -7920,7 +8097,7 @@
       <c r="H135" s="13"/>
       <c r="I135" s="13"/>
       <c r="J135" s="33" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="K135" s="18" t="s">
         <v>71</v>
@@ -7929,7 +8106,7 @@
       <c r="M135" s="19"/>
       <c r="N135" s="11"/>
       <c r="O135" s="12" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7975,13 +8152,13 @@
         <v>133</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E138" s="13" t="s">
         <v>30</v>
@@ -7991,16 +8168,16 @@
       <c r="H138" s="13"/>
       <c r="I138" s="13"/>
       <c r="J138" s="33" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="K138" s="18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="L138" s="19"/>
       <c r="M138" s="19"/>
       <c r="N138" s="11"/>
       <c r="O138" s="12" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8008,13 +8185,13 @@
         <v>134</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C139" s="21" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D139" s="22" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E139" s="27" t="s">
         <v>30</v>
@@ -8024,16 +8201,16 @@
       <c r="H139" s="27"/>
       <c r="I139" s="27"/>
       <c r="J139" s="38" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K139" s="24" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="L139" s="25"/>
       <c r="M139" s="25"/>
       <c r="N139" s="21"/>
       <c r="O139" s="22" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8060,13 +8237,13 @@
         <v>135</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E141" s="13" t="s">
         <v>30</v>
@@ -8076,21 +8253,21 @@
       <c r="H141" s="13"/>
       <c r="I141" s="13"/>
       <c r="J141" s="57" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="K141" s="18" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="L141" s="19"/>
       <c r="M141" s="19"/>
       <c r="N141" s="11"/>
       <c r="O141" s="12" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="9" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B142" s="55"/>
       <c r="C142" s="55"/>
@@ -8112,13 +8289,13 @@
         <v>136</v>
       </c>
       <c r="B143" s="21" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C143" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D143" s="22" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E143" s="27" t="s">
         <v>30</v>
@@ -8128,14 +8305,14 @@
       <c r="H143" s="27"/>
       <c r="I143" s="27"/>
       <c r="J143" s="54" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="K143" s="24"/>
       <c r="L143" s="25"/>
       <c r="M143" s="25"/>
       <c r="N143" s="21"/>
       <c r="O143" s="22" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8143,13 +8320,13 @@
         <v>137</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D144" s="12" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E144" s="13" t="s">
         <v>30</v>
@@ -8159,14 +8336,14 @@
       <c r="H144" s="13"/>
       <c r="I144" s="13"/>
       <c r="J144" s="57" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K144" s="18"/>
       <c r="L144" s="19"/>
       <c r="M144" s="19"/>
       <c r="N144" s="11"/>
       <c r="O144" s="12" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8174,13 +8351,13 @@
         <v>138</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C145" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D145" s="22" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E145" s="27" t="s">
         <v>30</v>
@@ -8190,7 +8367,7 @@
       <c r="H145" s="27"/>
       <c r="I145" s="27"/>
       <c r="J145" s="54" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="K145" s="24"/>
       <c r="L145" s="25"/>
@@ -8203,13 +8380,13 @@
         <v>139</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E146" s="13" t="s">
         <v>30</v>
@@ -8219,14 +8396,14 @@
       <c r="H146" s="13"/>
       <c r="I146" s="13"/>
       <c r="J146" s="57" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K146" s="18"/>
       <c r="L146" s="19"/>
       <c r="M146" s="19"/>
       <c r="N146" s="11"/>
       <c r="O146" s="12" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8234,13 +8411,13 @@
         <v>140</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C147" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D147" s="22" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E147" s="27" t="s">
         <v>30</v>
@@ -8250,7 +8427,7 @@
       <c r="H147" s="27"/>
       <c r="I147" s="27"/>
       <c r="J147" s="54" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="K147" s="24"/>
       <c r="L147" s="25"/>
@@ -8263,13 +8440,13 @@
         <v>141</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E148" s="13" t="s">
         <v>30</v>
@@ -8279,7 +8456,7 @@
       <c r="H148" s="13"/>
       <c r="I148" s="13"/>
       <c r="J148" s="57" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K148" s="18"/>
       <c r="L148" s="19"/>
@@ -8292,7 +8469,7 @@
       <c r="B149" s="58"/>
       <c r="C149" s="58"/>
       <c r="D149" s="59" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E149" s="58"/>
       <c r="L149" s="60" t="n">
@@ -8308,7 +8485,7 @@
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="9" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
@@ -8330,13 +8507,13 @@
         <v>15</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E151" s="20" t="s">
         <v>39</v>
@@ -8357,7 +8534,7 @@
       </c>
       <c r="N151" s="11"/>
       <c r="O151" s="12" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8365,13 +8542,13 @@
         <v>16</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C152" s="21" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D152" s="22" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E152" s="31" t="s">
         <v>39</v>
@@ -8394,13 +8571,13 @@
         <v>17</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E153" s="20" t="s">
         <v>39</v>
@@ -8417,7 +8594,7 @@
       <c r="M153" s="19"/>
       <c r="N153" s="11"/>
       <c r="O153" s="12" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8425,13 +8602,13 @@
         <v>18</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C154" s="21" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D154" s="22" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E154" s="27" t="s">
         <v>30</v>
@@ -8441,7 +8618,7 @@
       <c r="H154" s="27"/>
       <c r="I154" s="27"/>
       <c r="J154" s="38" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K154" s="24" t="s">
         <v>123</v>
@@ -8450,7 +8627,7 @@
       <c r="M154" s="25"/>
       <c r="N154" s="21"/>
       <c r="O154" s="22" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8458,13 +8635,13 @@
         <v>19</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E155" s="13" t="s">
         <v>30</v>
@@ -8474,7 +8651,7 @@
       <c r="H155" s="13"/>
       <c r="I155" s="13"/>
       <c r="J155" s="33" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K155" s="18" t="s">
         <v>123</v>
@@ -8483,7 +8660,7 @@
       <c r="M155" s="19"/>
       <c r="N155" s="11"/>
       <c r="O155" s="12" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8491,13 +8668,13 @@
         <v>20</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C156" s="21" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D156" s="22" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E156" s="31" t="s">
         <v>39</v>
@@ -8520,13 +8697,13 @@
         <v>21</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E157" s="13" t="s">
         <v>30</v>
@@ -8536,16 +8713,16 @@
       <c r="H157" s="13"/>
       <c r="I157" s="13"/>
       <c r="J157" s="33" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="K157" s="18" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L157" s="19"/>
       <c r="M157" s="19"/>
       <c r="N157" s="11"/>
       <c r="O157" s="12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8553,13 +8730,13 @@
         <v>22</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D158" s="22" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E158" s="27" t="s">
         <v>30</v>
@@ -8569,7 +8746,7 @@
       <c r="H158" s="27"/>
       <c r="I158" s="27"/>
       <c r="J158" s="38" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="K158" s="24" t="s">
         <v>123</v>
@@ -8584,13 +8761,13 @@
         <v>23</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D159" s="12" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E159" s="13" t="s">
         <v>30</v>
@@ -8600,14 +8777,14 @@
       <c r="H159" s="13"/>
       <c r="I159" s="13"/>
       <c r="J159" s="57" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K159" s="18"/>
       <c r="L159" s="19"/>
       <c r="M159" s="19"/>
       <c r="N159" s="11"/>
       <c r="O159" s="12" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8615,13 +8792,13 @@
         <v>24</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C160" s="21" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D160" s="22" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E160" s="31" t="s">
         <v>39</v>
@@ -8638,7 +8815,7 @@
       <c r="M160" s="25"/>
       <c r="N160" s="21"/>
       <c r="O160" s="22" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8646,13 +8823,13 @@
         <v>25</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E161" s="20" t="s">
         <v>39</v>
@@ -8673,7 +8850,7 @@
       </c>
       <c r="N161" s="11"/>
       <c r="O161" s="12" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8681,13 +8858,13 @@
         <v>26</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D162" s="22" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E162" s="31" t="s">
         <v>39</v>
@@ -8704,7 +8881,7 @@
       <c r="M162" s="25"/>
       <c r="N162" s="21"/>
       <c r="O162" s="22" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8712,13 +8889,13 @@
         <v>27</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E163" s="13" t="s">
         <v>30</v>
@@ -8728,7 +8905,7 @@
       <c r="H163" s="13"/>
       <c r="I163" s="13"/>
       <c r="J163" s="13" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K163" s="18" t="s">
         <v>53</v>
@@ -8737,7 +8914,7 @@
       <c r="M163" s="19"/>
       <c r="N163" s="11"/>
       <c r="O163" s="12" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8745,13 +8922,13 @@
         <v>28</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D164" s="22" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E164" s="27" t="s">
         <v>30</v>
@@ -8761,7 +8938,7 @@
       <c r="H164" s="27"/>
       <c r="I164" s="27"/>
       <c r="J164" s="27" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K164" s="24" t="s">
         <v>53</v>
@@ -8770,7 +8947,7 @@
       <c r="M164" s="25"/>
       <c r="N164" s="21"/>
       <c r="O164" s="22" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8778,13 +8955,13 @@
         <v>29</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E165" s="13" t="s">
         <v>30</v>
@@ -8794,7 +8971,7 @@
       <c r="H165" s="13"/>
       <c r="I165" s="13"/>
       <c r="J165" s="57" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K165" s="18"/>
       <c r="L165" s="19"/>
@@ -8807,13 +8984,13 @@
         <v>30</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D166" s="22" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E166" s="27" t="s">
         <v>30</v>
@@ -8823,10 +9000,10 @@
       <c r="H166" s="27"/>
       <c r="I166" s="27"/>
       <c r="J166" s="38" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K166" s="24" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L166" s="25" t="n">
         <v>7500</v>
@@ -8836,7 +9013,7 @@
       </c>
       <c r="N166" s="21"/>
       <c r="O166" s="22" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8844,13 +9021,13 @@
         <v>31</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E167" s="13" t="s">
         <v>30</v>
@@ -8860,16 +9037,16 @@
       <c r="H167" s="13"/>
       <c r="I167" s="13"/>
       <c r="J167" s="57" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K167" s="18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="L167" s="19"/>
       <c r="M167" s="19"/>
       <c r="N167" s="11"/>
       <c r="O167" s="12" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8877,13 +9054,13 @@
         <v>32</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E168" s="27" t="s">
         <v>30</v>
@@ -8893,14 +9070,14 @@
       <c r="H168" s="27"/>
       <c r="I168" s="27"/>
       <c r="J168" s="38" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K168" s="24"/>
       <c r="L168" s="25"/>
       <c r="M168" s="25"/>
       <c r="N168" s="21"/>
       <c r="O168" s="22" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8908,13 +9085,13 @@
         <v>33</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E169" s="33" t="s">
         <v>81</v>
@@ -8924,10 +9101,10 @@
       <c r="H169" s="33"/>
       <c r="I169" s="33"/>
       <c r="J169" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="K169" s="18" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="L169" s="19" t="n">
         <v>10000</v>
@@ -8937,7 +9114,7 @@
       </c>
       <c r="N169" s="11"/>
       <c r="O169" s="12" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8945,13 +9122,13 @@
         <v>34</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D170" s="22" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E170" s="27" t="s">
         <v>30</v>
@@ -8961,16 +9138,16 @@
       <c r="H170" s="27"/>
       <c r="I170" s="27"/>
       <c r="J170" s="38" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K170" s="24" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L170" s="25"/>
       <c r="M170" s="25"/>
       <c r="N170" s="21"/>
       <c r="O170" s="22" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8978,13 +9155,13 @@
         <v>35</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E171" s="13" t="s">
         <v>30</v>
@@ -8994,7 +9171,7 @@
       <c r="H171" s="13"/>
       <c r="I171" s="13"/>
       <c r="J171" s="33" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K171" s="18"/>
       <c r="L171" s="19" t="n">
@@ -9005,7 +9182,7 @@
       </c>
       <c r="N171" s="11"/>
       <c r="O171" s="12" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9013,13 +9190,13 @@
         <v>36</v>
       </c>
       <c r="B172" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C172" s="21" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D172" s="22" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E172" s="27" t="s">
         <v>30</v>
@@ -9029,10 +9206,10 @@
       <c r="H172" s="27"/>
       <c r="I172" s="27"/>
       <c r="J172" s="38" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="K172" s="24" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="L172" s="25" t="n">
         <v>2000</v>
@@ -9044,7 +9221,7 @@
         <v>175</v>
       </c>
       <c r="O172" s="22" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9052,13 +9229,13 @@
         <v>37</v>
       </c>
       <c r="B173" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E173" s="13" t="s">
         <v>30</v>
@@ -9068,16 +9245,16 @@
       <c r="H173" s="13"/>
       <c r="I173" s="13"/>
       <c r="J173" s="33" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K173" s="18" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="L173" s="19"/>
       <c r="M173" s="19"/>
       <c r="N173" s="11"/>
       <c r="O173" s="12" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9085,13 +9262,13 @@
         <v>38</v>
       </c>
       <c r="B174" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C174" s="21" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D174" s="22" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E174" s="27" t="s">
         <v>30</v>
@@ -9101,7 +9278,7 @@
       <c r="H174" s="27"/>
       <c r="I174" s="27"/>
       <c r="J174" s="27" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="K174" s="24" t="s">
         <v>53</v>
@@ -9112,7 +9289,7 @@
       </c>
       <c r="N174" s="21"/>
       <c r="O174" s="22" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9120,13 +9297,13 @@
         <v>39</v>
       </c>
       <c r="B175" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D175" s="12" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E175" s="13" t="s">
         <v>30</v>
@@ -9136,7 +9313,7 @@
       <c r="H175" s="13"/>
       <c r="I175" s="13"/>
       <c r="J175" s="13" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="K175" s="18" t="s">
         <v>53</v>
@@ -9145,7 +9322,7 @@
       <c r="M175" s="19"/>
       <c r="N175" s="11"/>
       <c r="O175" s="12" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9153,13 +9330,13 @@
         <v>40</v>
       </c>
       <c r="B176" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C176" s="21" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D176" s="22" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E176" s="27" t="s">
         <v>30</v>
@@ -9169,7 +9346,7 @@
       <c r="H176" s="27"/>
       <c r="I176" s="27"/>
       <c r="J176" s="27" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="K176" s="24" t="s">
         <v>53</v>
@@ -9178,7 +9355,7 @@
       <c r="M176" s="25"/>
       <c r="N176" s="21"/>
       <c r="O176" s="22" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9186,13 +9363,13 @@
         <v>41</v>
       </c>
       <c r="B177" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D177" s="12" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E177" s="13" t="s">
         <v>30</v>
@@ -9202,16 +9379,16 @@
       <c r="H177" s="13"/>
       <c r="I177" s="13"/>
       <c r="J177" s="57" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K177" s="18" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L177" s="19"/>
       <c r="M177" s="19"/>
       <c r="N177" s="11"/>
       <c r="O177" s="12" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9219,13 +9396,13 @@
         <v>42</v>
       </c>
       <c r="B178" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C178" s="21" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D178" s="22" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E178" s="27" t="s">
         <v>30</v>
@@ -9235,16 +9412,16 @@
       <c r="H178" s="27"/>
       <c r="I178" s="27"/>
       <c r="J178" s="38" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="K178" s="24" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L178" s="25"/>
       <c r="M178" s="25"/>
       <c r="N178" s="21"/>
       <c r="O178" s="22" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9252,13 +9429,13 @@
         <v>43</v>
       </c>
       <c r="B179" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D179" s="12" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E179" s="13" t="s">
         <v>30</v>
@@ -9268,10 +9445,10 @@
       <c r="H179" s="13"/>
       <c r="I179" s="13"/>
       <c r="J179" s="33" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K179" s="18" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L179" s="19"/>
       <c r="M179" s="19" t="n">
@@ -9279,7 +9456,7 @@
       </c>
       <c r="N179" s="11"/>
       <c r="O179" s="12" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9287,13 +9464,13 @@
         <v>44</v>
       </c>
       <c r="B180" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C180" s="21" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D180" s="22" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E180" s="27" t="s">
         <v>30</v>
@@ -9303,7 +9480,7 @@
       <c r="H180" s="27"/>
       <c r="I180" s="27"/>
       <c r="J180" s="38" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K180" s="24" t="s">
         <v>53</v>
@@ -9312,7 +9489,7 @@
       <c r="M180" s="25"/>
       <c r="N180" s="21"/>
       <c r="O180" s="22" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9320,13 +9497,13 @@
         <v>45</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D181" s="12" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E181" s="29" t="s">
         <v>126</v>
@@ -9349,13 +9526,13 @@
         <v>46</v>
       </c>
       <c r="B182" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C182" s="21" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D182" s="22" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E182" s="50" t="s">
         <v>126</v>
@@ -9372,7 +9549,7 @@
       <c r="M182" s="25"/>
       <c r="N182" s="21"/>
       <c r="O182" s="22" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9380,13 +9557,13 @@
         <v>47</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D183" s="12" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E183" s="20" t="s">
         <v>39</v>
@@ -9409,13 +9586,13 @@
         <v>48</v>
       </c>
       <c r="B184" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C184" s="21" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D184" s="22" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E184" s="27" t="s">
         <v>30</v>
@@ -9425,14 +9602,14 @@
       <c r="H184" s="27"/>
       <c r="I184" s="27"/>
       <c r="J184" s="54" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K184" s="24"/>
       <c r="L184" s="25"/>
       <c r="M184" s="25"/>
       <c r="N184" s="21"/>
       <c r="O184" s="22" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9440,13 +9617,13 @@
         <v>49</v>
       </c>
       <c r="B185" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D185" s="12" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E185" s="13" t="s">
         <v>30</v>
@@ -9463,7 +9640,7 @@
       <c r="M185" s="19"/>
       <c r="N185" s="11"/>
       <c r="O185" s="12" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9471,13 +9648,13 @@
         <v>50</v>
       </c>
       <c r="B186" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D186" s="22" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E186" s="27" t="s">
         <v>30</v>
@@ -9487,14 +9664,14 @@
       <c r="H186" s="27"/>
       <c r="I186" s="27"/>
       <c r="J186" s="54" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K186" s="24"/>
       <c r="L186" s="25"/>
       <c r="M186" s="25"/>
       <c r="N186" s="21"/>
       <c r="O186" s="22" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9502,13 +9679,13 @@
         <v>51</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D187" s="12" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E187" s="20" t="s">
         <v>39</v>
@@ -9525,16 +9702,15 @@
       <c r="M187" s="19"/>
       <c r="N187" s="11"/>
       <c r="O187" s="12" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A6:O6"/>
     <mergeCell ref="A32:O32"/>
     <mergeCell ref="A46:O46"/>
     <mergeCell ref="A58:O58"/>
-    <mergeCell ref="A74:O74"/>
     <mergeCell ref="A83:O83"/>
     <mergeCell ref="A102:O102"/>
     <mergeCell ref="A119:O119"/>
@@ -9542,7 +9718,7 @@
     <mergeCell ref="A150:O150"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E6:I6 E7:E65 E66:I148 E150:I187" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E6:I6 E7:E74 E75:I148 E150:I187" type="list">
       <formula1>"Pending,In Progress,Complete,Not Needed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9577,7 +9753,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -9597,28 +9773,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="61" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="62" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C3" s="63" t="n">
         <v>46300</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="64" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B5" s="64" t="s">
         <v>11</v>
@@ -9627,31 +9803,31 @@
         <v>14</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E5" s="64" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="G5" s="64" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="H5" s="64" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I5" s="64" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="J5" s="64" t="s">
         <v>21</v>
       </c>
       <c r="K5" s="64" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M5" s="65" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9672,7 +9848,7 @@
         <v>46337</v>
       </c>
       <c r="N6" s="68" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9688,7 +9864,7 @@
         <v>Determine specification sheets (Render)</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E7" s="72" t="n">
         <v>0</v>
@@ -9711,13 +9887,13 @@
         <v>53</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="M7" s="67" t="n">
         <v>46352</v>
       </c>
       <c r="N7" s="68" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9733,7 +9909,7 @@
         <v>Obtain access to Online Portal</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E8" s="72" t="n">
         <v>0</v>
@@ -9756,13 +9932,13 @@
         <v>53</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="M8" s="67" t="n">
         <v>46353</v>
       </c>
       <c r="N8" s="68" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9778,7 +9954,7 @@
         <v>Architecture &amp; Engineering design and proposal</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E9" s="72" t="n">
         <v>5</v>
@@ -9801,13 +9977,13 @@
         <v>99</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="M9" s="67" t="n">
         <v>46380</v>
       </c>
       <c r="N9" s="68" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9823,7 +9999,7 @@
         <v>Architecture &amp; Engineering Approval</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E10" s="72" t="n">
         <v>0</v>
@@ -9846,13 +10022,13 @@
         <v>53</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M10" s="67" t="n">
         <v>46381</v>
       </c>
       <c r="N10" s="68" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9868,7 +10044,7 @@
         <v>Select provides and assign budget</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E11" s="72" t="n">
         <v>0</v>
@@ -9891,13 +10067,13 @@
         <v>53</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="M11" s="67" t="n">
         <v>46388</v>
       </c>
       <c r="N11" s="68" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9913,7 +10089,7 @@
         <v>HOA / ARB approval - Garage Door</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E12" s="72" t="n">
         <v>0</v>
@@ -9936,7 +10112,7 @@
         <v>53</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9952,7 +10128,7 @@
         <v>HOA / ARB approval - exterior paint</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E13" s="72" t="n">
         <v>0</v>
@@ -9975,7 +10151,7 @@
         <v>53</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9991,7 +10167,7 @@
         <v>HOA / ARB approval - driveway</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E14" s="72" t="n">
         <v>0</v>
@@ -10014,7 +10190,7 @@
         <v>53</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10030,7 +10206,7 @@
         <v>HOA / ARB approval - Landscaping</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E15" s="72" t="n">
         <v>0</v>
@@ -10053,7 +10229,7 @@
         <v>53</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10069,7 +10245,7 @@
         <v>Certificate of insurance per trade per jurisdiction</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E16" s="72" t="n">
         <v>5</v>
@@ -10092,7 +10268,7 @@
         <v>53</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10108,7 +10284,7 @@
         <v>Workers compensation per trade</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E17" s="72" t="n">
         <v>5</v>
@@ -10131,7 +10307,7 @@
         <v>53</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10147,7 +10323,7 @@
         <v>DBPR license per trade</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E18" s="72" t="n">
         <v>5</v>
@@ -10170,7 +10346,7 @@
         <v>53</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10186,7 +10362,7 @@
         <v>Permits package submittal</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E19" s="72" t="n">
         <v>0</v>
@@ -10209,7 +10385,7 @@
         <v>53</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10225,7 +10401,7 @@
         <v>Notice of Commencement (NOC)</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E20" s="72" t="n">
         <v>0</v>
@@ -10248,7 +10424,7 @@
         <v>53</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10264,7 +10440,7 @@
         <v>GC master permit - Residential alterations and additions</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E21" s="72" t="n">
         <v>0</v>
@@ -10287,7 +10463,7 @@
         <v>53</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10303,7 +10479,7 @@
         <v>Mechanical permit</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E22" s="72" t="n">
         <v>5</v>
@@ -10326,7 +10502,7 @@
         <v>53</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10342,7 +10518,7 @@
         <v>Electrical permit</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E23" s="72" t="n">
         <v>5</v>
@@ -10365,7 +10541,7 @@
         <v>53</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10381,7 +10557,7 @@
         <v>Plumbing permit</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E24" s="72" t="n">
         <v>5</v>
@@ -10404,7 +10580,7 @@
         <v>53</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10420,7 +10596,7 @@
         <v>Fence permit</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E25" s="72" t="n">
         <v>0</v>
@@ -10443,7 +10619,7 @@
         <v>71</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10459,7 +10635,7 @@
         <v>Driveway permit</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E26" s="72" t="n">
         <v>0</v>
@@ -10482,7 +10658,7 @@
         <v>71</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10498,7 +10674,7 @@
         <v>Gazebo permit</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E27" s="72" t="n">
         <v>0</v>
@@ -10521,7 +10697,7 @@
         <v>53</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10537,7 +10713,7 @@
         <v>Garage-door permit</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E28" s="72" t="n">
         <v>0</v>
@@ -10560,7 +10736,7 @@
         <v>53</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10576,7 +10752,7 @@
         <v>Demolition &amp; Waste Management</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E29" s="72" t="n">
         <v>0</v>
@@ -10600,7 +10776,7 @@
         <v>53</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10616,7 +10792,7 @@
         <v>Utilities</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E30" s="72" t="n">
         <v>0</v>
@@ -10638,7 +10814,7 @@
         <v>53</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10669,7 +10845,7 @@
         <v>Site protection + inventory (windows, railings, outlets, switches, smoke detectors)</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E32" s="72" t="n">
         <v>0</v>
@@ -10692,7 +10868,7 @@
         <v>71</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10708,7 +10884,7 @@
         <v>Structural engineering review - removed interior walls / truss bearing</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E33" s="72" t="n">
         <v>0</v>
@@ -10731,7 +10907,7 @@
         <v>99</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10747,7 +10923,7 @@
         <v>Popcorn ceiling removal - flat finish &amp; skin coat</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E34" s="72" t="n">
         <v>0</v>
@@ -10770,7 +10946,7 @@
         <v>102</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10786,7 +10962,7 @@
         <v>Framing repairs / new partitions</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="E35" s="72" t="n">
         <v>0</v>
@@ -10809,7 +10985,7 @@
         <v>92</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10825,7 +11001,7 @@
         <v>Slab trench patch after underground plumbing (baths/kitchen) + slab inspection</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E36" s="72" t="n">
         <v>0</v>
@@ -10848,7 +11024,7 @@
         <v>92</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10864,7 +11040,7 @@
         <v>Concrete slab repair + tile infill under AC unit</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E37" s="72" t="n">
         <v>0</v>
@@ -10884,10 +11060,10 @@
         <v>12</v>
       </c>
       <c r="J37" s="69" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10903,7 +11079,7 @@
         <v>Framing + MEP rough-in inspections (pre-cover milestone)</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E38" s="72" t="n">
         <v>0</v>
@@ -10912,7 +11088,7 @@
         <v>5</v>
       </c>
       <c r="G38" s="14" t="n">
-        <f aca="false">WORKDAY(MAX(H35,H36,H37,H46,H47,H58),1+E38,$M$6:$M$11)</f>
+        <f aca="false">WORKDAY(MAX(H35,H36,H37,H46,H47,H58,H63),1+E38,$M$6:$M$11)</f>
         <v>46387</v>
       </c>
       <c r="H38" s="14" t="n">
@@ -10926,7 +11102,7 @@
         <v>53</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10942,7 +11118,7 @@
         <v>Drywall repair / install &amp; finish. 2nd phase </v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="E39" s="72" t="n">
         <v>0</v>
@@ -10965,7 +11141,7 @@
         <v>92</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10981,7 +11157,7 @@
         <v>Drywall repair / install &amp; finish. Final phase </v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E40" s="72" t="n">
         <v>0</v>
@@ -11004,7 +11180,7 @@
         <v>92</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11020,7 +11196,7 @@
         <v>Surface prep - primer on walls + ceilings</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E41" s="72" t="n">
         <v>0</v>
@@ -11043,12 +11219,12 @@
         <v>123</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B42" s="66"/>
       <c r="C42" s="66"/>
@@ -11069,10 +11245,10 @@
         <v>31</v>
       </c>
       <c r="C43" s="75" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D43" s="76" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E43" s="77" t="n">
         <v>20</v>
@@ -11095,7 +11271,7 @@
         <v>53</v>
       </c>
       <c r="K43" s="76" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11126,7 +11302,7 @@
         <v>Make-safe exposed wiring from demolition (cap, label, temp lighting)</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E45" s="72" t="n">
         <v>0</v>
@@ -11149,7 +11325,7 @@
         <v>102</v>
       </c>
       <c r="K45" s="12" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11165,7 +11341,7 @@
         <v>Electrical panel change out</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E46" s="72" t="n">
         <v>0</v>
@@ -11188,7 +11364,7 @@
         <v>71</v>
       </c>
       <c r="K46" s="12" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11204,7 +11380,7 @@
         <v>Electrical rough-in - relocated boxes, new kitchen/bath circuits</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="E47" s="72" t="n">
         <v>0</v>
@@ -11227,7 +11403,7 @@
         <v>102</v>
       </c>
       <c r="K47" s="12" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11243,7 +11419,7 @@
         <v>Outlets, switches, GFCI/AFCI</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E48" s="72" t="n">
         <v>0</v>
@@ -11266,7 +11442,7 @@
         <v>102</v>
       </c>
       <c r="K48" s="12" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11282,7 +11458,7 @@
         <v>Recessed lighting (LED)</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E49" s="72" t="n">
         <v>0</v>
@@ -11305,7 +11481,7 @@
         <v>102</v>
       </c>
       <c r="K49" s="12" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11321,7 +11497,7 @@
         <v>Ceiling fans</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="E50" s="72" t="n">
         <v>1</v>
@@ -11344,7 +11520,7 @@
         <v>102</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11360,7 +11536,7 @@
         <v>Dining fixture (kitchen chandelier)</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E51" s="72" t="n">
         <v>2</v>
@@ -11383,7 +11559,7 @@
         <v>102</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11399,7 +11575,7 @@
         <v>LED mirrors - install</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E52" s="72" t="n">
         <v>0</v>
@@ -11422,7 +11598,7 @@
         <v>92</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11438,7 +11614,7 @@
         <v>Smoke / CO detectors - replace all</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E53" s="72" t="n">
         <v>0</v>
@@ -11461,7 +11637,7 @@
         <v>158</v>
       </c>
       <c r="K53" s="12" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11477,7 +11653,7 @@
         <v>Doorbell / smart doorbell</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E54" s="72" t="n">
         <v>0</v>
@@ -11500,7 +11676,7 @@
         <v>102</v>
       </c>
       <c r="K54" s="12" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11516,7 +11692,7 @@
         <v>Electrical contract - overall</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E55" s="72" t="n">
         <v>0</v>
@@ -11540,7 +11716,7 @@
         <v>102</v>
       </c>
       <c r="K55" s="12" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11571,7 +11747,7 @@
         <v>Underground DWV rough-in (baths/kitchen) incl. P-traps + underground inspection PASS</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E57" s="72" t="n">
         <v>0</v>
@@ -11594,7 +11770,7 @@
         <v>92</v>
       </c>
       <c r="K57" s="12" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11610,7 +11786,7 @@
         <v>Water supply rough-in / top-out (shower valves, toilets, kitchen, fridge line) + pressure test</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E58" s="72" t="n">
         <v>0</v>
@@ -11633,7 +11809,7 @@
         <v>92</v>
       </c>
       <c r="K58" s="12" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11649,7 +11825,7 @@
         <v>Plumbing inventory check - supply lines, drainage, P-traps</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E59" s="72" t="n">
         <v>0</v>
@@ -11672,7 +11848,7 @@
         <v>92</v>
       </c>
       <c r="K59" s="12" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11688,7 +11864,7 @@
         <v>Final plumbing completion labor</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E60" s="72" t="n">
         <v>0</v>
@@ -11711,7 +11887,7 @@
         <v>92</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11727,7 +11903,7 @@
         <v>Angle stops and supply lines throughout</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E61" s="72" t="n">
         <v>0</v>
@@ -11750,111 +11926,418 @@
         <v>92</v>
       </c>
       <c r="K61" s="12" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="4" t="s">
-        <v>542</v>
+        <v>533</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B62" s="66"/>
+      <c r="C62" s="66"/>
+      <c r="D62" s="66"/>
+      <c r="E62" s="66"/>
+      <c r="F62" s="66"/>
+      <c r="G62" s="66"/>
+      <c r="H62" s="66"/>
+      <c r="I62" s="66"/>
+      <c r="J62" s="66"/>
+      <c r="K62" s="66"/>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="69" t="n">
+        <v>69</v>
+      </c>
+      <c r="B63" s="70" t="str">
+        <f aca="false">IF('Scope Checklist'!A69="","-",'Scope Checklist'!A69)</f>
+        <v>N10</v>
+      </c>
+      <c r="C63" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D69</f>
+        <v>Duct modifications - removed partitions, kitchen hood + bath exhaust ducting</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="E63" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" s="14" t="n">
+        <f aca="false">WORKDAY(MAX(H22,H35),1+E63,$M$6:$M$11)</f>
+        <v>46378</v>
+      </c>
+      <c r="H63" s="14" t="n">
+        <f aca="false">WORKDAY(G63,F63-1,$M$6:$M$11)</f>
+        <v>46384</v>
+      </c>
+      <c r="I63" s="72" t="n">
+        <v>24</v>
+      </c>
+      <c r="J63" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="K63" s="12" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="80" t="s">
-        <v>543</v>
-      </c>
-      <c r="H64" s="81" t="n">
+      <c r="A64" s="69" t="n">
+        <v>70</v>
+      </c>
+      <c r="B64" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A70="","-",'Scope Checklist'!A70)</f>
+        <v>77</v>
+      </c>
+      <c r="C64" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D70</f>
+        <v>Ductwork inspection / repair / clean</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="E64" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="14" t="n">
+        <f aca="false">WORKDAY(H41,1+E64,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="H64" s="14" t="n">
+        <f aca="false">WORKDAY(G64,F64-1,$M$6:$M$11)</f>
+        <v>46415</v>
+      </c>
+      <c r="I64" s="72" t="n">
+        <v>16</v>
+      </c>
+      <c r="J64" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="K64" s="12" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="69" t="n">
+        <v>71</v>
+      </c>
+      <c r="B65" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A71="","-",'Scope Checklist'!A71)</f>
+        <v>75</v>
+      </c>
+      <c r="C65" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D71</f>
+        <v>HVAC coil cleaning</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="E65" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="14" t="n">
+        <f aca="false">WORKDAY(H41,1+E65,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="H65" s="14" t="n">
+        <f aca="false">WORKDAY(G65,F65-1,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="I65" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="K65" s="12" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="69" t="n">
+        <v>72</v>
+      </c>
+      <c r="B66" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A72="","-",'Scope Checklist'!A72)</f>
+        <v>76</v>
+      </c>
+      <c r="C66" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D72</f>
+        <v>HVAC coolant refill service</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="E66" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="14" t="n">
+        <f aca="false">WORKDAY(G65,E66,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="H66" s="14" t="n">
+        <f aca="false">WORKDAY(G66,F66-1,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="I66" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="K66" s="12" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="69" t="n">
+        <v>73</v>
+      </c>
+      <c r="B67" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A73="","-",'Scope Checklist'!A73)</f>
+        <v>78</v>
+      </c>
+      <c r="C67" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D73</f>
+        <v>AC diffusers</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="E67" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="14" t="n">
+        <f aca="false">WORKDAY(H43,1+E67,$M$6:$M$11)</f>
+        <v>46443</v>
+      </c>
+      <c r="H67" s="14" t="n">
+        <f aca="false">WORKDAY(G67,F67-1,$M$6:$M$11)</f>
+        <v>46443</v>
+      </c>
+      <c r="I67" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J67" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="K67" s="12" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="69" t="n">
+        <v>74</v>
+      </c>
+      <c r="B68" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A74="","-",'Scope Checklist'!A74)</f>
+        <v>79</v>
+      </c>
+      <c r="C68" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D74</f>
+        <v>Thermostat</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="E68" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="14" t="n">
+        <f aca="false">WORKDAY(H43,1+E68,$M$6:$M$11)</f>
+        <v>46443</v>
+      </c>
+      <c r="H68" s="14" t="n">
+        <f aca="false">WORKDAY(G68,F68-1,$M$6:$M$11)</f>
+        <v>46443</v>
+      </c>
+      <c r="I68" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K68" s="12" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A68="","-",'Scope Checklist'!A68)</f>
+        <v>74</v>
+      </c>
+      <c r="C69" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D68</f>
+        <v>HVAC maintenance + concrete slab repair</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="E69" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="69" t="n">
+        <f aca="false">NETWORKDAYS(G69,H69,$M$6:$M$11)</f>
+        <v>30</v>
+      </c>
+      <c r="G69" s="14" t="n">
+        <f aca="false">G37</f>
+        <v>46371</v>
+      </c>
+      <c r="H69" s="14" t="n">
+        <f aca="false">MAX(H37,H63,H64,H65,H66)</f>
+        <v>46415</v>
+      </c>
+      <c r="I69" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="J69" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="K69" s="12" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C71" s="4" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C72" s="80" t="s">
+        <v>557</v>
+      </c>
+      <c r="H72" s="81" t="n">
         <f aca="false">MAX(H21,H22,H23,H24)</f>
         <v>46370</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="80" t="s">
-        <v>544</v>
-      </c>
-      <c r="H65" s="81" t="n">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C73" s="80" t="s">
+        <v>558</v>
+      </c>
+      <c r="H73" s="81" t="n">
         <f aca="false">H38</f>
         <v>46394</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C66" s="80" t="s">
-        <v>545</v>
-      </c>
-      <c r="H66" s="81" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C74" s="80" t="s">
+        <v>559</v>
+      </c>
+      <c r="H74" s="81" t="n">
         <f aca="false">H41</f>
         <v>46413</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C67" s="80" t="s">
-        <v>546</v>
-      </c>
-      <c r="H67" s="81" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C75" s="80" t="s">
+        <v>560</v>
+      </c>
+      <c r="H75" s="81" t="n">
         <f aca="false">H57</f>
         <v>46374</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C68" s="80" t="s">
-        <v>547</v>
-      </c>
-      <c r="H68" s="81" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C76" s="80" t="s">
+        <v>561</v>
+      </c>
+      <c r="H76" s="81" t="n">
         <f aca="false">H43</f>
         <v>46442</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C69" s="80" t="s">
-        <v>548</v>
-      </c>
-      <c r="H69" s="81" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C77" s="80" t="s">
+        <v>562</v>
+      </c>
+      <c r="H77" s="81" t="n">
         <f aca="false">H55</f>
         <v>46448</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C70" s="80" t="s">
-        <v>549</v>
-      </c>
-      <c r="H70" s="81" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C78" s="80" t="s">
+        <v>563</v>
+      </c>
+      <c r="H78" s="81" t="n">
         <f aca="false">MAX(H60,H61)</f>
         <v>46447</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C71" s="80" t="s">
-        <v>550</v>
-      </c>
-      <c r="I71" s="82" t="n">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C79" s="80" t="s">
+        <v>564</v>
+      </c>
+      <c r="H79" s="81" t="n">
+        <f aca="false">MAX(H67,H68)</f>
+        <v>46443</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C80" s="80" t="s">
+        <v>565</v>
+      </c>
+      <c r="I80" s="82" t="n">
         <f aca="false">SUM(I7:I30)</f>
         <v>217</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C72" s="80" t="s">
-        <v>551</v>
-      </c>
-      <c r="I72" s="82" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C81" s="80" t="s">
+        <v>566</v>
+      </c>
+      <c r="I81" s="82" t="n">
         <f aca="false">SUM(I32:I41)</f>
         <v>360</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C73" s="80" t="s">
-        <v>552</v>
-      </c>
-      <c r="I73" s="82" t="n">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C82" s="80" t="s">
+        <v>567</v>
+      </c>
+      <c r="I82" s="82" t="n">
         <f aca="false">SUM(I45:I55)</f>
         <v>139</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C74" s="80" t="s">
-        <v>553</v>
-      </c>
-      <c r="I74" s="82" t="n">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C83" s="80" t="s">
+        <v>568</v>
+      </c>
+      <c r="I83" s="82" t="n">
         <f aca="false">SUM(I57:I61)</f>
         <v>94</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C84" s="80" t="s">
+        <v>569</v>
+      </c>
+      <c r="I84" s="82" t="n">
+        <f aca="false">SUM(I63:I69)</f>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -11883,30 +12366,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="83" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="84" t="s">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="B4" s="84"/>
       <c r="C4" s="84"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="85" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="B5" s="85" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="85" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11917,7 +12400,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>559</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11928,7 +12411,7 @@
         <v>53</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11939,7 +12422,7 @@
         <v>53</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11950,7 +12433,7 @@
         <v>53</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11961,7 +12444,7 @@
         <v>71</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>563</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11972,18 +12455,18 @@
         <v>71</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="86" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11994,7 +12477,7 @@
         <v>92</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12002,10 +12485,10 @@
         <v>110</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12016,40 +12499,40 @@
         <v>71</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>570</v>
+        <v>586</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="86" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="86" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="86" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>574</v>
+        <v>590</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12057,116 +12540,116 @@
         <v>157</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="86" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>576</v>
+        <v>592</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="86" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="86" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="86" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>579</v>
+        <v>595</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="86" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="86" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="86" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>102</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="87" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="B28" s="87"/>
       <c r="C28" s="87"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="85" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="B29" s="85" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="85" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="86" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12174,10 +12657,10 @@
         <v>131</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12188,172 +12671,172 @@
         <v>92</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="86" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="86" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="86" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="86" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="86" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="86" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="86" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="86" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="86" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="86" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B42" s="18" t="s">
         <v>123</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="86" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B43" s="18" t="s">
         <v>123</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="86" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="86" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="86" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B46" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="86" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B47" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12364,80 +12847,80 @@
         <v>92</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="86" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="86" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="88" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="B52" s="88"/>
       <c r="C52" s="88"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="85" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="B53" s="85" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="85" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="86" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="86" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B55" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12448,144 +12931,144 @@
         <v>92</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="86" t="s">
-        <v>618</v>
+        <v>634</v>
       </c>
       <c r="B58" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="86" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B59" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="86" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="86" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="86" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="86" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B63" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>624</v>
+        <v>640</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="86" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>625</v>
+        <v>641</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="86" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="86" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B66" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="86" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="86" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="86" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
       <c r="B69" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="89" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="B71" s="89"/>
       <c r="C71" s="89"/>
@@ -12626,12 +13109,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="90" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12639,30 +13122,30 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>636</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>637</v>
+        <v>653</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="C5" s="19" t="n">
         <v>30297</v>
@@ -12672,18 +13155,18 @@
         <v>0</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>19825.36</v>
@@ -12695,18 +13178,18 @@
         <v>0</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="C7" s="19" t="n">
         <v>14000</v>
@@ -12718,10 +13201,10 @@
         <v>7000</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12729,7 +13212,7 @@
         <v>68</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="25" t="n">
@@ -12739,18 +13222,18 @@
         <v>1500</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19" t="n">
@@ -12760,18 +13243,18 @@
         <v>3500</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>3000</v>
@@ -12783,18 +13266,18 @@
         <v>3000</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>656</v>
+        <v>672</v>
       </c>
       <c r="C11" s="19" t="n">
         <v>21750</v>
@@ -12806,18 +13289,18 @@
         <v>4875</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
       <c r="C12" s="25" t="n">
         <v>5925</v>
@@ -12829,18 +13312,18 @@
         <v>4500</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="C13" s="19" t="n">
         <v>9100</v>
@@ -12852,18 +13335,18 @@
         <v>9100</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="25" t="n">
@@ -12873,18 +13356,18 @@
         <v>500</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19" t="n">
@@ -12894,18 +13377,18 @@
         <v>2500</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25" t="n">
@@ -12913,18 +13396,18 @@
       </c>
       <c r="E16" s="25"/>
       <c r="F16" s="22" t="s">
-        <v>668</v>
+        <v>684</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="C17" s="19"/>
       <c r="D17" s="19" t="n">
@@ -12932,18 +13415,18 @@
       </c>
       <c r="E17" s="19"/>
       <c r="F17" s="12" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>671</v>
+        <v>687</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25" t="n">
@@ -12951,18 +13434,18 @@
       </c>
       <c r="E18" s="25"/>
       <c r="F18" s="22" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
       <c r="C19" s="19" t="n">
         <v>10000</v>
@@ -12974,18 +13457,18 @@
         <v>10000</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="C20" s="25" t="n">
         <v>3000</v>
@@ -12997,18 +13480,18 @@
         <v>3000</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="C21" s="19" t="n">
         <v>2000</v>
@@ -13020,18 +13503,18 @@
         <v>1500</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25" t="n">
@@ -13039,18 +13522,18 @@
       </c>
       <c r="E22" s="25"/>
       <c r="F22" s="22" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="C23" s="19" t="n">
         <v>2100</v>
@@ -13062,18 +13545,18 @@
         <v>2000</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>687</v>
+        <v>703</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>688</v>
+        <v>704</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>689</v>
+        <v>705</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="C24" s="25" t="n">
         <v>7500</v>
@@ -13085,16 +13568,16 @@
         <v>4500</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="58"/>
       <c r="B25" s="59" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
       <c r="C25" s="58"/>
       <c r="D25" s="58"/>
@@ -13107,29 +13590,29 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>693</v>
+        <v>709</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="92" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="93"/>
       <c r="B29" s="93" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="C29" s="93" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="D29" s="93" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="B30" s="94" t="n">
         <v>107414.33</v>
@@ -13144,7 +13627,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>699</v>
+        <v>715</v>
       </c>
       <c r="B31" s="94" t="n">
         <v>22180.93</v>
@@ -13159,7 +13642,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="B32" s="96" t="n">
         <f aca="false">SUM(B30:B31)</f>
@@ -13176,7 +13659,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>701</v>
+        <v>717</v>
       </c>
       <c r="D33" s="97" t="n">
         <f aca="false">D32</f>
@@ -13213,12 +13696,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="90" t="s">
-        <v>702</v>
+        <v>718</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>703</v>
+        <v>719</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13226,7 +13709,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="98" t="s">
-        <v>704</v>
+        <v>720</v>
       </c>
       <c r="C4" s="98" t="s">
         <v>30</v>
@@ -13282,7 +13765,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$148,A6)</f>
@@ -13418,11 +13901,11 @@
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$148,A10)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">COUNTIFS('Scope Checklist'!$B$6:$B$148,A10,'Scope Checklist'!$E$6:$E$148,"Pending")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">COUNTIFS('Scope Checklist'!$B$6:$B$148,A10,'Scope Checklist'!$E$6:$E$148,"In Progress")</f>
@@ -13447,7 +13930,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B11" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$148,A11)</f>
@@ -13480,7 +13963,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B12" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$148,A12)</f>
@@ -13513,7 +13996,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$148,A13)</f>
@@ -13546,7 +14029,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$148,A14)</f>
@@ -13579,7 +14062,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B15" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$148,A15)</f>
@@ -13612,15 +14095,15 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="B16" s="86" t="n">
         <f aca="false">SUM(B5:B15)</f>
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C16" s="86" t="n">
         <f aca="false">SUM(C5:C15)</f>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D16" s="86" t="n">
         <f aca="false">SUM(D5:D15)</f>

--- a/Property_Scope_Plan_Jupiter_v2.xlsx
+++ b/Property_Scope_Plan_Jupiter_v2.xlsx
@@ -185,12 +185,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="O95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Status/notes look carried over from the previous property template; the 21-Sep session reports Jupiter fully stripped with no MEP work done - verify status, cost and balance.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O101" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Status/notes look carried over from the previous property template; the 21-Sep session reports Jupiter fully stripped with no MEP work done - verify status, cost and balance.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="806">
   <si>
     <t xml:space="preserve">COMPLETE RENOVATION - PENDING ITEMS + COST TRACKER</t>
   </si>
@@ -222,7 +246,7 @@
     <t xml:space="preserve">Updated: July 2, 2026 - costs per Project Status &amp; Cost Summary PDF</t>
   </si>
   <si>
-    <t xml:space="preserve">Schedule proposal Sep 24, 2026 (session 2026-ACTA-JUPITER-01): dates in F-H are driven by 'Schedule Logic'. N1-N12 = activities added from the 21-Sep session.</t>
+    <t xml:space="preserve">Schedule proposal Sep 24, 2026 (session 2026-ACTA-JUPITER-01): dates in F-H are driven by 'Schedule Logic'. N1-N13 = activities added from the 21-Sep session.</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -732,7 +756,7 @@
     <t xml:space="preserve">Victor</t>
   </si>
   <si>
-    <t xml:space="preserve">~3 days labor at Victor's daily rate; final inspection pending; trim-out after cabinets, tops + tile (PROVISIONAL anchor in Schedule Logic)</t>
+    <t xml:space="preserve">~3 days labor at Victor's daily rate; final inspection pending; trim-out after cabinets, tops + tile (finish-trades milestone in Schedule Logic)</t>
   </si>
   <si>
     <t xml:space="preserve">Angle stops and supply lines throughout</t>
@@ -888,27 +912,144 @@
     <t xml:space="preserve">Bath - Master</t>
   </si>
   <si>
+    <t xml:space="preserve">Shower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shower drains - select + purchase (BOTH baths)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needed on hand before pan liner / tile sequence</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vanity</t>
   </si>
   <si>
+    <t xml:space="preserve">Sink selection - double sinks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A purchases sinks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shower prep - confirm metal frame distance + shower door frame support (BOTH baths)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W1-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-liner check; do labor if needed; supports glass door install later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tub install</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W2-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bathtub electrical connection in electrical contract; Bathtub electrical connection ASAP in W1 - ready for inspection; set tub in W2 after inspections pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pan liner install + inspection pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W1-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shower sequence step 2 (after step 1 framing); CANNOT start before permit issuance + plumbing/framing/slab inspections scheduled/passed. Pre-slope + liner flat (no folds) [53:16]; 24 h flood test with drain plugged - inspector checks for leaks [55:37]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durock + waterproofing install</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shower sequence steps 3-4: Durock, then waterproofing - after pan liner inspection passes. Board screws at code spacing to metal studs (inspected) [54:00]; seams cemented + anti-mold membrane (inspected) [54:20]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED niche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASAP - confirm inventory or place supply order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metal trim (edge profile) - verify availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V: confirm metal trim color + count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shower waterproofing inspection PASS - both baths (gate for tile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added from 21-Sep session [54:00]-[56:43]: cement board screw spacing, cemented seams and anti-mold membrane are each inspected; after the liner flood test [55:37]. Keep weep holes open [56:20]. Tile cannot start before PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bathroom tile installation - labor (BOTH baths)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W2-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete bathroom tile install, both bathrooms; ~10 days total; Starts ONLY after framing, Durock, waterproofing + passed inspections (W1-18 sequence). Decide in spec sheets: full-height wall tile vs wet zones only [23:27]; with inspections already passed the tiler does not wait ([35:22] $1,900 vs $2,700)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finishes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paint all walls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W2-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pocket door - verify function + paint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W2-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vanity cabinetry - confirm quality</t>
   </si>
   <si>
     <t xml:space="preserve">In cabinet contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Sink selection - double sinks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A purchases sinks</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vanity stone top - select (~11 sq ft)</t>
   </si>
   <si>
     <t xml:space="preserve">In stone contract line</t>
   </si>
   <si>
+    <t xml:space="preserve">Threshold + bench top</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W3-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinate stone with countertop selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass shower enclosure - MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W3-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$2,500-$3,000; fabrication ~4 days; install 1-2 days; measurements pending; Gino: quote + install MASTER</t>
+  </si>
+  <si>
     <t xml:space="preserve">Double faucets + double sinks - install</t>
   </si>
   <si>
@@ -930,165 +1071,63 @@
     <t xml:space="preserve">New toilet position (drain relocated); New flange if necessary; verify supply line + drainage positioning; One row per bathroom (master + secondary)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tub install</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W2-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bathtub electrical connection in electrical contract; Bathtub electrical connection ASAP in W1 - ready for inspection; set tub in W2 after inspections pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED niche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASAP - confirm inventory or place supply order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shower drains - select + purchase (BOTH baths)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needed on hand before pan liner / tile sequence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shower prep - confirm metal frame distance + shower door frame support (BOTH baths)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W1-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-liner check; do labor if needed; supports glass door install later</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durock + waterproofing install</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W1-18</t>
+    <t xml:space="preserve">Bath hardware (towel bars, TP holder, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A &gt; V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchase W1 (A - Amazon / online / retail); install W3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ventilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhaust fan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct install - coupling pending; fan install in electrical contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BATH - SECONDARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bath - Secondary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sink selection - single sink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shower sequence step 2 (after step 1 framing); CANNOT start before permit issuance + plumbing/framing/slab inspections scheduled/passed</t>
   </si>
   <si>
     <t xml:space="preserve">Shower sequence steps 3-4: Durock, then waterproofing - after pan liner inspection passes</t>
   </si>
   <si>
-    <t xml:space="preserve">Pan liner install + inspection pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shower sequence step 2 (after step 1 framing); CANNOT start before permit issuance + plumbing/framing/slab inspections scheduled/passed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bathroom tile installation - labor (BOTH baths)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete bathroom tile install, both bathrooms; ~10 days total; Starts ONLY after framing, Durock, waterproofing + passed inspections (W1-18 sequence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metal trim (edge profile) - verify availability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V: confirm metal trim color + count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold + bench top</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinate stone with countertop selection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glass shower enclosure - MASTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W3-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$2,500-$3,000; fabrication ~4 days; install 1-2 days; measurements pending; Gino: quote + install MASTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finishes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paint all walls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W2-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pocket door - verify function + paint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W2-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bath hardware (towel bars, TP holder, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A &gt; V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchase W1 (A - Amazon / online / retail); install W3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ventilation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exhaust fan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duct install - coupling pending; fan install in electrical contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BATH - SECONDARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bath - Secondary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sink selection - single sink</t>
+    <t xml:space="preserve">Shower tile install</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor in master line (both baths, $3,500); Sub - after W1-18 sequence + inspections pass</t>
   </si>
   <si>
     <t xml:space="preserve">Vanity stone top - select (~8 sq ft)</t>
   </si>
   <si>
+    <t xml:space="preserve">Glass shower enclosure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A / V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In master line (both baths); Use existing inventory glass with black hardware (A provides); V must confirm width</t>
+  </si>
+  <si>
     <t xml:space="preserve">Faucet + sink - install</t>
   </si>
   <si>
     <t xml:space="preserve">New flange if necessary; verify supply line + drainage positioning; One row per bathroom (master + secondary)</t>
   </si>
   <si>
-    <t xml:space="preserve">Shower tile install</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor in master line (both baths, $3,500); Sub - after W1-18 sequence + inspections pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glass shower enclosure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A / V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In master line (both baths); Use existing inventory glass with black hardware (A provides); V must confirm width</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verify power supply; fan install in electrical contract</t>
   </si>
   <si>
@@ -1539,7 +1578,7 @@
     <t xml:space="preserve">Repaired / replaced as needed</t>
   </si>
   <si>
-    <t xml:space="preserve">SCHEDULE LOGIC - PRE-CONSTRUCTION, DEMO/STRUCTURE, ELECTRICAL, PLUMBING, HVAC, KITCHEN (proposed baseline)</t>
+    <t xml:space="preserve">SCHEDULE LOGIC - PRE-CONSTRUCTION, DEMO/STRUCTURE, ELECTRICAL, PLUMBING, HVAC, KITCHEN, BATHS (proposed baseline)</t>
   </si>
   <si>
     <t xml:space="preserve">Working days Mon-Fri excluding holidays in column M. Edit only the yellow cells (baseline) and blue cells (lag, duration, effort); Start/End recalculate and feed Scope Checklist columns F-H.</t>
@@ -1764,16 +1803,16 @@
     <t xml:space="preserve">[18:17]-[19:44] primer coat on walls + ceilings before wet trades</t>
   </si>
   <si>
-    <t xml:space="preserve">LINK TO FINISH TRADES (PROVISIONAL)</t>
+    <t xml:space="preserve">FINISH TRADES READY FOR MEP TRIM</t>
   </si>
   <si>
     <t xml:space="preserve">Finish trades ready for MEP trim (milestone)</t>
   </si>
   <si>
-    <t xml:space="preserve">PROVISIONAL: primer end + 20 wd - re-link to Kitchen/Bath rows once scheduled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheet data: cabinets install 1-2 d, bath tile ~10 d, countertops field measure + 5-d fabrication + install = ~20 wd before MEP trim</t>
+    <t xml:space="preserve">After kitchen countertops, both vanity tops + bath paint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replaces the provisional primer + 20 wd placeholder; one electrician + plumber trim visit for the whole house</t>
   </si>
   <si>
     <t xml:space="preserve">Baseline start (safety, before trades return)</t>
@@ -1794,7 +1833,7 @@
     <t xml:space="preserve">[12:07]-[12:38] open kitchen, removed partitions; [33:16] electrical sub-permit</t>
   </si>
   <si>
-    <t xml:space="preserve">Trim window (PROVISIONAL anchor)</t>
+    <t xml:space="preserve">Trim window (finish trades ready)</t>
   </si>
   <si>
     <t xml:space="preserve">Existing scope: incl. dedicated fridge + oven outlets</t>
@@ -1938,6 +1977,153 @@
     <t xml:space="preserve">Existing scope: transformer + LED strip / puck lights</t>
   </si>
   <si>
+    <t xml:space="preserve">BATH - MASTER (shower sequence covers both baths)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After provider selection (needed before liner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing scope: clamping shower drains, both baths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With kitchen sink purchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must be on site for vanity-top template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After framing (checked in N4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[53:04]-[53:16] wood blocking to hold the liner + metal framing spacing are checked by inspectors; both baths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After rough-in inspections PASS (tub power in N7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing scope: set tub before wall tile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After drywall final (Victor free): pre-slope, liner, 24 h flood test + inspection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[53:16]-[53:38] liner flat, no folds; [55:37] flood test with drain plugged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After liner flood test PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[54:00]-[54:42] board screw spacing inspected; seams cemented; anti-mold membrane inspected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With cement board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing scope; power from N7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before tile starts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing scope: color + count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After both baths waterproofed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[54:20]-[54:53] each step is an inspection; [55:16] many milestones = one per inspection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After waterproofing inspection PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheet: ~10 days both baths; [35:22] tiler does not wait when inspections are passed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After tile + grout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With bath paint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After bath tile + paint (2nd cabinet-maker visit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanities are in the kitchen cabinet contract; kitchen is installed before the baths are tiled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After vanities set: template -&gt; ~5 d fabrication -&gt; install</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same slab as kitchen saves $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same stone template/fabrication/install trip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After threshold + bench: measure -&gt; ~4 d fabrication -&gt; 1-2 d install</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheet: Gino quote + install</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After vanity tops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify vanity height</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After floor tile + bath paint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New wax ring; flange if needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchase early, install at trim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With electrical trim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct coupling done in N10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same days as master liner (one flood-test inspection)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[55:37] flood test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same days as master cement board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[54:00]-[54:42]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second half of the 10-day tile block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor + hours carried in the master tile row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same cabinet-maker visit as master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same stone trip as master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After threshold set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing inventory glass with black hardware; V confirms width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After vanity top</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify power supply</t>
+  </si>
+  <si>
     <t xml:space="preserve">Milestones</t>
   </si>
   <si>
@@ -1953,7 +2139,7 @@
     <t xml:space="preserve">Underground plumbing inspection passed</t>
   </si>
   <si>
-    <t xml:space="preserve">Finish trades ready for MEP trim (PROVISIONAL)</t>
+    <t xml:space="preserve">Finish trades ready for MEP trim</t>
   </si>
   <si>
     <t xml:space="preserve">Electrical complete (trim)</t>
@@ -1971,6 +2157,15 @@
     <t xml:space="preserve">Kitchen complete (appliances installed)</t>
   </si>
   <si>
+    <t xml:space="preserve">Shower waterproofing inspections passed (both baths)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bath tile complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baths complete (glass + fixtures)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total effort - Pre-Construction (hrs)</t>
   </si>
   <si>
@@ -1987,6 +2182,12 @@
   </si>
   <si>
     <t xml:space="preserve">Total effort - Kitchen (hrs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total effort - Bath Master (hrs, incl. tile both baths)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total effort - Bath Secondary (hrs)</t>
   </si>
   <si>
     <t xml:space="preserve">3-WEEK EXECUTION PLAN - A = Andres | V = Victor | H = Hans | S = Sub | M = Martin (stone) | G = Gino (glass)</t>
@@ -5222,7 +5423,7 @@
       </c>
       <c r="G47" s="47" t="n">
         <f aca="false">'Schedule Logic'!H55</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="H47" s="48" t="str">
         <f aca="false">'Schedule Logic'!I55</f>
@@ -5394,11 +5595,11 @@
       </c>
       <c r="F51" s="35" t="n">
         <f aca="false">'Schedule Logic'!G48</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="G51" s="35" t="n">
         <f aca="false">'Schedule Logic'!H48</f>
-        <v>46447</v>
+        <v>46455</v>
       </c>
       <c r="H51" s="36" t="n">
         <f aca="false">'Schedule Logic'!I48</f>
@@ -5438,11 +5639,11 @@
       </c>
       <c r="F52" s="52" t="n">
         <f aca="false">'Schedule Logic'!G49</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="G52" s="52" t="n">
         <f aca="false">'Schedule Logic'!H49</f>
-        <v>46444</v>
+        <v>46454</v>
       </c>
       <c r="H52" s="53" t="n">
         <f aca="false">'Schedule Logic'!I49</f>
@@ -5480,11 +5681,11 @@
       </c>
       <c r="F53" s="35" t="n">
         <f aca="false">'Schedule Logic'!G50</f>
-        <v>46444</v>
+        <v>46454</v>
       </c>
       <c r="G53" s="35" t="n">
         <f aca="false">'Schedule Logic'!H50</f>
-        <v>46447</v>
+        <v>46455</v>
       </c>
       <c r="H53" s="36" t="n">
         <f aca="false">'Schedule Logic'!I50</f>
@@ -5524,11 +5725,11 @@
       </c>
       <c r="F54" s="39" t="n">
         <f aca="false">'Schedule Logic'!G51</f>
-        <v>46447</v>
+        <v>46455</v>
       </c>
       <c r="G54" s="39" t="n">
         <f aca="false">'Schedule Logic'!H51</f>
-        <v>46447</v>
+        <v>46455</v>
       </c>
       <c r="H54" s="40" t="n">
         <f aca="false">'Schedule Logic'!I51</f>
@@ -5568,11 +5769,11 @@
       </c>
       <c r="F55" s="35" t="n">
         <f aca="false">'Schedule Logic'!G52</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="G55" s="35" t="n">
         <f aca="false">'Schedule Logic'!H52</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="H55" s="36" t="n">
         <f aca="false">'Schedule Logic'!I52</f>
@@ -5612,11 +5813,11 @@
       </c>
       <c r="F56" s="39" t="n">
         <f aca="false">'Schedule Logic'!G53</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="G56" s="39" t="n">
         <f aca="false">'Schedule Logic'!H53</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="H56" s="40" t="n">
         <f aca="false">'Schedule Logic'!I53</f>
@@ -5656,11 +5857,11 @@
       </c>
       <c r="F57" s="35" t="n">
         <f aca="false">'Schedule Logic'!G54</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="G57" s="35" t="n">
         <f aca="false">'Schedule Logic'!H54</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="H57" s="36" t="n">
         <f aca="false">'Schedule Logic'!I54</f>
@@ -5882,11 +6083,11 @@
       </c>
       <c r="F63" s="35" t="n">
         <f aca="false">'Schedule Logic'!G60</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="G63" s="35" t="n">
         <f aca="false">'Schedule Logic'!H60</f>
-        <v>46447</v>
+        <v>46455</v>
       </c>
       <c r="H63" s="36" t="n">
         <f aca="false">'Schedule Logic'!I60</f>
@@ -5930,11 +6131,11 @@
       </c>
       <c r="F64" s="39" t="n">
         <f aca="false">'Schedule Logic'!G61</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="G64" s="39" t="n">
         <f aca="false">'Schedule Logic'!H61</f>
-        <v>46444</v>
+        <v>46454</v>
       </c>
       <c r="H64" s="40" t="n">
         <f aca="false">'Schedule Logic'!I61</f>
@@ -6277,11 +6478,11 @@
       </c>
       <c r="F73" s="35" t="n">
         <f aca="false">'Schedule Logic'!G67</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="G73" s="35" t="n">
         <f aca="false">'Schedule Logic'!H67</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="H73" s="36" t="n">
         <f aca="false">'Schedule Logic'!I67</f>
@@ -6321,11 +6522,11 @@
       </c>
       <c r="F74" s="39" t="n">
         <f aca="false">'Schedule Logic'!G68</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="G74" s="39" t="n">
         <f aca="false">'Schedule Logic'!H68</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="H74" s="40" t="n">
         <f aca="false">'Schedule Logic'!I68</f>
@@ -6660,11 +6861,11 @@
       </c>
       <c r="F82" s="35" t="n">
         <f aca="false">'Schedule Logic'!G77</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="G82" s="35" t="n">
         <f aca="false">'Schedule Logic'!H77</f>
-        <v>46449</v>
+        <v>46457</v>
       </c>
       <c r="H82" s="36" t="n">
         <f aca="false">'Schedule Logic'!I77</f>
@@ -6704,11 +6905,11 @@
       </c>
       <c r="F83" s="39" t="n">
         <f aca="false">'Schedule Logic'!G78</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="G83" s="39" t="n">
         <f aca="false">'Schedule Logic'!H78</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="H83" s="40" t="n">
         <f aca="false">'Schedule Logic'!I78</f>
@@ -6779,590 +6980,806 @@
       <c r="O85" s="56"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="10" t="n">
+      <c r="A86" s="30" t="n">
+        <v>94</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D86" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E86" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F86" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G80</f>
+        <v>46335</v>
+      </c>
+      <c r="G86" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H80</f>
+        <v>46342</v>
+      </c>
+      <c r="H86" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I80</f>
+        <v>3</v>
+      </c>
+      <c r="I86" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="K86" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="L86" s="25"/>
+      <c r="M86" s="25"/>
+      <c r="N86" s="21"/>
+      <c r="O86" s="22" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F87" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G81</f>
+        <v>46387</v>
+      </c>
+      <c r="G87" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H81</f>
+        <v>46394</v>
+      </c>
+      <c r="H87" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I81</f>
+        <v>2</v>
+      </c>
+      <c r="I87" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="K87" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="L87" s="19"/>
+      <c r="M87" s="19"/>
+      <c r="N87" s="11"/>
+      <c r="O87" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="30" t="n">
+        <v>95</v>
+      </c>
+      <c r="B88" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D88" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="E88" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F88" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G82</f>
+        <v>46378</v>
+      </c>
+      <c r="G88" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H82</f>
+        <v>46378</v>
+      </c>
+      <c r="H88" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I82</f>
+        <v>8</v>
+      </c>
+      <c r="I88" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="K88" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="L88" s="25"/>
+      <c r="M88" s="25"/>
+      <c r="N88" s="21"/>
+      <c r="O88" s="22" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F89" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G83</f>
+        <v>46395</v>
+      </c>
+      <c r="G89" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H83</f>
+        <v>46395</v>
+      </c>
+      <c r="H89" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I83</f>
+        <v>8</v>
+      </c>
+      <c r="I89" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="K89" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="L89" s="19"/>
+      <c r="M89" s="19"/>
+      <c r="N89" s="11"/>
+      <c r="O89" s="12" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="30" t="n">
+        <v>97</v>
+      </c>
+      <c r="B90" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D90" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="E90" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F90" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G84</f>
+        <v>46409</v>
+      </c>
+      <c r="G90" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H84</f>
+        <v>46413</v>
+      </c>
+      <c r="H90" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I84</f>
+        <v>16</v>
+      </c>
+      <c r="I90" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="K90" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="L90" s="25"/>
+      <c r="M90" s="25"/>
+      <c r="N90" s="21"/>
+      <c r="O90" s="22" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F91" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G85</f>
+        <v>46414</v>
+      </c>
+      <c r="G91" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H85</f>
+        <v>46419</v>
+      </c>
+      <c r="H91" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I85</f>
+        <v>24</v>
+      </c>
+      <c r="I91" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="K91" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="L91" s="19"/>
+      <c r="M91" s="19"/>
+      <c r="N91" s="11"/>
+      <c r="O91" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="30" t="n">
+        <v>93</v>
+      </c>
+      <c r="B92" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C92" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D92" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E92" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F92" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G86</f>
+        <v>46414</v>
+      </c>
+      <c r="G92" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H86</f>
+        <v>46414</v>
+      </c>
+      <c r="H92" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I86</f>
+        <v>3</v>
+      </c>
+      <c r="I92" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="K92" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="L92" s="25"/>
+      <c r="M92" s="25"/>
+      <c r="N92" s="21"/>
+      <c r="O92" s="22" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F93" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G87</f>
+        <v>46409</v>
+      </c>
+      <c r="G93" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H87</f>
+        <v>46409</v>
+      </c>
+      <c r="H93" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I87</f>
+        <v>2</v>
+      </c>
+      <c r="I93" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="K93" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="L93" s="19"/>
+      <c r="M93" s="19"/>
+      <c r="N93" s="11"/>
+      <c r="O93" s="12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C94" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D94" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="E94" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F94" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G88</f>
+        <v>46420</v>
+      </c>
+      <c r="G94" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H88</f>
+        <v>46420</v>
+      </c>
+      <c r="H94" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I88</f>
+        <v>4</v>
+      </c>
+      <c r="I94" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="K94" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="L94" s="25"/>
+      <c r="M94" s="25"/>
+      <c r="N94" s="21"/>
+      <c r="O94" s="22" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F95" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G89</f>
+        <v>46421</v>
+      </c>
+      <c r="G95" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H89</f>
+        <v>46434</v>
+      </c>
+      <c r="H95" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I89</f>
+        <v>80</v>
+      </c>
+      <c r="I95" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="K95" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="L95" s="19"/>
+      <c r="M95" s="19" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N95" s="11"/>
+      <c r="O95" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="30" t="n">
+        <v>102</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="D96" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="E96" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F96" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G90</f>
+        <v>46435</v>
+      </c>
+      <c r="G96" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H90</f>
+        <v>46436</v>
+      </c>
+      <c r="H96" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I90</f>
+        <v>12</v>
+      </c>
+      <c r="I96" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="K96" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="L96" s="25"/>
+      <c r="M96" s="25"/>
+      <c r="N96" s="21"/>
+      <c r="O96" s="22"/>
+    </row>
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F97" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G91</f>
+        <v>46435</v>
+      </c>
+      <c r="G97" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H91</f>
+        <v>46435</v>
+      </c>
+      <c r="H97" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I91</f>
+        <v>3</v>
+      </c>
+      <c r="I97" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="K97" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="L97" s="19"/>
+      <c r="M97" s="19"/>
+      <c r="N97" s="11"/>
+      <c r="O97" s="12"/>
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="30" t="n">
         <v>87</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B98" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C98" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="D98" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="E98" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F98" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G92</f>
+        <v>46437</v>
+      </c>
+      <c r="G98" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H92</f>
+        <v>46437</v>
+      </c>
+      <c r="H98" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I92</f>
+        <v>4</v>
+      </c>
+      <c r="I98" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="K98" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="L98" s="25"/>
+      <c r="M98" s="25"/>
+      <c r="N98" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="O98" s="22" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F99" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G93</f>
+        <v>46440</v>
+      </c>
+      <c r="G99" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H93</f>
+        <v>46449</v>
+      </c>
+      <c r="H99" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I93</f>
+        <v>6</v>
+      </c>
+      <c r="I99" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="K99" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="L99" s="19"/>
+      <c r="M99" s="19"/>
+      <c r="N99" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="O99" s="12" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="B100" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C100" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="D86" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="E86" s="13" t="s">
+      <c r="D100" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="E100" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
-      <c r="J86" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="K86" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="L86" s="19"/>
-      <c r="M86" s="19"/>
-      <c r="N86" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="O86" s="12" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="30" t="n">
-        <v>88</v>
-      </c>
-      <c r="B87" s="21" t="s">
+      <c r="F100" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G94</f>
+        <v>46440</v>
+      </c>
+      <c r="G100" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H94</f>
+        <v>46449</v>
+      </c>
+      <c r="H100" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I94</f>
+        <v>4</v>
+      </c>
+      <c r="I100" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="54" t="s">
+        <v>266</v>
+      </c>
+      <c r="K100" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="L100" s="25"/>
+      <c r="M100" s="25"/>
+      <c r="N100" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="O100" s="22" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B101" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="C87" s="21" t="s">
+      <c r="C101" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="D87" s="22" t="s">
+      <c r="D101" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F101" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G95</f>
+        <v>46450</v>
+      </c>
+      <c r="G101" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H95</f>
+        <v>46458</v>
+      </c>
+      <c r="H101" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I95</f>
+        <v>6</v>
+      </c>
+      <c r="I101" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="57" t="s">
+        <v>270</v>
+      </c>
+      <c r="K101" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="L101" s="19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M101" s="19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N101" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="O101" s="12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="B102" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C102" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="E87" s="27" t="s">
+      <c r="D102" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="E102" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F87" s="27"/>
-      <c r="G87" s="27"/>
-      <c r="H87" s="27"/>
-      <c r="I87" s="27"/>
-      <c r="J87" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="K87" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="L87" s="25"/>
-      <c r="M87" s="25"/>
-      <c r="N87" s="21"/>
-      <c r="O87" s="22" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="10" t="n">
-        <v>89</v>
-      </c>
-      <c r="B88" s="11" t="s">
+      <c r="F102" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G96</f>
+        <v>46450</v>
+      </c>
+      <c r="G102" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H96</f>
+        <v>46450</v>
+      </c>
+      <c r="H102" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I96</f>
+        <v>6</v>
+      </c>
+      <c r="I102" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="K102" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="L102" s="25"/>
+      <c r="M102" s="25"/>
+      <c r="N102" s="21"/>
+      <c r="O102" s="22" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="B103" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="C88" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E88" s="13" t="s">
+      <c r="C103" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E103" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="13"/>
-      <c r="J88" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="K88" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="L88" s="19"/>
-      <c r="M88" s="19"/>
-      <c r="N88" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="O88" s="12" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="B89" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="C89" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="D89" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="E89" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F89" s="27"/>
-      <c r="G89" s="27"/>
-      <c r="H89" s="27"/>
-      <c r="I89" s="27"/>
-      <c r="J89" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="K89" s="24"/>
-      <c r="L89" s="25"/>
-      <c r="M89" s="25"/>
-      <c r="N89" s="21"/>
-      <c r="O89" s="22" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="10" t="n">
-        <v>91</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="K90" s="18" t="s">
+      <c r="F103" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G97</f>
+        <v>46437</v>
+      </c>
+      <c r="G103" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H97</f>
+        <v>46437</v>
+      </c>
+      <c r="H103" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I97</f>
+        <v>4</v>
+      </c>
+      <c r="I103" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="K103" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="L90" s="19"/>
-      <c r="M90" s="19"/>
-      <c r="N90" s="11"/>
-      <c r="O90" s="12" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="B91" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="C91" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="D91" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="E91" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F91" s="27"/>
-      <c r="G91" s="27"/>
-      <c r="H91" s="27"/>
-      <c r="I91" s="27"/>
-      <c r="J91" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="K91" s="24"/>
-      <c r="L91" s="25"/>
-      <c r="M91" s="25"/>
-      <c r="N91" s="21"/>
-      <c r="O91" s="22" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="10" t="n">
-        <v>93</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F92" s="13"/>
-      <c r="G92" s="13"/>
-      <c r="H92" s="13"/>
-      <c r="I92" s="13"/>
-      <c r="J92" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="K92" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="L92" s="19"/>
-      <c r="M92" s="19"/>
-      <c r="N92" s="11"/>
-      <c r="O92" s="12" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="30" t="n">
-        <v>94</v>
-      </c>
-      <c r="B93" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="C93" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="D93" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="E93" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F93" s="27"/>
-      <c r="G93" s="27"/>
-      <c r="H93" s="27"/>
-      <c r="I93" s="27"/>
-      <c r="J93" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="K93" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="L93" s="25"/>
-      <c r="M93" s="25"/>
-      <c r="N93" s="21"/>
-      <c r="O93" s="22" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="E94" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="13"/>
-      <c r="J94" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="K94" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="L94" s="19"/>
-      <c r="M94" s="19"/>
-      <c r="N94" s="11"/>
-      <c r="O94" s="12" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="30" t="n">
-        <v>96</v>
-      </c>
-      <c r="B95" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="C95" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="D95" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="E95" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F95" s="27"/>
-      <c r="G95" s="27"/>
-      <c r="H95" s="27"/>
-      <c r="I95" s="27"/>
-      <c r="J95" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="K95" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="L95" s="25"/>
-      <c r="M95" s="25"/>
-      <c r="N95" s="21"/>
-      <c r="O95" s="22" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="10" t="n">
-        <v>97</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
-      <c r="J96" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="K96" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="L96" s="19"/>
-      <c r="M96" s="19"/>
-      <c r="N96" s="11"/>
-      <c r="O96" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="30" t="n">
-        <v>98</v>
-      </c>
-      <c r="B97" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="C97" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="D97" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="E97" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F97" s="27"/>
-      <c r="G97" s="27"/>
-      <c r="H97" s="27"/>
-      <c r="I97" s="27"/>
-      <c r="J97" s="38" t="s">
-        <v>260</v>
-      </c>
-      <c r="K97" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L97" s="25"/>
-      <c r="M97" s="25" t="n">
-        <v>3500</v>
-      </c>
-      <c r="N97" s="21"/>
-      <c r="O97" s="22" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="E98" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="K98" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="L98" s="19"/>
-      <c r="M98" s="19"/>
-      <c r="N98" s="11"/>
-      <c r="O98" s="12" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="30" t="n">
-        <v>100</v>
-      </c>
-      <c r="B99" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="C99" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="D99" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="E99" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F99" s="27"/>
-      <c r="G99" s="27"/>
-      <c r="H99" s="27"/>
-      <c r="I99" s="27"/>
-      <c r="J99" s="54" t="s">
-        <v>265</v>
-      </c>
-      <c r="K99" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="L99" s="25"/>
-      <c r="M99" s="25"/>
-      <c r="N99" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="O99" s="22" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="10" t="n">
-        <v>101</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
-      <c r="J100" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="K100" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="L100" s="19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M100" s="19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="N100" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="O100" s="12" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="30" t="n">
-        <v>102</v>
-      </c>
-      <c r="B101" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="C101" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="D101" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="E101" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F101" s="27"/>
-      <c r="G101" s="27"/>
-      <c r="H101" s="27"/>
-      <c r="I101" s="27"/>
-      <c r="J101" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="K101" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="L101" s="25"/>
-      <c r="M101" s="25"/>
-      <c r="N101" s="21"/>
-      <c r="O101" s="22"/>
-    </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="10" t="n">
-        <v>103</v>
-      </c>
-      <c r="B102" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="E102" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="K102" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="L102" s="19"/>
-      <c r="M102" s="19"/>
-      <c r="N102" s="11"/>
-      <c r="O102" s="12"/>
-    </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="10" t="n">
-        <v>107</v>
-      </c>
-      <c r="B103" s="10"/>
-      <c r="C103" s="10"/>
-      <c r="D103" s="10"/>
-      <c r="E103" s="10"/>
-      <c r="F103" s="10"/>
-      <c r="G103" s="10"/>
-      <c r="H103" s="10"/>
-      <c r="I103" s="10"/>
-      <c r="J103" s="10"/>
-      <c r="K103" s="10"/>
-      <c r="L103" s="10"/>
-      <c r="M103" s="10"/>
-      <c r="N103" s="10"/>
-      <c r="O103" s="10"/>
+      <c r="L103" s="19"/>
+      <c r="M103" s="19"/>
+      <c r="N103" s="11"/>
+      <c r="O103" s="12" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="30" t="n">
@@ -7372,86 +7789,106 @@
         <v>227</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="D104" s="22" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E104" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F104" s="27"/>
-      <c r="G104" s="27"/>
-      <c r="H104" s="27"/>
-      <c r="I104" s="27"/>
+      <c r="F104" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G98</f>
+        <v>46451</v>
+      </c>
+      <c r="G104" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H98</f>
+        <v>46451</v>
+      </c>
+      <c r="H104" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I98</f>
+        <v>3</v>
+      </c>
+      <c r="I104" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="J104" s="54" t="s">
         <v>154</v>
       </c>
       <c r="K104" s="24" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L104" s="25"/>
       <c r="M104" s="25"/>
       <c r="N104" s="21"/>
       <c r="O104" s="22" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="n">
-        <v>107</v>
-      </c>
-      <c r="B105" s="55"/>
-      <c r="C105" s="55"/>
-      <c r="D105" s="55"/>
-      <c r="E105" s="55"/>
-      <c r="F105" s="55"/>
-      <c r="G105" s="55"/>
-      <c r="H105" s="55"/>
-      <c r="I105" s="55"/>
-      <c r="J105" s="55"/>
-      <c r="K105" s="55"/>
-      <c r="L105" s="55"/>
-      <c r="M105" s="55"/>
-      <c r="N105" s="55"/>
-      <c r="O105" s="56"/>
+        <v>105</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F105" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G99</f>
+        <v>46451</v>
+      </c>
+      <c r="G105" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H99</f>
+        <v>46451</v>
+      </c>
+      <c r="H105" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I99</f>
+        <v>3</v>
+      </c>
+      <c r="I105" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="K105" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="L105" s="19"/>
+      <c r="M105" s="19"/>
+      <c r="N105" s="11"/>
+      <c r="O105" s="12" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="10" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="E106" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F106" s="13"/>
-      <c r="G106" s="13"/>
-      <c r="H106" s="13"/>
-      <c r="I106" s="13"/>
-      <c r="J106" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="K106" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="L106" s="19"/>
-      <c r="M106" s="19"/>
-      <c r="N106" s="11"/>
-      <c r="O106" s="12" t="s">
-        <v>283</v>
-      </c>
+      <c r="A106" s="10"/>
+      <c r="B106" s="55"/>
+      <c r="C106" s="55"/>
+      <c r="D106" s="55"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="55"/>
+      <c r="G106" s="55"/>
+      <c r="H106" s="55"/>
+      <c r="I106" s="55"/>
+      <c r="J106" s="55"/>
+      <c r="K106" s="55"/>
+      <c r="L106" s="55"/>
+      <c r="M106" s="55"/>
+      <c r="N106" s="55"/>
+      <c r="O106" s="56"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="9" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B107" s="55"/>
       <c r="C107" s="55"/>
@@ -7470,160 +7907,213 @@
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="30" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B108" s="21" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D108" s="22" t="s">
-        <v>229</v>
+        <v>289</v>
       </c>
       <c r="E108" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F108" s="27"/>
-      <c r="G108" s="27"/>
-      <c r="H108" s="27"/>
-      <c r="I108" s="27"/>
+      <c r="F108" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G101</f>
+        <v>46387</v>
+      </c>
+      <c r="G108" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H101</f>
+        <v>46394</v>
+      </c>
+      <c r="H108" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I101</f>
+        <v>1</v>
+      </c>
+      <c r="I108" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="J108" s="27" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="K108" s="24" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="L108" s="25"/>
       <c r="M108" s="25"/>
-      <c r="N108" s="21" t="s">
-        <v>206</v>
-      </c>
+      <c r="N108" s="21"/>
       <c r="O108" s="22" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="10" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C109" s="11" t="s">
         <v>228</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>286</v>
+        <v>241</v>
       </c>
       <c r="E109" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F109" s="13"/>
-      <c r="G109" s="13"/>
-      <c r="H109" s="13"/>
-      <c r="I109" s="13"/>
+      <c r="F109" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G102</f>
+        <v>46409</v>
+      </c>
+      <c r="G109" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H102</f>
+        <v>46413</v>
+      </c>
+      <c r="H109" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I102</f>
+        <v>16</v>
+      </c>
+      <c r="I109" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="J109" s="13" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="K109" s="18" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="L109" s="19"/>
       <c r="M109" s="19"/>
       <c r="N109" s="11"/>
       <c r="O109" s="12" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="30" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C110" s="21" t="s">
         <v>228</v>
       </c>
       <c r="D110" s="22" t="s">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="E110" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F110" s="27"/>
-      <c r="G110" s="27"/>
-      <c r="H110" s="27"/>
-      <c r="I110" s="27"/>
+      <c r="F110" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G103</f>
+        <v>46414</v>
+      </c>
+      <c r="G110" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H103</f>
+        <v>46419</v>
+      </c>
+      <c r="H110" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I103</f>
+        <v>24</v>
+      </c>
+      <c r="I110" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="J110" s="27" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="K110" s="24" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="L110" s="25"/>
       <c r="M110" s="25"/>
-      <c r="N110" s="21" t="s">
-        <v>212</v>
-      </c>
+      <c r="N110" s="21"/>
       <c r="O110" s="22" t="s">
-        <v>234</v>
+        <v>291</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>228</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="E111" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F111" s="13"/>
-      <c r="G111" s="13"/>
-      <c r="H111" s="13"/>
-      <c r="I111" s="13"/>
-      <c r="J111" s="57" t="s">
-        <v>236</v>
-      </c>
-      <c r="K111" s="18"/>
+      <c r="F111" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G104</f>
+        <v>46414</v>
+      </c>
+      <c r="G111" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H104</f>
+        <v>46414</v>
+      </c>
+      <c r="H111" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I104</f>
+        <v>3</v>
+      </c>
+      <c r="I111" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="K111" s="18" t="s">
+        <v>92</v>
+      </c>
       <c r="L111" s="19"/>
       <c r="M111" s="19"/>
       <c r="N111" s="11"/>
       <c r="O111" s="12" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="30" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B112" s="21" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D112" s="22" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E112" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F112" s="27"/>
-      <c r="G112" s="27"/>
-      <c r="H112" s="27"/>
-      <c r="I112" s="27"/>
+      <c r="F112" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G105</f>
+        <v>46409</v>
+      </c>
+      <c r="G112" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H105</f>
+        <v>46409</v>
+      </c>
+      <c r="H112" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I105</f>
+        <v>2</v>
+      </c>
+      <c r="I112" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="J112" s="27" t="s">
-        <v>240</v>
+        <v>157</v>
       </c>
       <c r="K112" s="24" t="s">
         <v>92</v>
@@ -7632,294 +8122,409 @@
       <c r="M112" s="25"/>
       <c r="N112" s="21"/>
       <c r="O112" s="22" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="E113" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
-      <c r="I113" s="13"/>
+      <c r="F113" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G106</f>
+        <v>46428</v>
+      </c>
+      <c r="G113" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H106</f>
+        <v>46434</v>
+      </c>
+      <c r="H113" s="40" t="str">
+        <f aca="false">'Schedule Logic'!I106</f>
+        <v>-</v>
+      </c>
+      <c r="I113" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="J113" s="33" t="s">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="K113" s="18" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L113" s="19"/>
       <c r="M113" s="19"/>
       <c r="N113" s="11"/>
       <c r="O113" s="12" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="30" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="D114" s="22" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E114" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F114" s="27"/>
-      <c r="G114" s="27"/>
-      <c r="H114" s="27"/>
-      <c r="I114" s="27"/>
-      <c r="J114" s="27" t="s">
-        <v>255</v>
+      <c r="F114" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G107</f>
+        <v>46435</v>
+      </c>
+      <c r="G114" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H107</f>
+        <v>46435</v>
+      </c>
+      <c r="H114" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I107</f>
+        <v>3</v>
+      </c>
+      <c r="I114" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="38" t="s">
+        <v>260</v>
       </c>
       <c r="K114" s="24" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="L114" s="25"/>
       <c r="M114" s="25"/>
       <c r="N114" s="21"/>
-      <c r="O114" s="22" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="O114" s="22"/>
+    </row>
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="10" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E115" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F115" s="13"/>
-      <c r="G115" s="13"/>
-      <c r="H115" s="13"/>
-      <c r="I115" s="13"/>
+      <c r="F115" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G108</f>
+        <v>46437</v>
+      </c>
+      <c r="G115" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H108</f>
+        <v>46437</v>
+      </c>
+      <c r="H115" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I108</f>
+        <v>4</v>
+      </c>
+      <c r="I115" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="J115" s="13" t="s">
-        <v>255</v>
+        <v>205</v>
       </c>
       <c r="K115" s="18" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="L115" s="19"/>
       <c r="M115" s="19"/>
-      <c r="N115" s="11"/>
+      <c r="N115" s="11" t="s">
+        <v>206</v>
+      </c>
       <c r="O115" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="30" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="D116" s="22" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E116" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F116" s="27"/>
-      <c r="G116" s="27"/>
-      <c r="H116" s="27"/>
-      <c r="I116" s="27"/>
-      <c r="J116" s="38" t="s">
-        <v>260</v>
+      <c r="F116" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G109</f>
+        <v>46440</v>
+      </c>
+      <c r="G116" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H109</f>
+        <v>46449</v>
+      </c>
+      <c r="H116" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I109</f>
+        <v>4</v>
+      </c>
+      <c r="I116" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="27" t="s">
+        <v>210</v>
       </c>
       <c r="K116" s="24" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="L116" s="25"/>
       <c r="M116" s="25"/>
-      <c r="N116" s="21"/>
+      <c r="N116" s="21" t="s">
+        <v>212</v>
+      </c>
       <c r="O116" s="22" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E117" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F117" s="13"/>
-      <c r="G117" s="13"/>
-      <c r="H117" s="13"/>
-      <c r="I117" s="13"/>
-      <c r="J117" s="13" t="s">
-        <v>157</v>
+      <c r="F117" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G110</f>
+        <v>46440</v>
+      </c>
+      <c r="G117" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H110</f>
+        <v>46449</v>
+      </c>
+      <c r="H117" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I110</f>
+        <v>3</v>
+      </c>
+      <c r="I117" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="57" t="s">
+        <v>266</v>
       </c>
       <c r="K117" s="18" t="s">
-        <v>92</v>
+        <v>267</v>
       </c>
       <c r="L117" s="19"/>
       <c r="M117" s="19"/>
-      <c r="N117" s="11"/>
-      <c r="O117" s="12" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N117" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="O117" s="12"/>
+    </row>
+    <row r="118" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="30" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="D118" s="22" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E118" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F118" s="27"/>
-      <c r="G118" s="27"/>
-      <c r="H118" s="27"/>
-      <c r="I118" s="27"/>
+      <c r="F118" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G111</f>
+        <v>46450</v>
+      </c>
+      <c r="G118" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H111</f>
+        <v>46451</v>
+      </c>
+      <c r="H118" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I111</f>
+        <v>8</v>
+      </c>
+      <c r="I118" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="J118" s="54" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K118" s="24" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="L118" s="25"/>
       <c r="M118" s="25"/>
-      <c r="N118" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="O118" s="22"/>
-    </row>
-    <row r="119" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N118" s="21"/>
+      <c r="O118" s="22" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E119" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F119" s="13"/>
-      <c r="G119" s="13"/>
-      <c r="H119" s="13"/>
-      <c r="I119" s="13"/>
+      <c r="F119" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G112</f>
+        <v>46450</v>
+      </c>
+      <c r="G119" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H112</f>
+        <v>46450</v>
+      </c>
+      <c r="H119" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I112</f>
+        <v>4</v>
+      </c>
+      <c r="I119" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="J119" s="57" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K119" s="18" t="s">
-        <v>293</v>
+        <v>92</v>
       </c>
       <c r="L119" s="19"/>
       <c r="M119" s="19"/>
       <c r="N119" s="11"/>
       <c r="O119" s="12" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="30" t="n">
-        <v>122</v>
-      </c>
-      <c r="B120" s="30"/>
-      <c r="C120" s="30"/>
-      <c r="D120" s="30"/>
-      <c r="E120" s="30"/>
-      <c r="F120" s="30"/>
-      <c r="G120" s="30"/>
-      <c r="H120" s="30"/>
-      <c r="I120" s="30"/>
-      <c r="J120" s="30"/>
-      <c r="K120" s="30"/>
-      <c r="L120" s="30"/>
-      <c r="M120" s="30"/>
-      <c r="N120" s="30"/>
-      <c r="O120" s="30"/>
+        <v>110</v>
+      </c>
+      <c r="B120" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C120" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="D120" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="E120" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F120" s="35" t="n">
+        <f aca="false">'Schedule Logic'!G113</f>
+        <v>46437</v>
+      </c>
+      <c r="G120" s="35" t="n">
+        <f aca="false">'Schedule Logic'!H113</f>
+        <v>46437</v>
+      </c>
+      <c r="H120" s="36" t="n">
+        <f aca="false">'Schedule Logic'!I113</f>
+        <v>4</v>
+      </c>
+      <c r="I120" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="K120" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="L120" s="25"/>
+      <c r="M120" s="25"/>
+      <c r="N120" s="21"/>
+      <c r="O120" s="22" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="30" t="n">
-        <v>118</v>
-      </c>
-      <c r="B121" s="21" t="s">
+      <c r="A121" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D121" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="C121" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="D121" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="E121" s="27" t="s">
+      <c r="E121" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F121" s="27"/>
-      <c r="G121" s="27"/>
-      <c r="H121" s="27"/>
-      <c r="I121" s="27"/>
-      <c r="J121" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="K121" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="L121" s="25"/>
-      <c r="M121" s="25"/>
-      <c r="N121" s="21"/>
-      <c r="O121" s="22"/>
+      <c r="F121" s="39" t="n">
+        <f aca="false">'Schedule Logic'!G114</f>
+        <v>46451</v>
+      </c>
+      <c r="G121" s="39" t="n">
+        <f aca="false">'Schedule Logic'!H114</f>
+        <v>46451</v>
+      </c>
+      <c r="H121" s="40" t="n">
+        <f aca="false">'Schedule Logic'!I114</f>
+        <v>3</v>
+      </c>
+      <c r="I121" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="K121" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="L121" s="19"/>
+      <c r="M121" s="19"/>
+      <c r="N121" s="11"/>
+      <c r="O121" s="12" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="10" t="n">
-        <v>123</v>
-      </c>
+      <c r="A122" s="10"/>
       <c r="B122" s="55"/>
       <c r="C122" s="55"/>
       <c r="D122" s="55"/>
@@ -7936,41 +8541,25 @@
       <c r="O122" s="56"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="10" t="n">
-        <v>119</v>
-      </c>
-      <c r="B123" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="C123" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="E123" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F123" s="13"/>
-      <c r="G123" s="13"/>
-      <c r="H123" s="13"/>
-      <c r="I123" s="13"/>
-      <c r="J123" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="K123" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="L123" s="19"/>
-      <c r="M123" s="19"/>
-      <c r="N123" s="11"/>
-      <c r="O123" s="12" t="s">
-        <v>295</v>
-      </c>
+      <c r="A123" s="10"/>
+      <c r="B123" s="55"/>
+      <c r="C123" s="55"/>
+      <c r="D123" s="55"/>
+      <c r="E123" s="55"/>
+      <c r="F123" s="55"/>
+      <c r="G123" s="55"/>
+      <c r="H123" s="55"/>
+      <c r="I123" s="55"/>
+      <c r="J123" s="55"/>
+      <c r="K123" s="55"/>
+      <c r="L123" s="55"/>
+      <c r="M123" s="55"/>
+      <c r="N123" s="55"/>
+      <c r="O123" s="56"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="9" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B124" s="55"/>
       <c r="C124" s="55"/>
@@ -7992,13 +8581,13 @@
         <v>120</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C125" s="21" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D125" s="22" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E125" s="27" t="s">
         <v>30</v>
@@ -8008,7 +8597,7 @@
       <c r="H125" s="27"/>
       <c r="I125" s="27"/>
       <c r="J125" s="38" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K125" s="24"/>
       <c r="L125" s="25"/>
@@ -8021,13 +8610,13 @@
         <v>121</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E126" s="13" t="s">
         <v>30</v>
@@ -8037,7 +8626,7 @@
       <c r="H126" s="13"/>
       <c r="I126" s="13"/>
       <c r="J126" s="33" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K126" s="18"/>
       <c r="L126" s="19"/>
@@ -8050,13 +8639,13 @@
         <v>122</v>
       </c>
       <c r="B127" s="21" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E127" s="27" t="s">
         <v>30</v>
@@ -8066,16 +8655,16 @@
       <c r="H127" s="27"/>
       <c r="I127" s="27"/>
       <c r="J127" s="38" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K127" s="24" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L127" s="25"/>
       <c r="M127" s="25"/>
       <c r="N127" s="21"/>
       <c r="O127" s="22" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8083,13 +8672,13 @@
         <v>123</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E128" s="13" t="s">
         <v>30</v>
@@ -8099,7 +8688,7 @@
       <c r="H128" s="13"/>
       <c r="I128" s="13"/>
       <c r="J128" s="33" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="K128" s="18" t="s">
         <v>123</v>
@@ -8114,13 +8703,13 @@
         <v>124</v>
       </c>
       <c r="B129" s="21" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C129" s="21" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D129" s="22" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E129" s="27" t="s">
         <v>30</v>
@@ -8130,7 +8719,7 @@
       <c r="H129" s="27"/>
       <c r="I129" s="27"/>
       <c r="J129" s="38" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="K129" s="24" t="s">
         <v>123</v>
@@ -8145,13 +8734,13 @@
         <v>125</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E130" s="13" t="s">
         <v>30</v>
@@ -8161,7 +8750,7 @@
       <c r="H130" s="13"/>
       <c r="I130" s="13"/>
       <c r="J130" s="33" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="K130" s="18" t="s">
         <v>123</v>
@@ -8176,13 +8765,13 @@
         <v>126</v>
       </c>
       <c r="B131" s="21" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C131" s="21" t="s">
         <v>134</v>
       </c>
       <c r="D131" s="22" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E131" s="27" t="s">
         <v>30</v>
@@ -8192,7 +8781,7 @@
       <c r="H131" s="27"/>
       <c r="I131" s="27"/>
       <c r="J131" s="38" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="K131" s="24" t="s">
         <v>123</v>
@@ -8201,7 +8790,7 @@
       <c r="M131" s="25"/>
       <c r="N131" s="21"/>
       <c r="O131" s="22" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8209,13 +8798,13 @@
         <v>127</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C132" s="11" t="s">
         <v>134</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E132" s="13" t="s">
         <v>30</v>
@@ -8225,14 +8814,14 @@
       <c r="H132" s="13"/>
       <c r="I132" s="13"/>
       <c r="J132" s="33" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K132" s="11"/>
       <c r="L132" s="19"/>
       <c r="M132" s="19"/>
       <c r="N132" s="11"/>
       <c r="O132" s="12" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8240,13 +8829,13 @@
         <v>128</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C133" s="21" t="s">
         <v>134</v>
       </c>
       <c r="D133" s="22" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E133" s="27" t="s">
         <v>30</v>
@@ -8256,7 +8845,7 @@
       <c r="H133" s="27"/>
       <c r="I133" s="27"/>
       <c r="J133" s="38" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="K133" s="24" t="s">
         <v>123</v>
@@ -8271,13 +8860,13 @@
         <v>129</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C134" s="11" t="s">
         <v>134</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E134" s="13" t="s">
         <v>30</v>
@@ -8287,7 +8876,7 @@
       <c r="H134" s="13"/>
       <c r="I134" s="13"/>
       <c r="J134" s="57" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K134" s="18" t="s">
         <v>71</v>
@@ -8296,7 +8885,7 @@
       <c r="M134" s="19"/>
       <c r="N134" s="11"/>
       <c r="O134" s="12" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8304,13 +8893,13 @@
         <v>130</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C135" s="21" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D135" s="22" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>30</v>
@@ -8320,7 +8909,7 @@
       <c r="H135" s="27"/>
       <c r="I135" s="27"/>
       <c r="J135" s="38" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K135" s="24" t="s">
         <v>71</v>
@@ -8329,7 +8918,7 @@
       <c r="M135" s="25"/>
       <c r="N135" s="21"/>
       <c r="O135" s="22" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8337,13 +8926,13 @@
         <v>131</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E136" s="13" t="s">
         <v>30</v>
@@ -8353,7 +8942,7 @@
       <c r="H136" s="13"/>
       <c r="I136" s="13"/>
       <c r="J136" s="33" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K136" s="18" t="s">
         <v>71</v>
@@ -8362,7 +8951,7 @@
       <c r="M136" s="19"/>
       <c r="N136" s="11"/>
       <c r="O136" s="12" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8408,13 +8997,13 @@
         <v>133</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E139" s="13" t="s">
         <v>30</v>
@@ -8424,16 +9013,16 @@
       <c r="H139" s="13"/>
       <c r="I139" s="13"/>
       <c r="J139" s="33" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K139" s="18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L139" s="19"/>
       <c r="M139" s="19"/>
       <c r="N139" s="11"/>
       <c r="O139" s="12" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8441,13 +9030,13 @@
         <v>134</v>
       </c>
       <c r="B140" s="21" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C140" s="21" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D140" s="22" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E140" s="27" t="s">
         <v>30</v>
@@ -8457,16 +9046,16 @@
       <c r="H140" s="27"/>
       <c r="I140" s="27"/>
       <c r="J140" s="38" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="K140" s="24" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L140" s="25"/>
       <c r="M140" s="25"/>
       <c r="N140" s="21"/>
       <c r="O140" s="22" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8493,13 +9082,13 @@
         <v>135</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E142" s="13" t="s">
         <v>30</v>
@@ -8509,21 +9098,21 @@
       <c r="H142" s="13"/>
       <c r="I142" s="13"/>
       <c r="J142" s="57" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K142" s="18" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="L142" s="19"/>
       <c r="M142" s="19"/>
       <c r="N142" s="11"/>
       <c r="O142" s="12" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B143" s="55"/>
       <c r="C143" s="55"/>
@@ -8545,13 +9134,13 @@
         <v>136</v>
       </c>
       <c r="B144" s="21" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C144" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D144" s="22" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E144" s="27" t="s">
         <v>30</v>
@@ -8561,14 +9150,14 @@
       <c r="H144" s="27"/>
       <c r="I144" s="27"/>
       <c r="J144" s="54" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="K144" s="24"/>
       <c r="L144" s="25"/>
       <c r="M144" s="25"/>
       <c r="N144" s="21"/>
       <c r="O144" s="22" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8576,13 +9165,13 @@
         <v>137</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E145" s="13" t="s">
         <v>30</v>
@@ -8592,14 +9181,14 @@
       <c r="H145" s="13"/>
       <c r="I145" s="13"/>
       <c r="J145" s="57" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="K145" s="18"/>
       <c r="L145" s="19"/>
       <c r="M145" s="19"/>
       <c r="N145" s="11"/>
       <c r="O145" s="12" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8607,13 +9196,13 @@
         <v>138</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C146" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D146" s="22" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E146" s="27" t="s">
         <v>30</v>
@@ -8623,7 +9212,7 @@
       <c r="H146" s="27"/>
       <c r="I146" s="27"/>
       <c r="J146" s="54" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K146" s="24"/>
       <c r="L146" s="25"/>
@@ -8636,13 +9225,13 @@
         <v>139</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C147" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E147" s="13" t="s">
         <v>30</v>
@@ -8652,14 +9241,14 @@
       <c r="H147" s="13"/>
       <c r="I147" s="13"/>
       <c r="J147" s="57" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K147" s="18"/>
       <c r="L147" s="19"/>
       <c r="M147" s="19"/>
       <c r="N147" s="11"/>
       <c r="O147" s="12" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8667,13 +9256,13 @@
         <v>140</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C148" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D148" s="22" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E148" s="27" t="s">
         <v>30</v>
@@ -8683,7 +9272,7 @@
       <c r="H148" s="27"/>
       <c r="I148" s="27"/>
       <c r="J148" s="54" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K148" s="24"/>
       <c r="L148" s="25"/>
@@ -8696,13 +9285,13 @@
         <v>141</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C149" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E149" s="13" t="s">
         <v>30</v>
@@ -8712,7 +9301,7 @@
       <c r="H149" s="13"/>
       <c r="I149" s="13"/>
       <c r="J149" s="57" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K149" s="18"/>
       <c r="L149" s="19"/>
@@ -8725,7 +9314,7 @@
       <c r="B150" s="58"/>
       <c r="C150" s="58"/>
       <c r="D150" s="59" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E150" s="58"/>
       <c r="L150" s="60" t="n">
@@ -8741,7 +9330,7 @@
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="9" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
@@ -8763,13 +9352,13 @@
         <v>15</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E152" s="20" t="s">
         <v>39</v>
@@ -8790,7 +9379,7 @@
       </c>
       <c r="N152" s="11"/>
       <c r="O152" s="12" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8798,13 +9387,13 @@
         <v>16</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C153" s="21" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D153" s="22" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E153" s="31" t="s">
         <v>39</v>
@@ -8827,13 +9416,13 @@
         <v>17</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E154" s="20" t="s">
         <v>39</v>
@@ -8850,7 +9439,7 @@
       <c r="M154" s="19"/>
       <c r="N154" s="11"/>
       <c r="O154" s="12" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8858,13 +9447,13 @@
         <v>18</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C155" s="21" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D155" s="22" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="E155" s="27" t="s">
         <v>30</v>
@@ -8874,7 +9463,7 @@
       <c r="H155" s="27"/>
       <c r="I155" s="27"/>
       <c r="J155" s="38" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K155" s="24" t="s">
         <v>123</v>
@@ -8883,7 +9472,7 @@
       <c r="M155" s="25"/>
       <c r="N155" s="21"/>
       <c r="O155" s="22" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8891,13 +9480,13 @@
         <v>19</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E156" s="13" t="s">
         <v>30</v>
@@ -8907,7 +9496,7 @@
       <c r="H156" s="13"/>
       <c r="I156" s="13"/>
       <c r="J156" s="33" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K156" s="18" t="s">
         <v>123</v>
@@ -8916,7 +9505,7 @@
       <c r="M156" s="19"/>
       <c r="N156" s="11"/>
       <c r="O156" s="12" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8924,13 +9513,13 @@
         <v>20</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C157" s="21" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D157" s="22" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E157" s="31" t="s">
         <v>39</v>
@@ -8953,13 +9542,13 @@
         <v>21</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D158" s="12" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E158" s="13" t="s">
         <v>30</v>
@@ -8969,16 +9558,16 @@
       <c r="H158" s="13"/>
       <c r="I158" s="13"/>
       <c r="J158" s="33" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K158" s="18" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L158" s="19"/>
       <c r="M158" s="19"/>
       <c r="N158" s="11"/>
       <c r="O158" s="12" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8986,13 +9575,13 @@
         <v>22</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C159" s="21" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D159" s="22" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E159" s="27" t="s">
         <v>30</v>
@@ -9002,7 +9591,7 @@
       <c r="H159" s="27"/>
       <c r="I159" s="27"/>
       <c r="J159" s="38" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K159" s="24" t="s">
         <v>123</v>
@@ -9017,13 +9606,13 @@
         <v>23</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E160" s="13" t="s">
         <v>30</v>
@@ -9033,14 +9622,14 @@
       <c r="H160" s="13"/>
       <c r="I160" s="13"/>
       <c r="J160" s="57" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K160" s="18"/>
       <c r="L160" s="19"/>
       <c r="M160" s="19"/>
       <c r="N160" s="11"/>
       <c r="O160" s="12" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9048,13 +9637,13 @@
         <v>24</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C161" s="21" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D161" s="22" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E161" s="31" t="s">
         <v>39</v>
@@ -9071,7 +9660,7 @@
       <c r="M161" s="25"/>
       <c r="N161" s="21"/>
       <c r="O161" s="22" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9079,13 +9668,13 @@
         <v>25</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E162" s="20" t="s">
         <v>39</v>
@@ -9106,7 +9695,7 @@
       </c>
       <c r="N162" s="11"/>
       <c r="O162" s="12" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9114,13 +9703,13 @@
         <v>26</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D163" s="22" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E163" s="31" t="s">
         <v>39</v>
@@ -9137,7 +9726,7 @@
       <c r="M163" s="25"/>
       <c r="N163" s="21"/>
       <c r="O163" s="22" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9145,13 +9734,13 @@
         <v>27</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E164" s="13" t="s">
         <v>30</v>
@@ -9161,7 +9750,7 @@
       <c r="H164" s="13"/>
       <c r="I164" s="13"/>
       <c r="J164" s="13" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="K164" s="18" t="s">
         <v>53</v>
@@ -9170,7 +9759,7 @@
       <c r="M164" s="19"/>
       <c r="N164" s="11"/>
       <c r="O164" s="12" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9178,13 +9767,13 @@
         <v>28</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D165" s="22" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E165" s="27" t="s">
         <v>30</v>
@@ -9194,7 +9783,7 @@
       <c r="H165" s="27"/>
       <c r="I165" s="27"/>
       <c r="J165" s="27" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="K165" s="24" t="s">
         <v>53</v>
@@ -9203,7 +9792,7 @@
       <c r="M165" s="25"/>
       <c r="N165" s="21"/>
       <c r="O165" s="22" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9211,13 +9800,13 @@
         <v>29</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E166" s="13" t="s">
         <v>30</v>
@@ -9227,7 +9816,7 @@
       <c r="H166" s="13"/>
       <c r="I166" s="13"/>
       <c r="J166" s="57" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="K166" s="18"/>
       <c r="L166" s="19"/>
@@ -9240,13 +9829,13 @@
         <v>30</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D167" s="22" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E167" s="27" t="s">
         <v>30</v>
@@ -9256,10 +9845,10 @@
       <c r="H167" s="27"/>
       <c r="I167" s="27"/>
       <c r="J167" s="38" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="K167" s="24" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L167" s="25" t="n">
         <v>7500</v>
@@ -9269,7 +9858,7 @@
       </c>
       <c r="N167" s="21"/>
       <c r="O167" s="22" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9277,13 +9866,13 @@
         <v>31</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D168" s="12" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E168" s="13" t="s">
         <v>30</v>
@@ -9293,16 +9882,16 @@
       <c r="H168" s="13"/>
       <c r="I168" s="13"/>
       <c r="J168" s="57" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="K168" s="18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L168" s="19"/>
       <c r="M168" s="19"/>
       <c r="N168" s="11"/>
       <c r="O168" s="12" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9310,13 +9899,13 @@
         <v>32</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D169" s="22" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E169" s="27" t="s">
         <v>30</v>
@@ -9326,14 +9915,14 @@
       <c r="H169" s="27"/>
       <c r="I169" s="27"/>
       <c r="J169" s="38" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="K169" s="24"/>
       <c r="L169" s="25"/>
       <c r="M169" s="25"/>
       <c r="N169" s="21"/>
       <c r="O169" s="22" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9341,13 +9930,13 @@
         <v>33</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E170" s="33" t="s">
         <v>81</v>
@@ -9357,10 +9946,10 @@
       <c r="H170" s="33"/>
       <c r="I170" s="33"/>
       <c r="J170" s="13" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="K170" s="18" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="L170" s="19" t="n">
         <v>10000</v>
@@ -9370,7 +9959,7 @@
       </c>
       <c r="N170" s="11"/>
       <c r="O170" s="12" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9378,13 +9967,13 @@
         <v>34</v>
       </c>
       <c r="B171" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D171" s="22" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E171" s="27" t="s">
         <v>30</v>
@@ -9394,16 +9983,16 @@
       <c r="H171" s="27"/>
       <c r="I171" s="27"/>
       <c r="J171" s="38" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K171" s="24" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L171" s="25"/>
       <c r="M171" s="25"/>
       <c r="N171" s="21"/>
       <c r="O171" s="22" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9411,13 +10000,13 @@
         <v>35</v>
       </c>
       <c r="B172" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E172" s="13" t="s">
         <v>30</v>
@@ -9427,7 +10016,7 @@
       <c r="H172" s="13"/>
       <c r="I172" s="13"/>
       <c r="J172" s="33" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K172" s="18"/>
       <c r="L172" s="19" t="n">
@@ -9438,7 +10027,7 @@
       </c>
       <c r="N172" s="11"/>
       <c r="O172" s="12" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9446,13 +10035,13 @@
         <v>36</v>
       </c>
       <c r="B173" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C173" s="21" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D173" s="22" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E173" s="27" t="s">
         <v>30</v>
@@ -9462,10 +10051,10 @@
       <c r="H173" s="27"/>
       <c r="I173" s="27"/>
       <c r="J173" s="38" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="K173" s="24" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="L173" s="25" t="n">
         <v>2000</v>
@@ -9477,7 +10066,7 @@
         <v>175</v>
       </c>
       <c r="O173" s="22" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9485,13 +10074,13 @@
         <v>37</v>
       </c>
       <c r="B174" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E174" s="13" t="s">
         <v>30</v>
@@ -9501,16 +10090,16 @@
       <c r="H174" s="13"/>
       <c r="I174" s="13"/>
       <c r="J174" s="33" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="K174" s="18" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="L174" s="19"/>
       <c r="M174" s="19"/>
       <c r="N174" s="11"/>
       <c r="O174" s="12" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9518,13 +10107,13 @@
         <v>38</v>
       </c>
       <c r="B175" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C175" s="21" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D175" s="22" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E175" s="27" t="s">
         <v>30</v>
@@ -9534,7 +10123,7 @@
       <c r="H175" s="27"/>
       <c r="I175" s="27"/>
       <c r="J175" s="27" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="K175" s="24" t="s">
         <v>53</v>
@@ -9545,7 +10134,7 @@
       </c>
       <c r="N175" s="21"/>
       <c r="O175" s="22" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9553,13 +10142,13 @@
         <v>39</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D176" s="12" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E176" s="13" t="s">
         <v>30</v>
@@ -9569,7 +10158,7 @@
       <c r="H176" s="13"/>
       <c r="I176" s="13"/>
       <c r="J176" s="13" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="K176" s="18" t="s">
         <v>53</v>
@@ -9578,7 +10167,7 @@
       <c r="M176" s="19"/>
       <c r="N176" s="11"/>
       <c r="O176" s="12" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9586,13 +10175,13 @@
         <v>40</v>
       </c>
       <c r="B177" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C177" s="21" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D177" s="22" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E177" s="27" t="s">
         <v>30</v>
@@ -9602,7 +10191,7 @@
       <c r="H177" s="27"/>
       <c r="I177" s="27"/>
       <c r="J177" s="27" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="K177" s="24" t="s">
         <v>53</v>
@@ -9611,7 +10200,7 @@
       <c r="M177" s="25"/>
       <c r="N177" s="21"/>
       <c r="O177" s="22" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9619,13 +10208,13 @@
         <v>41</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D178" s="12" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E178" s="13" t="s">
         <v>30</v>
@@ -9635,16 +10224,16 @@
       <c r="H178" s="13"/>
       <c r="I178" s="13"/>
       <c r="J178" s="57" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K178" s="18" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L178" s="19"/>
       <c r="M178" s="19"/>
       <c r="N178" s="11"/>
       <c r="O178" s="12" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9652,13 +10241,13 @@
         <v>42</v>
       </c>
       <c r="B179" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C179" s="21" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D179" s="22" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E179" s="27" t="s">
         <v>30</v>
@@ -9668,16 +10257,16 @@
       <c r="H179" s="27"/>
       <c r="I179" s="27"/>
       <c r="J179" s="38" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K179" s="24" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L179" s="25"/>
       <c r="M179" s="25"/>
       <c r="N179" s="21"/>
       <c r="O179" s="22" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9685,13 +10274,13 @@
         <v>43</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D180" s="12" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="E180" s="13" t="s">
         <v>30</v>
@@ -9701,10 +10290,10 @@
       <c r="H180" s="13"/>
       <c r="I180" s="13"/>
       <c r="J180" s="33" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K180" s="18" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L180" s="19"/>
       <c r="M180" s="19" t="n">
@@ -9712,7 +10301,7 @@
       </c>
       <c r="N180" s="11"/>
       <c r="O180" s="12" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9720,13 +10309,13 @@
         <v>44</v>
       </c>
       <c r="B181" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C181" s="21" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D181" s="22" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E181" s="27" t="s">
         <v>30</v>
@@ -9736,7 +10325,7 @@
       <c r="H181" s="27"/>
       <c r="I181" s="27"/>
       <c r="J181" s="38" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K181" s="24" t="s">
         <v>53</v>
@@ -9745,7 +10334,7 @@
       <c r="M181" s="25"/>
       <c r="N181" s="21"/>
       <c r="O181" s="22" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9753,13 +10342,13 @@
         <v>45</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D182" s="12" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E182" s="29" t="s">
         <v>126</v>
@@ -9782,13 +10371,13 @@
         <v>46</v>
       </c>
       <c r="B183" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C183" s="21" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D183" s="22" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E183" s="50" t="s">
         <v>126</v>
@@ -9805,7 +10394,7 @@
       <c r="M183" s="25"/>
       <c r="N183" s="21"/>
       <c r="O183" s="22" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9813,13 +10402,13 @@
         <v>47</v>
       </c>
       <c r="B184" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="D184" s="12" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E184" s="20" t="s">
         <v>39</v>
@@ -9842,13 +10431,13 @@
         <v>48</v>
       </c>
       <c r="B185" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="D185" s="22" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="E185" s="27" t="s">
         <v>30</v>
@@ -9858,14 +10447,14 @@
       <c r="H185" s="27"/>
       <c r="I185" s="27"/>
       <c r="J185" s="54" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="K185" s="24"/>
       <c r="L185" s="25"/>
       <c r="M185" s="25"/>
       <c r="N185" s="21"/>
       <c r="O185" s="22" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9873,13 +10462,13 @@
         <v>49</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="D186" s="12" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E186" s="13" t="s">
         <v>30</v>
@@ -9896,7 +10485,7 @@
       <c r="M186" s="19"/>
       <c r="N186" s="11"/>
       <c r="O186" s="12" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9904,13 +10493,13 @@
         <v>50</v>
       </c>
       <c r="B187" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C187" s="21" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="D187" s="22" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E187" s="27" t="s">
         <v>30</v>
@@ -9920,14 +10509,14 @@
       <c r="H187" s="27"/>
       <c r="I187" s="27"/>
       <c r="J187" s="54" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="K187" s="24"/>
       <c r="L187" s="25"/>
       <c r="M187" s="25"/>
       <c r="N187" s="21"/>
       <c r="O187" s="22" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9935,13 +10524,13 @@
         <v>51</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="D188" s="12" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E188" s="20" t="s">
         <v>39</v>
@@ -9958,22 +10547,20 @@
       <c r="M188" s="19"/>
       <c r="N188" s="11"/>
       <c r="O188" s="12" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="6">
     <mergeCell ref="A6:O6"/>
     <mergeCell ref="A32:O32"/>
     <mergeCell ref="A46:O46"/>
     <mergeCell ref="A58:O58"/>
-    <mergeCell ref="A103:O103"/>
-    <mergeCell ref="A120:O120"/>
     <mergeCell ref="A137:O137"/>
     <mergeCell ref="A151:O151"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E6:I6 E7:E84 E85:I149 E151:I188" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E6:I6 E7:E123 E124:I149 E151:I188" type="list">
       <formula1>"Pending,In Progress,Complete,Not Needed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10008,7 +10595,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -10028,28 +10615,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="61" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="62" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C3" s="63" t="n">
         <v>46300</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="64" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B5" s="64" t="s">
         <v>11</v>
@@ -10058,31 +10645,31 @@
         <v>14</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E5" s="64" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="G5" s="64" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="H5" s="64" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="I5" s="64" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="J5" s="64" t="s">
         <v>21</v>
       </c>
       <c r="K5" s="64" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="M5" s="65" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10103,7 +10690,7 @@
         <v>46337</v>
       </c>
       <c r="N6" s="68" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10119,7 +10706,7 @@
         <v>Determine specification sheets (Render)</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E7" s="72" t="n">
         <v>0</v>
@@ -10142,13 +10729,13 @@
         <v>53</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="M7" s="67" t="n">
         <v>46352</v>
       </c>
       <c r="N7" s="68" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10164,7 +10751,7 @@
         <v>Obtain access to Online Portal</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E8" s="72" t="n">
         <v>0</v>
@@ -10187,13 +10774,13 @@
         <v>53</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="M8" s="67" t="n">
         <v>46353</v>
       </c>
       <c r="N8" s="68" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10209,7 +10796,7 @@
         <v>Architecture &amp; Engineering design and proposal</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="E9" s="72" t="n">
         <v>5</v>
@@ -10232,13 +10819,13 @@
         <v>99</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="M9" s="67" t="n">
         <v>46380</v>
       </c>
       <c r="N9" s="68" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10254,7 +10841,7 @@
         <v>Architecture &amp; Engineering Approval</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E10" s="72" t="n">
         <v>0</v>
@@ -10277,13 +10864,13 @@
         <v>53</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M10" s="67" t="n">
         <v>46381</v>
       </c>
       <c r="N10" s="68" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10299,7 +10886,7 @@
         <v>Select provides and assign budget</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E11" s="72" t="n">
         <v>0</v>
@@ -10322,13 +10909,13 @@
         <v>53</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M11" s="67" t="n">
         <v>46388</v>
       </c>
       <c r="N11" s="68" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10344,7 +10931,7 @@
         <v>HOA / ARB approval - Garage Door</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E12" s="72" t="n">
         <v>0</v>
@@ -10367,7 +10954,7 @@
         <v>53</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10383,7 +10970,7 @@
         <v>HOA / ARB approval - exterior paint</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E13" s="72" t="n">
         <v>0</v>
@@ -10406,7 +10993,7 @@
         <v>53</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10422,7 +11009,7 @@
         <v>HOA / ARB approval - driveway</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E14" s="72" t="n">
         <v>0</v>
@@ -10445,7 +11032,7 @@
         <v>53</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10461,7 +11048,7 @@
         <v>HOA / ARB approval - Landscaping</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E15" s="72" t="n">
         <v>0</v>
@@ -10484,7 +11071,7 @@
         <v>53</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10500,7 +11087,7 @@
         <v>Certificate of insurance per trade per jurisdiction</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E16" s="72" t="n">
         <v>5</v>
@@ -10523,7 +11110,7 @@
         <v>53</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10539,7 +11126,7 @@
         <v>Workers compensation per trade</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E17" s="72" t="n">
         <v>5</v>
@@ -10562,7 +11149,7 @@
         <v>53</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10578,7 +11165,7 @@
         <v>DBPR license per trade</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E18" s="72" t="n">
         <v>5</v>
@@ -10601,7 +11188,7 @@
         <v>53</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10617,7 +11204,7 @@
         <v>Permits package submittal</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E19" s="72" t="n">
         <v>0</v>
@@ -10640,7 +11227,7 @@
         <v>53</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10656,7 +11243,7 @@
         <v>Notice of Commencement (NOC)</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E20" s="72" t="n">
         <v>0</v>
@@ -10679,7 +11266,7 @@
         <v>53</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10695,7 +11282,7 @@
         <v>GC master permit - Residential alterations and additions</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E21" s="72" t="n">
         <v>0</v>
@@ -10718,7 +11305,7 @@
         <v>53</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10734,7 +11321,7 @@
         <v>Mechanical permit</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E22" s="72" t="n">
         <v>5</v>
@@ -10757,7 +11344,7 @@
         <v>53</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10773,7 +11360,7 @@
         <v>Electrical permit</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E23" s="72" t="n">
         <v>5</v>
@@ -10796,7 +11383,7 @@
         <v>53</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10812,7 +11399,7 @@
         <v>Plumbing permit</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E24" s="72" t="n">
         <v>5</v>
@@ -10835,7 +11422,7 @@
         <v>53</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10851,7 +11438,7 @@
         <v>Fence permit</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="E25" s="72" t="n">
         <v>0</v>
@@ -10874,7 +11461,7 @@
         <v>71</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10890,7 +11477,7 @@
         <v>Driveway permit</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E26" s="72" t="n">
         <v>0</v>
@@ -10913,7 +11500,7 @@
         <v>71</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10929,7 +11516,7 @@
         <v>Gazebo permit</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="E27" s="72" t="n">
         <v>0</v>
@@ -10952,7 +11539,7 @@
         <v>53</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10968,7 +11555,7 @@
         <v>Garage-door permit</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E28" s="72" t="n">
         <v>0</v>
@@ -10991,7 +11578,7 @@
         <v>53</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11007,7 +11594,7 @@
         <v>Demolition &amp; Waste Management</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="E29" s="72" t="n">
         <v>0</v>
@@ -11031,7 +11618,7 @@
         <v>53</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11047,7 +11634,7 @@
         <v>Utilities</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="E30" s="72" t="n">
         <v>0</v>
@@ -11069,7 +11656,7 @@
         <v>53</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11100,7 +11687,7 @@
         <v>Site protection + inventory (windows, railings, outlets, switches, smoke detectors)</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E32" s="72" t="n">
         <v>0</v>
@@ -11123,7 +11710,7 @@
         <v>71</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11139,7 +11726,7 @@
         <v>Structural engineering review - removed interior walls / truss bearing</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="E33" s="72" t="n">
         <v>0</v>
@@ -11162,7 +11749,7 @@
         <v>99</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11178,7 +11765,7 @@
         <v>Popcorn ceiling removal - flat finish &amp; skin coat</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E34" s="72" t="n">
         <v>0</v>
@@ -11201,7 +11788,7 @@
         <v>102</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11217,7 +11804,7 @@
         <v>Framing repairs / new partitions</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="E35" s="72" t="n">
         <v>0</v>
@@ -11240,7 +11827,7 @@
         <v>92</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11256,7 +11843,7 @@
         <v>Slab trench patch after underground plumbing (baths/kitchen) + slab inspection</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="E36" s="72" t="n">
         <v>0</v>
@@ -11279,7 +11866,7 @@
         <v>92</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11295,7 +11882,7 @@
         <v>Concrete slab repair + tile infill under AC unit</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="E37" s="72" t="n">
         <v>0</v>
@@ -11315,10 +11902,10 @@
         <v>12</v>
       </c>
       <c r="J37" s="69" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11334,7 +11921,7 @@
         <v>Framing + MEP rough-in inspections (pre-cover milestone)</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="E38" s="72" t="n">
         <v>0</v>
@@ -11357,7 +11944,7 @@
         <v>53</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11373,7 +11960,7 @@
         <v>Drywall repair / install &amp; finish. 2nd phase </v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E39" s="72" t="n">
         <v>0</v>
@@ -11396,7 +11983,7 @@
         <v>92</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11412,7 +11999,7 @@
         <v>Drywall repair / install &amp; finish. Final phase </v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="E40" s="72" t="n">
         <v>0</v>
@@ -11435,7 +12022,7 @@
         <v>92</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11451,7 +12038,7 @@
         <v>Surface prep - primer on walls + ceilings</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="E41" s="72" t="n">
         <v>0</v>
@@ -11474,12 +12061,12 @@
         <v>123</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B42" s="66"/>
       <c r="C42" s="66"/>
@@ -11500,24 +12087,24 @@
         <v>31</v>
       </c>
       <c r="C43" s="75" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D43" s="76" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E43" s="77" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F43" s="78" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="79" t="n">
-        <f aca="false">WORKDAY(H41,1+E43,$M$6:$M$11)</f>
-        <v>46442</v>
+        <f aca="false">WORKDAY(MAX(H73,H93,H109,H90),1+E43,$M$6:$M$11)</f>
+        <v>46450</v>
       </c>
       <c r="H43" s="79" t="n">
         <f aca="false">WORKDAY(G43,F43-1,$M$6:$M$11)</f>
-        <v>46442</v>
+        <v>46450</v>
       </c>
       <c r="I43" s="73" t="s">
         <v>31</v>
@@ -11526,7 +12113,7 @@
         <v>53</v>
       </c>
       <c r="K43" s="76" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11557,7 +12144,7 @@
         <v>Make-safe exposed wiring from demolition (cap, label, temp lighting)</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="E45" s="72" t="n">
         <v>0</v>
@@ -11580,7 +12167,7 @@
         <v>102</v>
       </c>
       <c r="K45" s="12" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11596,7 +12183,7 @@
         <v>Electrical panel change out</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E46" s="72" t="n">
         <v>0</v>
@@ -11619,7 +12206,7 @@
         <v>71</v>
       </c>
       <c r="K46" s="12" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11635,7 +12222,7 @@
         <v>Electrical rough-in - relocated boxes, new kitchen/bath circuits</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="E47" s="72" t="n">
         <v>0</v>
@@ -11658,7 +12245,7 @@
         <v>102</v>
       </c>
       <c r="K47" s="12" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11674,7 +12261,7 @@
         <v>Outlets, switches, GFCI/AFCI</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="E48" s="72" t="n">
         <v>0</v>
@@ -11684,11 +12271,11 @@
       </c>
       <c r="G48" s="14" t="n">
         <f aca="false">WORKDAY(H43,1+E48,$M$6:$M$11)</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="H48" s="14" t="n">
         <f aca="false">WORKDAY(G48,F48-1,$M$6:$M$11)</f>
-        <v>46447</v>
+        <v>46455</v>
       </c>
       <c r="I48" s="72" t="n">
         <v>24</v>
@@ -11697,7 +12284,7 @@
         <v>102</v>
       </c>
       <c r="K48" s="12" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11713,7 +12300,7 @@
         <v>Recessed lighting (LED)</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="E49" s="72" t="n">
         <v>0</v>
@@ -11723,11 +12310,11 @@
       </c>
       <c r="G49" s="14" t="n">
         <f aca="false">WORKDAY(G48,E49,$M$6:$M$11)</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="H49" s="14" t="n">
         <f aca="false">WORKDAY(G49,F49-1,$M$6:$M$11)</f>
-        <v>46444</v>
+        <v>46454</v>
       </c>
       <c r="I49" s="72" t="n">
         <v>12</v>
@@ -11736,7 +12323,7 @@
         <v>102</v>
       </c>
       <c r="K49" s="12" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11752,7 +12339,7 @@
         <v>Ceiling fans</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="E50" s="72" t="n">
         <v>1</v>
@@ -11762,11 +12349,11 @@
       </c>
       <c r="G50" s="14" t="n">
         <f aca="false">WORKDAY(G48,E50,$M$6:$M$11)</f>
-        <v>46444</v>
+        <v>46454</v>
       </c>
       <c r="H50" s="14" t="n">
         <f aca="false">WORKDAY(G50,F50-1,$M$6:$M$11)</f>
-        <v>46447</v>
+        <v>46455</v>
       </c>
       <c r="I50" s="72" t="n">
         <v>12</v>
@@ -11775,7 +12362,7 @@
         <v>102</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11791,7 +12378,7 @@
         <v>Dining fixture (kitchen chandelier)</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="E51" s="72" t="n">
         <v>2</v>
@@ -11801,11 +12388,11 @@
       </c>
       <c r="G51" s="14" t="n">
         <f aca="false">WORKDAY(G48,E51,$M$6:$M$11)</f>
-        <v>46447</v>
+        <v>46455</v>
       </c>
       <c r="H51" s="14" t="n">
         <f aca="false">WORKDAY(G51,F51-1,$M$6:$M$11)</f>
-        <v>46447</v>
+        <v>46455</v>
       </c>
       <c r="I51" s="72" t="n">
         <v>3</v>
@@ -11814,7 +12401,7 @@
         <v>102</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11830,7 +12417,7 @@
         <v>LED mirrors - install</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="E52" s="72" t="n">
         <v>0</v>
@@ -11840,11 +12427,11 @@
       </c>
       <c r="G52" s="14" t="n">
         <f aca="false">WORKDAY(H48,1+E52,$M$6:$M$11)</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="H52" s="14" t="n">
         <f aca="false">WORKDAY(G52,F52-1,$M$6:$M$11)</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="I52" s="72" t="n">
         <v>4</v>
@@ -11853,7 +12440,7 @@
         <v>92</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11869,7 +12456,7 @@
         <v>Smoke / CO detectors - replace all</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="E53" s="72" t="n">
         <v>0</v>
@@ -11879,11 +12466,11 @@
       </c>
       <c r="G53" s="14" t="n">
         <f aca="false">WORKDAY(H48,1+E53,$M$6:$M$11)</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="H53" s="14" t="n">
         <f aca="false">WORKDAY(G53,F53-1,$M$6:$M$11)</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="I53" s="72" t="n">
         <v>4</v>
@@ -11892,7 +12479,7 @@
         <v>158</v>
       </c>
       <c r="K53" s="12" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11908,7 +12495,7 @@
         <v>Doorbell / smart doorbell</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="E54" s="72" t="n">
         <v>0</v>
@@ -11918,11 +12505,11 @@
       </c>
       <c r="G54" s="14" t="n">
         <f aca="false">WORKDAY(H48,1+E54,$M$6:$M$11)</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="H54" s="14" t="n">
         <f aca="false">WORKDAY(G54,F54-1,$M$6:$M$11)</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="I54" s="72" t="n">
         <v>2</v>
@@ -11931,7 +12518,7 @@
         <v>102</v>
       </c>
       <c r="K54" s="12" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11947,14 +12534,14 @@
         <v>Electrical contract - overall</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="E55" s="72" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="69" t="n">
         <f aca="false">NETWORKDAYS(G55,H55,$M$6:$M$11)</f>
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G55" s="14" t="n">
         <f aca="false">G45</f>
@@ -11962,7 +12549,7 @@
       </c>
       <c r="H55" s="14" t="n">
         <f aca="false">MAX(H46,H47,H48,H49,H50,H51,H52,H53,H54)</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="I55" s="69" t="s">
         <v>31</v>
@@ -11971,7 +12558,7 @@
         <v>102</v>
       </c>
       <c r="K55" s="12" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12002,7 +12589,7 @@
         <v>Underground DWV rough-in (baths/kitchen) incl. P-traps + underground inspection PASS</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="E57" s="72" t="n">
         <v>0</v>
@@ -12025,7 +12612,7 @@
         <v>92</v>
       </c>
       <c r="K57" s="12" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12041,7 +12628,7 @@
         <v>Water supply rough-in / top-out (shower valves, toilets, kitchen, fridge line) + pressure test</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="E58" s="72" t="n">
         <v>0</v>
@@ -12064,7 +12651,7 @@
         <v>92</v>
       </c>
       <c r="K58" s="12" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12080,7 +12667,7 @@
         <v>Plumbing inventory check - supply lines, drainage, P-traps</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="E59" s="72" t="n">
         <v>0</v>
@@ -12103,7 +12690,7 @@
         <v>92</v>
       </c>
       <c r="K59" s="12" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12119,7 +12706,7 @@
         <v>Final plumbing completion labor</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="E60" s="72" t="n">
         <v>0</v>
@@ -12129,11 +12716,11 @@
       </c>
       <c r="G60" s="14" t="n">
         <f aca="false">WORKDAY(H43,1+E60,$M$6:$M$11)</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="H60" s="14" t="n">
         <f aca="false">WORKDAY(G60,F60-1,$M$6:$M$11)</f>
-        <v>46447</v>
+        <v>46455</v>
       </c>
       <c r="I60" s="72" t="n">
         <v>24</v>
@@ -12142,7 +12729,7 @@
         <v>92</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12158,7 +12745,7 @@
         <v>Angle stops and supply lines throughout</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="E61" s="72" t="n">
         <v>0</v>
@@ -12168,11 +12755,11 @@
       </c>
       <c r="G61" s="14" t="n">
         <f aca="false">WORKDAY(G60,E61,$M$6:$M$11)</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="H61" s="14" t="n">
         <f aca="false">WORKDAY(G61,F61-1,$M$6:$M$11)</f>
-        <v>46444</v>
+        <v>46454</v>
       </c>
       <c r="I61" s="72" t="n">
         <v>8</v>
@@ -12181,7 +12768,7 @@
         <v>92</v>
       </c>
       <c r="K61" s="12" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12212,7 +12799,7 @@
         <v>Duct modifications - removed partitions, kitchen hood + bath exhaust ducting</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E63" s="72" t="n">
         <v>0</v>
@@ -12235,7 +12822,7 @@
         <v>102</v>
       </c>
       <c r="K63" s="12" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12251,7 +12838,7 @@
         <v>Ductwork inspection / repair / clean</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E64" s="72" t="n">
         <v>0</v>
@@ -12274,7 +12861,7 @@
         <v>102</v>
       </c>
       <c r="K64" s="12" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12290,7 +12877,7 @@
         <v>HVAC coil cleaning</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="E65" s="72" t="n">
         <v>0</v>
@@ -12313,7 +12900,7 @@
         <v>102</v>
       </c>
       <c r="K65" s="12" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12329,7 +12916,7 @@
         <v>HVAC coolant refill service</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="E66" s="72" t="n">
         <v>0</v>
@@ -12352,7 +12939,7 @@
         <v>102</v>
       </c>
       <c r="K66" s="12" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12368,7 +12955,7 @@
         <v>AC diffusers</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="E67" s="72" t="n">
         <v>0</v>
@@ -12378,11 +12965,11 @@
       </c>
       <c r="G67" s="14" t="n">
         <f aca="false">WORKDAY(H43,1+E67,$M$6:$M$11)</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="H67" s="14" t="n">
         <f aca="false">WORKDAY(G67,F67-1,$M$6:$M$11)</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="I67" s="72" t="n">
         <v>4</v>
@@ -12391,7 +12978,7 @@
         <v>53</v>
       </c>
       <c r="K67" s="12" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12407,7 +12994,7 @@
         <v>Thermostat</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="E68" s="72" t="n">
         <v>0</v>
@@ -12417,11 +13004,11 @@
       </c>
       <c r="G68" s="14" t="n">
         <f aca="false">WORKDAY(H43,1+E68,$M$6:$M$11)</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="H68" s="14" t="n">
         <f aca="false">WORKDAY(G68,F68-1,$M$6:$M$11)</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="I68" s="72" t="n">
         <v>2</v>
@@ -12430,7 +13017,7 @@
         <v>92</v>
       </c>
       <c r="K68" s="12" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12446,7 +13033,7 @@
         <v>HVAC maintenance + concrete slab repair</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="E69" s="72" t="n">
         <v>0</v>
@@ -12470,7 +13057,7 @@
         <v>99</v>
       </c>
       <c r="K69" s="12" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12501,7 +13088,7 @@
         <v>Cabinet order - field-verify dimensions, PO + fabrication (3-4 wk)</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="E71" s="72" t="n">
         <v>0</v>
@@ -12524,7 +13111,7 @@
         <v>53</v>
       </c>
       <c r="K71" s="12" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12540,7 +13127,7 @@
         <v>Kitchen cabinets + bathroom vanities (combined contract)</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="E72" s="72" t="n">
         <v>0</v>
@@ -12563,7 +13150,7 @@
         <v>71</v>
       </c>
       <c r="K72" s="12" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12579,7 +13166,7 @@
         <v>Stone countertops + backsplash (kitchen + baths)</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="E73" s="72" t="n">
         <v>0</v>
@@ -12602,7 +13189,7 @@
         <v>211</v>
       </c>
       <c r="K73" s="12" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12618,7 +13205,7 @@
         <v>Kitchen sink - purchase</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="E74" s="72" t="n">
         <v>5</v>
@@ -12641,7 +13228,7 @@
         <v>53</v>
       </c>
       <c r="K74" s="12" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12657,7 +13244,7 @@
         <v>Kitchen faucet</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E75" s="72" t="n">
         <v>5</v>
@@ -12680,7 +13267,7 @@
         <v>158</v>
       </c>
       <c r="K75" s="12" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12696,7 +13283,7 @@
         <v>Appliance package - purchase, transport, install</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="E76" s="72" t="n">
         <v>5</v>
@@ -12719,7 +13306,7 @@
         <v>53</v>
       </c>
       <c r="K76" s="12" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12735,7 +13322,7 @@
         <v>Appliance install + hook-ups (oven, cooktop, DW, disposal, hood, fridge line)</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="E77" s="72" t="n">
         <v>0</v>
@@ -12745,11 +13332,11 @@
       </c>
       <c r="G77" s="14" t="n">
         <f aca="false">WORKDAY(MAX(H73,H48,H60),1+E77,$M$6:$M$11)</f>
-        <v>46448</v>
+        <v>46456</v>
       </c>
       <c r="H77" s="14" t="n">
         <f aca="false">WORKDAY(G77,F77-1,$M$6:$M$11)</f>
-        <v>46449</v>
+        <v>46457</v>
       </c>
       <c r="I77" s="72" t="n">
         <v>12</v>
@@ -12758,7 +13345,7 @@
         <v>92</v>
       </c>
       <c r="K77" s="12" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12774,7 +13361,7 @@
         <v>Under-cabinet lighting</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="E78" s="72" t="n">
         <v>0</v>
@@ -12784,11 +13371,11 @@
       </c>
       <c r="G78" s="14" t="n">
         <f aca="false">WORKDAY(G48,E78,$M$6:$M$11)</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="H78" s="14" t="n">
         <f aca="false">WORKDAY(G78,F78-1,$M$6:$M$11)</f>
-        <v>46443</v>
+        <v>46451</v>
       </c>
       <c r="I78" s="72" t="n">
         <v>4</v>
@@ -12797,156 +13384,1557 @@
         <v>53</v>
       </c>
       <c r="K78" s="12" t="s">
-        <v>577</v>
-      </c>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="B79" s="66"/>
+      <c r="C79" s="66"/>
+      <c r="D79" s="66"/>
+      <c r="E79" s="66"/>
+      <c r="F79" s="66"/>
+      <c r="G79" s="66"/>
+      <c r="H79" s="66"/>
+      <c r="I79" s="66"/>
+      <c r="J79" s="66"/>
+      <c r="K79" s="66"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C80" s="4" t="s">
-        <v>578</v>
+      <c r="A80" s="69" t="n">
+        <v>86</v>
+      </c>
+      <c r="B80" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A86="","-",'Scope Checklist'!A86)</f>
+        <v>94</v>
+      </c>
+      <c r="C80" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D86</f>
+        <v>Shower drains - select + purchase (BOTH baths)</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="E80" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" s="14" t="n">
+        <f aca="false">WORKDAY(H11,1+E80,$M$6:$M$11)</f>
+        <v>46335</v>
+      </c>
+      <c r="H80" s="14" t="n">
+        <f aca="false">WORKDAY(G80,F80-1,$M$6:$M$11)</f>
+        <v>46342</v>
+      </c>
+      <c r="I80" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="K80" s="12" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C81" s="80" t="s">
-        <v>579</v>
-      </c>
-      <c r="H81" s="81" t="n">
+      <c r="A81" s="69" t="n">
+        <v>87</v>
+      </c>
+      <c r="B81" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A87="","-",'Scope Checklist'!A87)</f>
+        <v>88</v>
+      </c>
+      <c r="C81" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D87</f>
+        <v>Sink selection - double sinks</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="E81" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G81" s="14" t="n">
+        <f aca="false">WORKDAY(G71,E81,$M$6:$M$11)</f>
+        <v>46387</v>
+      </c>
+      <c r="H81" s="14" t="n">
+        <f aca="false">WORKDAY(G81,F81-1,$M$6:$M$11)</f>
+        <v>46394</v>
+      </c>
+      <c r="I81" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J81" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="K81" s="12" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="69" t="n">
+        <v>88</v>
+      </c>
+      <c r="B82" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A88="","-",'Scope Checklist'!A88)</f>
+        <v>95</v>
+      </c>
+      <c r="C82" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D88</f>
+        <v>Shower prep - confirm metal frame distance + shower door frame support (BOTH baths)</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="E82" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="14" t="n">
+        <f aca="false">WORKDAY(H35,1+E82,$M$6:$M$11)</f>
+        <v>46378</v>
+      </c>
+      <c r="H82" s="14" t="n">
+        <f aca="false">WORKDAY(G82,F82-1,$M$6:$M$11)</f>
+        <v>46378</v>
+      </c>
+      <c r="I82" s="72" t="n">
+        <v>8</v>
+      </c>
+      <c r="J82" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K82" s="12" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="69" t="n">
+        <v>89</v>
+      </c>
+      <c r="B83" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A89="","-",'Scope Checklist'!A89)</f>
+        <v>92</v>
+      </c>
+      <c r="C83" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D89</f>
+        <v>Tub install</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="E83" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="14" t="n">
+        <f aca="false">WORKDAY(H38,1+E83,$M$6:$M$11)</f>
+        <v>46395</v>
+      </c>
+      <c r="H83" s="14" t="n">
+        <f aca="false">WORKDAY(G83,F83-1,$M$6:$M$11)</f>
+        <v>46395</v>
+      </c>
+      <c r="I83" s="72" t="n">
+        <v>8</v>
+      </c>
+      <c r="J83" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K83" s="12" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="69" t="n">
+        <v>90</v>
+      </c>
+      <c r="B84" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A90="","-",'Scope Checklist'!A90)</f>
+        <v>97</v>
+      </c>
+      <c r="C84" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D90</f>
+        <v>Pan liner install + inspection pass</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="E84" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" s="14" t="n">
+        <f aca="false">WORKDAY(MAX(H40,H80),1+E84,$M$6:$M$11)</f>
+        <v>46409</v>
+      </c>
+      <c r="H84" s="14" t="n">
+        <f aca="false">WORKDAY(G84,F84-1,$M$6:$M$11)</f>
+        <v>46413</v>
+      </c>
+      <c r="I84" s="72" t="n">
+        <v>16</v>
+      </c>
+      <c r="J84" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K84" s="12" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="69" t="n">
+        <v>91</v>
+      </c>
+      <c r="B85" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A91="","-",'Scope Checklist'!A91)</f>
+        <v>96</v>
+      </c>
+      <c r="C85" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D91</f>
+        <v>Durock + waterproofing install</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>594</v>
+      </c>
+      <c r="E85" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="G85" s="14" t="n">
+        <f aca="false">WORKDAY(H84,1+E85,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="H85" s="14" t="n">
+        <f aca="false">WORKDAY(G85,F85-1,$M$6:$M$11)</f>
+        <v>46419</v>
+      </c>
+      <c r="I85" s="72" t="n">
+        <v>24</v>
+      </c>
+      <c r="J85" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K85" s="12" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="69" t="n">
+        <v>92</v>
+      </c>
+      <c r="B86" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A92="","-",'Scope Checklist'!A92)</f>
+        <v>93</v>
+      </c>
+      <c r="C86" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D92</f>
+        <v>LED niche</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="E86" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="14" t="n">
+        <f aca="false">WORKDAY(G85,E86,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="H86" s="14" t="n">
+        <f aca="false">WORKDAY(G86,F86-1,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="I86" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K86" s="12" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="69" t="n">
+        <v>93</v>
+      </c>
+      <c r="B87" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A93="","-",'Scope Checklist'!A93)</f>
+        <v>99</v>
+      </c>
+      <c r="C87" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D93</f>
+        <v>Metal trim (edge profile) - verify availability</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="E87" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="14" t="n">
+        <f aca="false">WORKDAY(G84,E87,$M$6:$M$11)</f>
+        <v>46409</v>
+      </c>
+      <c r="H87" s="14" t="n">
+        <f aca="false">WORKDAY(G87,F87-1,$M$6:$M$11)</f>
+        <v>46409</v>
+      </c>
+      <c r="I87" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K87" s="12" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="69" t="n">
+        <v>94</v>
+      </c>
+      <c r="B88" s="70" t="str">
+        <f aca="false">IF('Scope Checklist'!A94="","-",'Scope Checklist'!A94)</f>
+        <v>N13</v>
+      </c>
+      <c r="C88" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D94</f>
+        <v>Shower waterproofing inspection PASS - both baths (gate for tile)</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E88" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="14" t="n">
+        <f aca="false">WORKDAY(MAX(H85,H103),1+E88,$M$6:$M$11)</f>
+        <v>46420</v>
+      </c>
+      <c r="H88" s="14" t="n">
+        <f aca="false">WORKDAY(G88,F88-1,$M$6:$M$11)</f>
+        <v>46420</v>
+      </c>
+      <c r="I88" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J88" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="K88" s="12" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="69" t="n">
+        <v>95</v>
+      </c>
+      <c r="B89" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A95="","-",'Scope Checklist'!A95)</f>
+        <v>98</v>
+      </c>
+      <c r="C89" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D95</f>
+        <v>Bathroom tile installation - labor (BOTH baths)</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="E89" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="72" t="n">
+        <v>10</v>
+      </c>
+      <c r="G89" s="14" t="n">
+        <f aca="false">WORKDAY(MAX(H88,H83,H87,H105,H86,H104),1+E89,$M$6:$M$11)</f>
+        <v>46421</v>
+      </c>
+      <c r="H89" s="14" t="n">
+        <f aca="false">WORKDAY(G89,F89-1,$M$6:$M$11)</f>
+        <v>46434</v>
+      </c>
+      <c r="I89" s="72" t="n">
+        <v>80</v>
+      </c>
+      <c r="J89" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="K89" s="12" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="69" t="n">
+        <v>96</v>
+      </c>
+      <c r="B90" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A96="","-",'Scope Checklist'!A96)</f>
+        <v>102</v>
+      </c>
+      <c r="C90" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D96</f>
+        <v>Paint all walls</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="E90" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="14" t="n">
+        <f aca="false">WORKDAY(H89,1+E90,$M$6:$M$11)</f>
+        <v>46435</v>
+      </c>
+      <c r="H90" s="14" t="n">
+        <f aca="false">WORKDAY(G90,F90-1,$M$6:$M$11)</f>
+        <v>46436</v>
+      </c>
+      <c r="I90" s="72" t="n">
+        <v>12</v>
+      </c>
+      <c r="J90" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="K90" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="69" t="n">
+        <v>97</v>
+      </c>
+      <c r="B91" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A97="","-",'Scope Checklist'!A97)</f>
+        <v>103</v>
+      </c>
+      <c r="C91" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D97</f>
+        <v>Pocket door - verify function + paint</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="E91" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="14" t="n">
+        <f aca="false">WORKDAY(G90,E91,$M$6:$M$11)</f>
+        <v>46435</v>
+      </c>
+      <c r="H91" s="14" t="n">
+        <f aca="false">WORKDAY(G91,F91-1,$M$6:$M$11)</f>
+        <v>46435</v>
+      </c>
+      <c r="I91" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J91" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="K91" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="69" t="n">
+        <v>98</v>
+      </c>
+      <c r="B92" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A98="","-",'Scope Checklist'!A98)</f>
+        <v>87</v>
+      </c>
+      <c r="C92" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D98</f>
+        <v>Vanity cabinetry - confirm quality</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="E92" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="14" t="n">
+        <f aca="false">WORKDAY(MAX(H90,H72),1+E92,$M$6:$M$11)</f>
+        <v>46437</v>
+      </c>
+      <c r="H92" s="14" t="n">
+        <f aca="false">WORKDAY(G92,F92-1,$M$6:$M$11)</f>
+        <v>46437</v>
+      </c>
+      <c r="I92" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J92" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="K92" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="69" t="n">
+        <v>99</v>
+      </c>
+      <c r="B93" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A99="","-",'Scope Checklist'!A99)</f>
+        <v>89</v>
+      </c>
+      <c r="C93" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D99</f>
+        <v>Vanity stone top - select (~11 sq ft)</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="E93" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="72" t="n">
+        <v>8</v>
+      </c>
+      <c r="G93" s="14" t="n">
+        <f aca="false">WORKDAY(H92,1+E93,$M$6:$M$11)</f>
+        <v>46440</v>
+      </c>
+      <c r="H93" s="14" t="n">
+        <f aca="false">WORKDAY(G93,F93-1,$M$6:$M$11)</f>
+        <v>46449</v>
+      </c>
+      <c r="I93" s="72" t="n">
+        <v>6</v>
+      </c>
+      <c r="J93" s="69" t="s">
+        <v>211</v>
+      </c>
+      <c r="K93" s="12" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="69" t="n">
+        <v>100</v>
+      </c>
+      <c r="B94" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A100="","-",'Scope Checklist'!A100)</f>
+        <v>100</v>
+      </c>
+      <c r="C94" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D100</f>
+        <v>Threshold + bench top</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="E94" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="72" t="n">
+        <v>8</v>
+      </c>
+      <c r="G94" s="14" t="n">
+        <f aca="false">WORKDAY(G93,E94,$M$6:$M$11)</f>
+        <v>46440</v>
+      </c>
+      <c r="H94" s="14" t="n">
+        <f aca="false">WORKDAY(G94,F94-1,$M$6:$M$11)</f>
+        <v>46449</v>
+      </c>
+      <c r="I94" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J94" s="69" t="s">
+        <v>267</v>
+      </c>
+      <c r="K94" s="12" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="69" t="n">
+        <v>101</v>
+      </c>
+      <c r="B95" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A101="","-",'Scope Checklist'!A101)</f>
+        <v>101</v>
+      </c>
+      <c r="C95" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D101</f>
+        <v>Glass shower enclosure - MASTER</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="E95" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="72" t="n">
+        <v>7</v>
+      </c>
+      <c r="G95" s="14" t="n">
+        <f aca="false">WORKDAY(H94,1+E95,$M$6:$M$11)</f>
+        <v>46450</v>
+      </c>
+      <c r="H95" s="14" t="n">
+        <f aca="false">WORKDAY(G95,F95-1,$M$6:$M$11)</f>
+        <v>46458</v>
+      </c>
+      <c r="I95" s="72" t="n">
+        <v>6</v>
+      </c>
+      <c r="J95" s="69" t="s">
+        <v>271</v>
+      </c>
+      <c r="K95" s="12" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="69" t="n">
+        <v>102</v>
+      </c>
+      <c r="B96" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A102="","-",'Scope Checklist'!A102)</f>
+        <v>90</v>
+      </c>
+      <c r="C96" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D102</f>
+        <v>Double faucets + double sinks - install</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="E96" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="14" t="n">
+        <f aca="false">WORKDAY(H93,1+E96,$M$6:$M$11)</f>
+        <v>46450</v>
+      </c>
+      <c r="H96" s="14" t="n">
+        <f aca="false">WORKDAY(G96,F96-1,$M$6:$M$11)</f>
+        <v>46450</v>
+      </c>
+      <c r="I96" s="72" t="n">
+        <v>6</v>
+      </c>
+      <c r="J96" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K96" s="12" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="69" t="n">
+        <v>103</v>
+      </c>
+      <c r="B97" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A103="","-",'Scope Checklist'!A103)</f>
+        <v>91</v>
+      </c>
+      <c r="C97" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D103</f>
+        <v>Toilet install + new wax ring</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="E97" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="14" t="n">
+        <f aca="false">WORKDAY(H90,1+E97,$M$6:$M$11)</f>
+        <v>46437</v>
+      </c>
+      <c r="H97" s="14" t="n">
+        <f aca="false">WORKDAY(G97,F97-1,$M$6:$M$11)</f>
+        <v>46437</v>
+      </c>
+      <c r="I97" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J97" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K97" s="12" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="69" t="n">
+        <v>104</v>
+      </c>
+      <c r="B98" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A104="","-",'Scope Checklist'!A104)</f>
+        <v>104</v>
+      </c>
+      <c r="C98" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D104</f>
+        <v>Bath hardware (towel bars, TP holder, etc.)</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="E98" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="14" t="n">
+        <f aca="false">WORKDAY(H43,1+E98,$M$6:$M$11)</f>
+        <v>46451</v>
+      </c>
+      <c r="H98" s="14" t="n">
+        <f aca="false">WORKDAY(G98,F98-1,$M$6:$M$11)</f>
+        <v>46451</v>
+      </c>
+      <c r="I98" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J98" s="69" t="s">
+        <v>282</v>
+      </c>
+      <c r="K98" s="12" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="69" t="n">
+        <v>105</v>
+      </c>
+      <c r="B99" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A105="","-",'Scope Checklist'!A105)</f>
+        <v>105</v>
+      </c>
+      <c r="C99" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D105</f>
+        <v>Exhaust fan</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="E99" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="14" t="n">
+        <f aca="false">WORKDAY(G48,E99,$M$6:$M$11)</f>
+        <v>46451</v>
+      </c>
+      <c r="H99" s="14" t="n">
+        <f aca="false">WORKDAY(G99,F99-1,$M$6:$M$11)</f>
+        <v>46451</v>
+      </c>
+      <c r="I99" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J99" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K99" s="12" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B100" s="66"/>
+      <c r="C100" s="66"/>
+      <c r="D100" s="66"/>
+      <c r="E100" s="66"/>
+      <c r="F100" s="66"/>
+      <c r="G100" s="66"/>
+      <c r="H100" s="66"/>
+      <c r="I100" s="66"/>
+      <c r="J100" s="66"/>
+      <c r="K100" s="66"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="69" t="n">
+        <v>108</v>
+      </c>
+      <c r="B101" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A108="","-",'Scope Checklist'!A108)</f>
+        <v>107</v>
+      </c>
+      <c r="C101" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D108</f>
+        <v>Sink selection - single sink</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="E101" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G101" s="14" t="n">
+        <f aca="false">WORKDAY(G71,E101,$M$6:$M$11)</f>
+        <v>46387</v>
+      </c>
+      <c r="H101" s="14" t="n">
+        <f aca="false">WORKDAY(G101,F101-1,$M$6:$M$11)</f>
+        <v>46394</v>
+      </c>
+      <c r="I101" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="K101" s="12" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="69" t="n">
+        <v>109</v>
+      </c>
+      <c r="B102" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A109="","-",'Scope Checklist'!A109)</f>
+        <v>113</v>
+      </c>
+      <c r="C102" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D109</f>
+        <v>Pan liner install + inspection pass</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="E102" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" s="14" t="n">
+        <f aca="false">WORKDAY(G84,E102,$M$6:$M$11)</f>
+        <v>46409</v>
+      </c>
+      <c r="H102" s="14" t="n">
+        <f aca="false">WORKDAY(G102,F102-1,$M$6:$M$11)</f>
+        <v>46413</v>
+      </c>
+      <c r="I102" s="72" t="n">
+        <v>16</v>
+      </c>
+      <c r="J102" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K102" s="12" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="69" t="n">
+        <v>110</v>
+      </c>
+      <c r="B103" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A110="","-",'Scope Checklist'!A110)</f>
+        <v>112</v>
+      </c>
+      <c r="C103" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D110</f>
+        <v>Durock + waterproofing install</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="E103" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="G103" s="14" t="n">
+        <f aca="false">WORKDAY(G85,E103,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="H103" s="14" t="n">
+        <f aca="false">WORKDAY(G103,F103-1,$M$6:$M$11)</f>
+        <v>46419</v>
+      </c>
+      <c r="I103" s="72" t="n">
+        <v>24</v>
+      </c>
+      <c r="J103" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K103" s="12" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="69" t="n">
+        <v>111</v>
+      </c>
+      <c r="B104" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A111="","-",'Scope Checklist'!A111)</f>
+        <v>111</v>
+      </c>
+      <c r="C104" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D111</f>
+        <v>LED niche</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="E104" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="14" t="n">
+        <f aca="false">WORKDAY(G103,E104,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="H104" s="14" t="n">
+        <f aca="false">WORKDAY(G104,F104-1,$M$6:$M$11)</f>
+        <v>46414</v>
+      </c>
+      <c r="I104" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J104" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K104" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="69" t="n">
+        <v>112</v>
+      </c>
+      <c r="B105" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A112="","-",'Scope Checklist'!A112)</f>
+        <v>115</v>
+      </c>
+      <c r="C105" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D112</f>
+        <v>Metal trim (edge profile) - verify availability</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="E105" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <f aca="false">WORKDAY(G102,E105,$M$6:$M$11)</f>
+        <v>46409</v>
+      </c>
+      <c r="H105" s="14" t="n">
+        <f aca="false">WORKDAY(G105,F105-1,$M$6:$M$11)</f>
+        <v>46409</v>
+      </c>
+      <c r="I105" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K105" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="69" t="n">
+        <v>113</v>
+      </c>
+      <c r="B106" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A113="","-",'Scope Checklist'!A113)</f>
+        <v>114</v>
+      </c>
+      <c r="C106" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D113</f>
+        <v>Shower tile install</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="E106" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F106" s="72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G106" s="14" t="n">
+        <f aca="false">WORKDAY(G89,E106,$M$6:$M$11)</f>
+        <v>46428</v>
+      </c>
+      <c r="H106" s="14" t="n">
+        <f aca="false">WORKDAY(G106,F106-1,$M$6:$M$11)</f>
+        <v>46434</v>
+      </c>
+      <c r="I106" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="J106" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="K106" s="12" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="69" t="n">
+        <v>114</v>
+      </c>
+      <c r="B107" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A114="","-",'Scope Checklist'!A114)</f>
+        <v>118</v>
+      </c>
+      <c r="C107" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D114</f>
+        <v>Pocket door - verify function + paint</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="E107" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="14" t="n">
+        <f aca="false">WORKDAY(G90,E107,$M$6:$M$11)</f>
+        <v>46435</v>
+      </c>
+      <c r="H107" s="14" t="n">
+        <f aca="false">WORKDAY(G107,F107-1,$M$6:$M$11)</f>
+        <v>46435</v>
+      </c>
+      <c r="I107" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J107" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="K107" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="69" t="n">
+        <v>115</v>
+      </c>
+      <c r="B108" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A115="","-",'Scope Checklist'!A115)</f>
+        <v>106</v>
+      </c>
+      <c r="C108" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D115</f>
+        <v>Vanity cabinetry - confirm quality</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="E108" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="14" t="n">
+        <f aca="false">WORKDAY(G92,E108,$M$6:$M$11)</f>
+        <v>46437</v>
+      </c>
+      <c r="H108" s="14" t="n">
+        <f aca="false">WORKDAY(G108,F108-1,$M$6:$M$11)</f>
+        <v>46437</v>
+      </c>
+      <c r="I108" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J108" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="K108" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="69" t="n">
+        <v>116</v>
+      </c>
+      <c r="B109" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A116="","-",'Scope Checklist'!A116)</f>
+        <v>108</v>
+      </c>
+      <c r="C109" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D116</f>
+        <v>Vanity stone top - select (~8 sq ft)</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="E109" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="72" t="n">
+        <v>8</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <f aca="false">WORKDAY(G93,E109,$M$6:$M$11)</f>
+        <v>46440</v>
+      </c>
+      <c r="H109" s="14" t="n">
+        <f aca="false">WORKDAY(G109,F109-1,$M$6:$M$11)</f>
+        <v>46449</v>
+      </c>
+      <c r="I109" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J109" s="69" t="s">
+        <v>211</v>
+      </c>
+      <c r="K109" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="69" t="n">
+        <v>117</v>
+      </c>
+      <c r="B110" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A117="","-",'Scope Checklist'!A117)</f>
+        <v>116</v>
+      </c>
+      <c r="C110" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D117</f>
+        <v>Threshold + bench top</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="E110" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="72" t="n">
+        <v>8</v>
+      </c>
+      <c r="G110" s="14" t="n">
+        <f aca="false">WORKDAY(G94,E110,$M$6:$M$11)</f>
+        <v>46440</v>
+      </c>
+      <c r="H110" s="14" t="n">
+        <f aca="false">WORKDAY(G110,F110-1,$M$6:$M$11)</f>
+        <v>46449</v>
+      </c>
+      <c r="I110" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J110" s="69" t="s">
+        <v>267</v>
+      </c>
+      <c r="K110" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="69" t="n">
+        <v>118</v>
+      </c>
+      <c r="B111" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A118="","-",'Scope Checklist'!A118)</f>
+        <v>117</v>
+      </c>
+      <c r="C111" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D118</f>
+        <v>Glass shower enclosure</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="E111" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <f aca="false">WORKDAY(H110,1+E111,$M$6:$M$11)</f>
+        <v>46450</v>
+      </c>
+      <c r="H111" s="14" t="n">
+        <f aca="false">WORKDAY(G111,F111-1,$M$6:$M$11)</f>
+        <v>46451</v>
+      </c>
+      <c r="I111" s="72" t="n">
+        <v>8</v>
+      </c>
+      <c r="J111" s="69" t="s">
+        <v>296</v>
+      </c>
+      <c r="K111" s="12" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="69" t="n">
+        <v>119</v>
+      </c>
+      <c r="B112" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A119="","-",'Scope Checklist'!A119)</f>
+        <v>109</v>
+      </c>
+      <c r="C112" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D119</f>
+        <v>Faucet + sink - install</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="E112" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="14" t="n">
+        <f aca="false">WORKDAY(H109,1+E112,$M$6:$M$11)</f>
+        <v>46450</v>
+      </c>
+      <c r="H112" s="14" t="n">
+        <f aca="false">WORKDAY(G112,F112-1,$M$6:$M$11)</f>
+        <v>46450</v>
+      </c>
+      <c r="I112" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J112" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K112" s="12" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="69" t="n">
+        <v>120</v>
+      </c>
+      <c r="B113" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A120="","-",'Scope Checklist'!A120)</f>
+        <v>110</v>
+      </c>
+      <c r="C113" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D120</f>
+        <v>Toilet install + new wax ring</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="E113" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <f aca="false">WORKDAY(H90,1+E113,$M$6:$M$11)</f>
+        <v>46437</v>
+      </c>
+      <c r="H113" s="14" t="n">
+        <f aca="false">WORKDAY(G113,F113-1,$M$6:$M$11)</f>
+        <v>46437</v>
+      </c>
+      <c r="I113" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J113" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K113" s="12" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="69" t="n">
+        <v>121</v>
+      </c>
+      <c r="B114" s="70" t="n">
+        <f aca="false">IF('Scope Checklist'!A121="","-",'Scope Checklist'!A121)</f>
+        <v>119</v>
+      </c>
+      <c r="C114" s="71" t="str">
+        <f aca="false">'Scope Checklist'!D121</f>
+        <v>Exhaust fan</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="E114" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="14" t="n">
+        <f aca="false">WORKDAY(G48,E114,$M$6:$M$11)</f>
+        <v>46451</v>
+      </c>
+      <c r="H114" s="14" t="n">
+        <f aca="false">WORKDAY(G114,F114-1,$M$6:$M$11)</f>
+        <v>46451</v>
+      </c>
+      <c r="I114" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J114" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="K114" s="12" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C116" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C117" s="80" t="s">
+        <v>633</v>
+      </c>
+      <c r="H117" s="81" t="n">
         <f aca="false">MAX(H21,H22,H23,H24)</f>
         <v>46370</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C82" s="80" t="s">
-        <v>580</v>
-      </c>
-      <c r="H82" s="81" t="n">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C118" s="80" t="s">
+        <v>634</v>
+      </c>
+      <c r="H118" s="81" t="n">
         <f aca="false">H38</f>
         <v>46394</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C83" s="80" t="s">
-        <v>581</v>
-      </c>
-      <c r="H83" s="81" t="n">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C119" s="80" t="s">
+        <v>635</v>
+      </c>
+      <c r="H119" s="81" t="n">
         <f aca="false">H41</f>
         <v>46413</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C84" s="80" t="s">
-        <v>582</v>
-      </c>
-      <c r="H84" s="81" t="n">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C120" s="80" t="s">
+        <v>636</v>
+      </c>
+      <c r="H120" s="81" t="n">
         <f aca="false">H57</f>
         <v>46374</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C85" s="80" t="s">
-        <v>583</v>
-      </c>
-      <c r="H85" s="81" t="n">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C121" s="80" t="s">
+        <v>637</v>
+      </c>
+      <c r="H121" s="81" t="n">
         <f aca="false">H43</f>
-        <v>46442</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C86" s="80" t="s">
-        <v>584</v>
-      </c>
-      <c r="H86" s="81" t="n">
+        <v>46450</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C122" s="80" t="s">
+        <v>638</v>
+      </c>
+      <c r="H122" s="81" t="n">
         <f aca="false">H55</f>
-        <v>46448</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="80" t="s">
-        <v>585</v>
-      </c>
-      <c r="H87" s="81" t="n">
+        <v>46456</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C123" s="80" t="s">
+        <v>639</v>
+      </c>
+      <c r="H123" s="81" t="n">
         <f aca="false">MAX(H60,H61)</f>
-        <v>46447</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="80" t="s">
-        <v>586</v>
-      </c>
-      <c r="H88" s="81" t="n">
+        <v>46455</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C124" s="80" t="s">
+        <v>640</v>
+      </c>
+      <c r="H124" s="81" t="n">
         <f aca="false">MAX(H67,H68)</f>
-        <v>46443</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C89" s="80" t="s">
-        <v>587</v>
-      </c>
-      <c r="H89" s="81" t="n">
+        <v>46451</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C125" s="80" t="s">
+        <v>641</v>
+      </c>
+      <c r="H125" s="81" t="n">
         <f aca="false">H73</f>
         <v>46427</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C90" s="80" t="s">
-        <v>588</v>
-      </c>
-      <c r="H90" s="81" t="n">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C126" s="80" t="s">
+        <v>642</v>
+      </c>
+      <c r="H126" s="81" t="n">
         <f aca="false">MAX(H77,H78)</f>
-        <v>46449</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C91" s="80" t="s">
-        <v>589</v>
-      </c>
-      <c r="I91" s="82" t="n">
+        <v>46457</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C127" s="80" t="s">
+        <v>643</v>
+      </c>
+      <c r="H127" s="81" t="n">
+        <f aca="false">H88</f>
+        <v>46420</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C128" s="80" t="s">
+        <v>644</v>
+      </c>
+      <c r="H128" s="81" t="n">
+        <f aca="false">MAX(H89,H106)</f>
+        <v>46434</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C129" s="80" t="s">
+        <v>645</v>
+      </c>
+      <c r="H129" s="81" t="n">
+        <f aca="false">MAX(H95,H111,H96,H112,H98,H99,H114)</f>
+        <v>46458</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C130" s="80" t="s">
+        <v>646</v>
+      </c>
+      <c r="I130" s="82" t="n">
         <f aca="false">SUM(I7:I30)</f>
         <v>217</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C92" s="80" t="s">
-        <v>590</v>
-      </c>
-      <c r="I92" s="82" t="n">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C131" s="80" t="s">
+        <v>647</v>
+      </c>
+      <c r="I131" s="82" t="n">
         <f aca="false">SUM(I32:I41)</f>
         <v>360</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C93" s="80" t="s">
-        <v>591</v>
-      </c>
-      <c r="I93" s="82" t="n">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C132" s="80" t="s">
+        <v>648</v>
+      </c>
+      <c r="I132" s="82" t="n">
         <f aca="false">SUM(I45:I55)</f>
         <v>139</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C94" s="80" t="s">
-        <v>592</v>
-      </c>
-      <c r="I94" s="82" t="n">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C133" s="80" t="s">
+        <v>649</v>
+      </c>
+      <c r="I133" s="82" t="n">
         <f aca="false">SUM(I57:I61)</f>
         <v>94</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="80" t="s">
-        <v>593</v>
-      </c>
-      <c r="I95" s="82" t="n">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C134" s="80" t="s">
+        <v>650</v>
+      </c>
+      <c r="I134" s="82" t="n">
         <f aca="false">SUM(I63:I69)</f>
         <v>53</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C96" s="80" t="s">
-        <v>594</v>
-      </c>
-      <c r="I96" s="82" t="n">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C135" s="80" t="s">
+        <v>651</v>
+      </c>
+      <c r="I135" s="82" t="n">
         <f aca="false">SUM(I71:I78)</f>
         <v>71</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C136" s="80" t="s">
+        <v>652</v>
+      </c>
+      <c r="I136" s="82" t="n">
+        <f aca="false">SUM(I80:I99)</f>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C137" s="80" t="s">
+        <v>653</v>
+      </c>
+      <c r="I137" s="82" t="n">
+        <f aca="false">SUM(I101:I114)</f>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -12975,30 +14963,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="83" t="s">
-        <v>595</v>
+        <v>654</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>596</v>
+        <v>655</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="84" t="s">
-        <v>597</v>
+        <v>656</v>
       </c>
       <c r="B4" s="84"/>
       <c r="C4" s="84"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="85" t="s">
-        <v>598</v>
+        <v>657</v>
       </c>
       <c r="B5" s="85" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="85" t="s">
-        <v>599</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13009,7 +14997,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>600</v>
+        <v>659</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13020,7 +15008,7 @@
         <v>53</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>601</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13031,7 +15019,7 @@
         <v>53</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>602</v>
+        <v>661</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13042,7 +15030,7 @@
         <v>53</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>603</v>
+        <v>662</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13053,7 +15041,7 @@
         <v>71</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>604</v>
+        <v>663</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13064,18 +15052,18 @@
         <v>71</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>605</v>
+        <v>664</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="86" t="s">
-        <v>606</v>
+        <v>665</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>607</v>
+        <v>666</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13086,7 +15074,7 @@
         <v>92</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>608</v>
+        <v>667</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13094,10 +15082,10 @@
         <v>110</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>609</v>
+        <v>668</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>610</v>
+        <v>669</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13108,7 +15096,7 @@
         <v>71</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>611</v>
+        <v>670</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13119,7 +15107,7 @@
         <v>71</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>612</v>
+        <v>671</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13127,10 +15115,10 @@
         <v>210</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>613</v>
+        <v>672</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>614</v>
+        <v>673</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13138,10 +15126,10 @@
         <v>215</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>615</v>
+        <v>674</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13149,116 +15137,116 @@
         <v>157</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>616</v>
+        <v>675</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="86" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>617</v>
+        <v>676</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="86" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>618</v>
+        <v>677</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="86" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>619</v>
+        <v>678</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="86" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>620</v>
+        <v>679</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="86" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>621</v>
+        <v>680</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="86" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>622</v>
+        <v>681</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="86" t="s">
-        <v>623</v>
+        <v>682</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>102</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>624</v>
+        <v>683</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="87" t="s">
-        <v>625</v>
+        <v>684</v>
       </c>
       <c r="B28" s="87"/>
       <c r="C28" s="87"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="85" t="s">
-        <v>598</v>
+        <v>657</v>
       </c>
       <c r="B29" s="85" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="85" t="s">
-        <v>599</v>
+        <v>658</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="86" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>626</v>
+        <v>685</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13266,10 +15254,10 @@
         <v>131</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>627</v>
+        <v>686</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>628</v>
+        <v>687</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13280,172 +15268,172 @@
         <v>92</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>629</v>
+        <v>688</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="86" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>630</v>
+        <v>689</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>631</v>
+        <v>690</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="86" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>632</v>
+        <v>691</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>633</v>
+        <v>692</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="86" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>634</v>
+        <v>693</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="86" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>635</v>
+        <v>694</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="86" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>636</v>
+        <v>695</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="86" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>637</v>
+        <v>696</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>638</v>
+        <v>697</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="86" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>639</v>
+        <v>698</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="86" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>640</v>
+        <v>699</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="86" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>641</v>
+        <v>700</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="86" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="B42" s="18" t="s">
         <v>123</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>642</v>
+        <v>701</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="86" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="B43" s="18" t="s">
         <v>123</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>643</v>
+        <v>702</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="86" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>644</v>
+        <v>703</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="86" t="s">
-        <v>645</v>
+        <v>704</v>
       </c>
       <c r="B45" s="18" t="s">
         <v>211</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>646</v>
+        <v>705</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="86" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B46" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>647</v>
+        <v>706</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="86" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B47" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>648</v>
+        <v>707</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13456,80 +15444,80 @@
         <v>92</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>649</v>
+        <v>708</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="86" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>650</v>
+        <v>709</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>651</v>
+        <v>710</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="86" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>652</v>
+        <v>711</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="88" t="s">
-        <v>653</v>
+        <v>712</v>
       </c>
       <c r="B52" s="88"/>
       <c r="C52" s="88"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="85" t="s">
-        <v>598</v>
+        <v>657</v>
       </c>
       <c r="B53" s="85" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="85" t="s">
-        <v>599</v>
+        <v>658</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="86" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>654</v>
+        <v>713</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="86" t="s">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="B55" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>655</v>
+        <v>714</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="86" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>656</v>
+        <v>715</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>657</v>
+        <v>716</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13540,144 +15528,144 @@
         <v>92</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>658</v>
+        <v>717</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="86" t="s">
-        <v>659</v>
+        <v>718</v>
       </c>
       <c r="B58" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>660</v>
+        <v>719</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="86" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B59" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>661</v>
+        <v>720</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="86" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>662</v>
+        <v>721</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="86" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>663</v>
+        <v>722</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="86" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>664</v>
+        <v>723</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="86" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B63" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>665</v>
+        <v>724</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="86" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>666</v>
+        <v>725</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="86" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>650</v>
+        <v>709</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>667</v>
+        <v>726</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="86" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B66" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="86" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>650</v>
+        <v>709</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="86" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>650</v>
+        <v>709</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>668</v>
+        <v>727</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="86" t="s">
-        <v>669</v>
+        <v>728</v>
       </c>
       <c r="B69" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>670</v>
+        <v>729</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="89" t="s">
-        <v>671</v>
+        <v>730</v>
       </c>
       <c r="B71" s="89"/>
       <c r="C71" s="89"/>
@@ -13718,12 +15706,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="90" t="s">
-        <v>672</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>673</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13731,30 +15719,30 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>674</v>
+        <v>733</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>675</v>
+        <v>734</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>676</v>
+        <v>735</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>677</v>
+        <v>736</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>678</v>
+        <v>737</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>679</v>
+        <v>738</v>
       </c>
       <c r="C5" s="19" t="n">
         <v>30297</v>
@@ -13764,18 +15752,18 @@
         <v>0</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>680</v>
+        <v>739</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>681</v>
+        <v>740</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>682</v>
+        <v>741</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>683</v>
+        <v>742</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>19825.36</v>
@@ -13787,18 +15775,18 @@
         <v>0</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>680</v>
+        <v>739</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>684</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>685</v>
+        <v>744</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>686</v>
+        <v>745</v>
       </c>
       <c r="C7" s="19" t="n">
         <v>14000</v>
@@ -13810,10 +15798,10 @@
         <v>7000</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>680</v>
+        <v>739</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>687</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13821,7 +15809,7 @@
         <v>68</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>688</v>
+        <v>747</v>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="25" t="n">
@@ -13831,18 +15819,18 @@
         <v>1500</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>680</v>
+        <v>739</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>689</v>
+        <v>748</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>690</v>
+        <v>749</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>691</v>
+        <v>750</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19" t="n">
@@ -13852,18 +15840,18 @@
         <v>3500</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>693</v>
+        <v>752</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>694</v>
+        <v>753</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>695</v>
+        <v>754</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>3000</v>
@@ -13875,10 +15863,10 @@
         <v>3000</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>696</v>
+        <v>755</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13886,7 +15874,7 @@
         <v>201</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>697</v>
+        <v>756</v>
       </c>
       <c r="C11" s="19" t="n">
         <v>21750</v>
@@ -13898,10 +15886,10 @@
         <v>4875</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>698</v>
+        <v>757</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13909,7 +15897,7 @@
         <v>208</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>699</v>
+        <v>758</v>
       </c>
       <c r="C12" s="25" t="n">
         <v>5925</v>
@@ -13921,18 +15909,18 @@
         <v>4500</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>700</v>
+        <v>759</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>701</v>
+        <v>760</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>702</v>
+        <v>761</v>
       </c>
       <c r="C13" s="19" t="n">
         <v>9100</v>
@@ -13944,18 +15932,18 @@
         <v>9100</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>703</v>
+        <v>762</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>704</v>
+        <v>763</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>705</v>
+        <v>764</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="25" t="n">
@@ -13965,18 +15953,18 @@
         <v>500</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>706</v>
+        <v>765</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>704</v>
+        <v>763</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>707</v>
+        <v>766</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19" t="n">
@@ -13986,18 +15974,18 @@
         <v>2500</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>650</v>
+        <v>709</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>704</v>
+        <v>763</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>708</v>
+        <v>767</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25" t="n">
@@ -14005,18 +15993,18 @@
       </c>
       <c r="E16" s="25"/>
       <c r="F16" s="22" t="s">
-        <v>709</v>
+        <v>768</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>710</v>
+        <v>769</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>704</v>
+        <v>763</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>711</v>
+        <v>770</v>
       </c>
       <c r="C17" s="19"/>
       <c r="D17" s="19" t="n">
@@ -14024,18 +16012,18 @@
       </c>
       <c r="E17" s="19"/>
       <c r="F17" s="12" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>650</v>
+        <v>709</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>704</v>
+        <v>763</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>712</v>
+        <v>771</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25" t="n">
@@ -14043,18 +16031,18 @@
       </c>
       <c r="E18" s="25"/>
       <c r="F18" s="22" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>650</v>
+        <v>709</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>713</v>
+        <v>772</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>714</v>
+        <v>773</v>
       </c>
       <c r="C19" s="19" t="n">
         <v>10000</v>
@@ -14066,18 +16054,18 @@
         <v>10000</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>715</v>
+        <v>774</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>716</v>
+        <v>775</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>717</v>
+        <v>776</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>718</v>
+        <v>777</v>
       </c>
       <c r="C20" s="25" t="n">
         <v>3000</v>
@@ -14089,18 +16077,18 @@
         <v>3000</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>715</v>
+        <v>774</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>719</v>
+        <v>778</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>720</v>
+        <v>779</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>721</v>
+        <v>780</v>
       </c>
       <c r="C21" s="19" t="n">
         <v>2000</v>
@@ -14112,18 +16100,18 @@
         <v>1500</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>650</v>
+        <v>709</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>722</v>
+        <v>781</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>723</v>
+        <v>782</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>724</v>
+        <v>783</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="25" t="n">
@@ -14131,18 +16119,18 @@
       </c>
       <c r="E22" s="25"/>
       <c r="F22" s="22" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>725</v>
+        <v>784</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>726</v>
+        <v>785</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>727</v>
+        <v>786</v>
       </c>
       <c r="C23" s="19" t="n">
         <v>2100</v>
@@ -14154,18 +16142,18 @@
         <v>2000</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>728</v>
+        <v>787</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>729</v>
+        <v>788</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>730</v>
+        <v>789</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>731</v>
+        <v>790</v>
       </c>
       <c r="C24" s="25" t="n">
         <v>7500</v>
@@ -14177,16 +16165,16 @@
         <v>4500</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>715</v>
+        <v>774</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>732</v>
+        <v>791</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="58"/>
       <c r="B25" s="59" t="s">
-        <v>733</v>
+        <v>792</v>
       </c>
       <c r="C25" s="58"/>
       <c r="D25" s="58"/>
@@ -14199,29 +16187,29 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>734</v>
+        <v>793</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="92" t="s">
-        <v>735</v>
+        <v>794</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="93"/>
       <c r="B29" s="93" t="s">
-        <v>736</v>
+        <v>795</v>
       </c>
       <c r="C29" s="93" t="s">
-        <v>737</v>
+        <v>796</v>
       </c>
       <c r="D29" s="93" t="s">
-        <v>738</v>
+        <v>797</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>739</v>
+        <v>798</v>
       </c>
       <c r="B30" s="94" t="n">
         <v>107414.33</v>
@@ -14236,7 +16224,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>740</v>
+        <v>799</v>
       </c>
       <c r="B31" s="94" t="n">
         <v>22180.93</v>
@@ -14251,7 +16239,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
-        <v>741</v>
+        <v>800</v>
       </c>
       <c r="B32" s="96" t="n">
         <f aca="false">SUM(B30:B31)</f>
@@ -14268,7 +16256,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>742</v>
+        <v>801</v>
       </c>
       <c r="D33" s="97" t="n">
         <f aca="false">D32</f>
@@ -14305,12 +16293,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="90" t="s">
-        <v>743</v>
+        <v>802</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>744</v>
+        <v>803</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14318,7 +16306,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="98" t="s">
-        <v>745</v>
+        <v>804</v>
       </c>
       <c r="C4" s="98" t="s">
         <v>30</v>
@@ -14374,7 +16362,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$149,A6)</f>
@@ -14576,11 +16564,11 @@
       </c>
       <c r="B12" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$149,A12)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">COUNTIFS('Scope Checklist'!$B$6:$B$149,A12,'Scope Checklist'!$E$6:$E$149,"Pending")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">COUNTIFS('Scope Checklist'!$B$6:$B$149,A12,'Scope Checklist'!$E$6:$E$149,"In Progress")</f>
@@ -14605,7 +16593,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$149,A13)</f>
@@ -14638,7 +16626,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$149,A14)</f>
@@ -14671,7 +16659,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B15" s="10" t="n">
         <f aca="false">COUNTIF('Scope Checklist'!$B$6:$B$149,A15)</f>
@@ -14704,15 +16692,15 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>746</v>
+        <v>805</v>
       </c>
       <c r="B16" s="86" t="n">
         <f aca="false">SUM(B5:B15)</f>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="86" t="n">
         <f aca="false">SUM(C5:C15)</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D16" s="86" t="n">
         <f aca="false">SUM(D5:D15)</f>
